--- a/hil_i2c_components.xlsx
+++ b/hil_i2c_components.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,10 +74,14 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00833C0B"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -104,14 +108,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BF8F00"/>
-        <bgColor rgb="00BF8F00"/>
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00BF8F00"/>
+        <bgColor rgb="00BF8F00"/>
       </patternFill>
     </fill>
     <fill>
@@ -148,6 +152,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C55A11"/>
         <bgColor rgb="00C55A11"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B084"/>
+        <bgColor rgb="00F4B084"/>
       </patternFill>
     </fill>
     <fill>
@@ -203,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -226,11 +236,11 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -245,10 +255,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -264,6 +274,9 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -274,9 +287,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2224,12 +2237,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>pct2075</t>
+          <t>ltr303</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>PCT2075</t>
+          <t>LTR-303</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr"/>
@@ -2240,28 +2253,28 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>0x28, 0x29, 0x2A, 0x2B, 0x2C, 0x2D, 0x2E, 0x2F, 0x35, 0x36, 0x37, 0x48, 0x49, 0x4A, 0x4B, 0x4C, 0x4D, 0x4E, 0x4F, 0x70, 0x71, 0x72, 0x73, 0x74, 0x75, 0x76, 0x77</t>
+          <t>0x29</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0x28, 0x29, 0x2A, 0x2B, 0x2C, 0x2D, 0x2E, 0x2F, 0x35, 0x36, 0x37, 0x48, 0x49, 0x4A, 0x4B, 0x4C, 0x4D, 0x4E, 0x4F, 0x70, 0x72, 0x73, 0x74, 0x75, 0x76</t>
+          <t>0x29</t>
         </is>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>adt7410, as5600, as7331, bme280, bme680, bme688, bmp280, bmp388, bmp390, dps310, ltr303, ltr329, max17048, max44009, ms8607, nau7802, qmc5883p, rotary_encoder, shtc3, spa06_003, stemma_soil, tc74a0, tmp117, tmp119, tsl2591, vl53l0x, vl53l1x, vl53l4cd, vl53l4cx, vl6180x</t>
+          <t>ltr329, pct2075, tsl2591, vl53l0x, vl53l1x, vl53l4cd, vl53l4cx, vl6180x</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>ambient-temp, ambient-temp-fahrenheit</t>
+          <t>light, raw</t>
         </is>
       </c>
       <c r="K11" s="5" t="n"/>
@@ -2278,39 +2291,19 @@
       <c r="V11" s="5" t="n"/>
       <c r="W11" s="5" t="n"/>
       <c r="X11" s="5" t="n"/>
-      <c r="Y11" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y11" s="5" t="n"/>
       <c r="Z11" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AA11" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC11" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH11" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI11" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="AA11" s="5" t="n"/>
+      <c r="AB11" s="5" t="n"/>
+      <c r="AC11" s="5" t="n"/>
+      <c r="AD11" s="5" t="n"/>
+      <c r="AE11" s="5" t="n"/>
+      <c r="AF11" s="5" t="n"/>
+      <c r="AG11" s="5" t="n"/>
+      <c r="AH11" s="5" t="n"/>
+      <c r="AI11" s="5" t="n"/>
       <c r="AJ11" s="5" t="n"/>
       <c r="AK11" s="5" t="n"/>
       <c r="AL11" s="5" t="n"/>
@@ -2323,30 +2316,14 @@
       <c r="AS11" s="5" t="n"/>
       <c r="AT11" s="5" t="n"/>
       <c r="AU11" s="5" t="n"/>
-      <c r="AV11" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW11" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX11" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY11" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC11" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AV11" s="5" t="n"/>
+      <c r="AW11" s="5" t="n"/>
+      <c r="AX11" s="5" t="n"/>
+      <c r="AY11" s="5" t="n"/>
+      <c r="AZ11" s="5" t="n"/>
+      <c r="BA11" s="5" t="n"/>
+      <c r="BB11" s="5" t="n"/>
+      <c r="BC11" s="5" t="n"/>
       <c r="BD11" s="5" t="n"/>
       <c r="BE11" s="5" t="n"/>
       <c r="BF11" s="5" t="n"/>
@@ -2366,40 +2343,24 @@
       <c r="BT11" s="5" t="n"/>
       <c r="BU11" s="5" t="n"/>
       <c r="BV11" s="5" t="n"/>
-      <c r="BW11" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BX11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BZ11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CA11" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="CB11" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="CC11" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="CD11" s="8" t="n">
-        <v>10</v>
-      </c>
+      <c r="BW11" s="5" t="n"/>
+      <c r="BX11" s="5" t="n"/>
+      <c r="BY11" s="5" t="n"/>
+      <c r="BZ11" s="5" t="n"/>
+      <c r="CA11" s="5" t="n"/>
+      <c r="CB11" s="5" t="n"/>
+      <c r="CC11" s="5" t="n"/>
+      <c r="CD11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ltr303</t>
+          <t>ltr329</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>LTR-303</t>
+          <t>LTR-329</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr"/>
@@ -2423,7 +2384,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>ltr329, pct2075, tsl2591, vl53l0x, vl53l1x, vl53l4cd, vl53l4cx, vl6180x</t>
+          <t>ltr303, pct2075, tsl2591, vl53l0x, vl53l1x, vl53l4cd, vl53l4cx, vl6180x</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
@@ -2512,12 +2473,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ltr329</t>
+          <t>tsl2591</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>LTR-329</t>
+          <t>TSL2591</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
@@ -2528,28 +2489,28 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>0x29</t>
+          <t>0x29, 0x39, 0x49</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0x29</t>
+          <t>0x29, 0x39, 0x49</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>ltr303, pct2075, tsl2591, vl53l0x, vl53l1x, vl53l4cd, vl53l4cx, vl6180x</t>
+          <t>adt7410, ltr303, ltr329, pct2075, rotary_encoder, stemma_soil, tmp117, tmp119, vl53l0x, vl53l1x, vl53l4cd, vl53l4cx, vl6180x</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>light, raw</t>
+          <t>light</t>
         </is>
       </c>
       <c r="K13" s="5" t="n"/>
@@ -2580,7 +2541,9 @@
       <c r="AH13" s="5" t="n"/>
       <c r="AI13" s="5" t="n"/>
       <c r="AJ13" s="5" t="n"/>
-      <c r="AK13" s="5" t="n"/>
+      <c r="AK13" s="7" t="n">
+        <v>3</v>
+      </c>
       <c r="AL13" s="5" t="n"/>
       <c r="AM13" s="5" t="n"/>
       <c r="AN13" s="5" t="n"/>
@@ -2592,7 +2555,9 @@
       <c r="AT13" s="5" t="n"/>
       <c r="AU13" s="5" t="n"/>
       <c r="AV13" s="5" t="n"/>
-      <c r="AW13" s="5" t="n"/>
+      <c r="AW13" s="7" t="n">
+        <v>5</v>
+      </c>
       <c r="AX13" s="5" t="n"/>
       <c r="AY13" s="5" t="n"/>
       <c r="AZ13" s="5" t="n"/>
@@ -2630,12 +2595,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>tsl2591</t>
+          <t>vl53l0x</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>TSL2591</t>
+          <t>VL53L0X</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr"/>
@@ -2646,28 +2611,28 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>0x29, 0x39, 0x49</t>
+          <t>0x29</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0x29, 0x39, 0x49</t>
+          <t>0x29</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>adt7410, ltr303, ltr329, pct2075, rotary_encoder, stemma_soil, tmp117, tmp119, vl53l0x, vl53l1x, vl53l4cd, vl53l4cx, vl6180x</t>
+          <t>ltr303, ltr329, pct2075, tsl2591, vl53l1x, vl53l4cd, vl53l4cx, vl6180x</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>proximity</t>
         </is>
       </c>
       <c r="K14" s="5" t="n"/>
@@ -2698,9 +2663,7 @@
       <c r="AH14" s="5" t="n"/>
       <c r="AI14" s="5" t="n"/>
       <c r="AJ14" s="5" t="n"/>
-      <c r="AK14" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="AK14" s="5" t="n"/>
       <c r="AL14" s="5" t="n"/>
       <c r="AM14" s="5" t="n"/>
       <c r="AN14" s="5" t="n"/>
@@ -2712,9 +2675,7 @@
       <c r="AT14" s="5" t="n"/>
       <c r="AU14" s="5" t="n"/>
       <c r="AV14" s="5" t="n"/>
-      <c r="AW14" s="7" t="n">
-        <v>5</v>
-      </c>
+      <c r="AW14" s="5" t="n"/>
       <c r="AX14" s="5" t="n"/>
       <c r="AY14" s="5" t="n"/>
       <c r="AZ14" s="5" t="n"/>
@@ -2752,12 +2713,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>vl53l0x</t>
+          <t>vl53l1x</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>VL53L0X</t>
+          <t>VL53L1X</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr"/>
@@ -2781,7 +2742,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>ltr303, ltr329, pct2075, tsl2591, vl53l1x, vl53l4cd, vl53l4cx, vl6180x</t>
+          <t>ltr303, ltr329, pct2075, tsl2591, vl53l0x, vl53l4cd, vl53l4cx, vl6180x</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
@@ -2870,12 +2831,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>vl53l1x</t>
+          <t>vl53l4cd</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>VL53L1X</t>
+          <t>VL53L4CD</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr"/>
@@ -2899,7 +2860,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>ltr303, ltr329, pct2075, tsl2591, vl53l0x, vl53l4cd, vl53l4cx, vl6180x</t>
+          <t>ltr303, ltr329, pct2075, tsl2591, vl53l0x, vl53l1x, vl53l4cx, vl6180x</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
@@ -2988,12 +2949,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>vl53l4cd</t>
+          <t>vl53l4cx</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>VL53L4CD</t>
+          <t>VL53L4CX</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr"/>
@@ -3017,7 +2978,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>ltr303, ltr329, pct2075, tsl2591, vl53l0x, vl53l1x, vl53l4cx, vl6180x</t>
+          <t>ltr303, ltr329, pct2075, tsl2591, vl53l0x, vl53l1x, vl53l4cd, vl6180x</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
@@ -3025,7 +2986,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>proximity</t>
+          <t>proximity, raw</t>
         </is>
       </c>
       <c r="K17" s="5" t="n"/>
@@ -3106,12 +3067,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>vl53l4cx</t>
+          <t>vl6180x</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VL53L4CX</t>
+          <t>VL6180X</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
@@ -3135,7 +3096,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>ltr303, ltr329, pct2075, tsl2591, vl53l0x, vl53l1x, vl53l4cd, vl6180x</t>
+          <t>ltr303, ltr329, pct2075, tsl2591, vl53l0x, vl53l1x, vl53l4cd, vl53l4cx</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
@@ -3143,7 +3104,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>proximity, raw</t>
+          <t>proximity, light</t>
         </is>
       </c>
       <c r="K18" s="5" t="n"/>
@@ -3224,12 +3185,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>vl6180x</t>
+          <t>nau7802</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>VL6180X</t>
+          <t>NAU7802</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr"/>
@@ -3240,7 +3201,7 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>0x29</t>
+          <t>0x2A</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
@@ -3248,20 +3209,20 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0x29</t>
+          <t>0x2A</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>ltr303, ltr329, pct2075, tsl2591, vl53l0x, vl53l1x, vl53l4cd, vl53l4cx</t>
+          <t>pct2075</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>proximity, light</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="K19" s="5" t="n"/>
@@ -3279,10 +3240,10 @@
       <c r="W19" s="5" t="n"/>
       <c r="X19" s="5" t="n"/>
       <c r="Y19" s="5" t="n"/>
-      <c r="Z19" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA19" s="5" t="n"/>
+      <c r="Z19" s="5" t="n"/>
+      <c r="AA19" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="AB19" s="5" t="n"/>
       <c r="AC19" s="5" t="n"/>
       <c r="AD19" s="5" t="n"/>
@@ -3342,12 +3303,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>nau7802</t>
+          <t>qmc5883p</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>NAU7802</t>
+          <t>QMC5883P</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
@@ -3358,7 +3319,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>0x2A</t>
+          <t>0x2C</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -3366,7 +3327,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0x2A</t>
+          <t>0x2C</t>
         </is>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -3398,11 +3359,11 @@
       <c r="X20" s="5" t="n"/>
       <c r="Y20" s="5" t="n"/>
       <c r="Z20" s="5" t="n"/>
-      <c r="AA20" s="7" t="n">
+      <c r="AA20" s="5" t="n"/>
+      <c r="AB20" s="5" t="n"/>
+      <c r="AC20" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AB20" s="5" t="n"/>
-      <c r="AC20" s="5" t="n"/>
       <c r="AD20" s="5" t="n"/>
       <c r="AE20" s="5" t="n"/>
       <c r="AF20" s="5" t="n"/>
@@ -3460,12 +3421,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>qmc5883p</t>
+          <t>as5600</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>QMC5883P</t>
+          <t>AS5600 Magnetic Angle</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr"/>
@@ -3476,7 +3437,7 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>0x2C</t>
+          <t>0x36</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -3484,16 +3445,16 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0x2C</t>
+          <t>0x36</t>
         </is>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>pct2075</t>
+          <t>max17048, pct2075, rotary_encoder, stemma_soil</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -3518,14 +3479,14 @@
       <c r="Z21" s="5" t="n"/>
       <c r="AA21" s="5" t="n"/>
       <c r="AB21" s="5" t="n"/>
-      <c r="AC21" s="7" t="n">
-        <v>2</v>
-      </c>
+      <c r="AC21" s="5" t="n"/>
       <c r="AD21" s="5" t="n"/>
       <c r="AE21" s="5" t="n"/>
       <c r="AF21" s="5" t="n"/>
       <c r="AG21" s="5" t="n"/>
-      <c r="AH21" s="5" t="n"/>
+      <c r="AH21" s="7" t="n">
+        <v>5</v>
+      </c>
       <c r="AI21" s="5" t="n"/>
       <c r="AJ21" s="5" t="n"/>
       <c r="AK21" s="5" t="n"/>
@@ -3578,12 +3539,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>as5600</t>
+          <t>max17048</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>AS5600 Magnetic Angle</t>
+          <t>MAX17048/MAX17049</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr"/>
@@ -3607,7 +3568,7 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>max17048, pct2075, rotary_encoder, stemma_soil</t>
+          <t>as5600, pct2075, rotary_encoder, stemma_soil</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
@@ -3615,7 +3576,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>voltage, unitless-percent</t>
         </is>
       </c>
       <c r="K22" s="5" t="n"/>
@@ -3694,46 +3655,46 @@
       <c r="CD22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>max17048</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>MAX17048/MAX17049</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr"/>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>0x36</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>0x36</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>as5600, pct2075, rotary_encoder, stemma_soil</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>voltage, unitless-percent</t>
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>rotary_encoder</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>STEMMA QT Rotary Encoder</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>0x36, 0x37, 0x38, 0x39, 0x3A, 0x3B, 0x3C, 0x3D</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>0x36, 0x37, 0x38, 0x39, 0x3A, 0x3B, 0x3C, 0x3D</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>aht20, aht21, am2301b, am2315c, as5600, dht20, max17048, mlx90632b, mlx90632d_ext, mlx90632d_med, pct2075, stemma_soil, tsl2591</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>raw</t>
         </is>
       </c>
       <c r="K23" s="5" t="n"/>
@@ -3762,13 +3723,27 @@
       <c r="AH23" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AI23" s="5" t="n"/>
-      <c r="AJ23" s="5" t="n"/>
-      <c r="AK23" s="5" t="n"/>
-      <c r="AL23" s="5" t="n"/>
-      <c r="AM23" s="5" t="n"/>
-      <c r="AN23" s="5" t="n"/>
-      <c r="AO23" s="5" t="n"/>
+      <c r="AI23" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ23" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK23" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL23" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM23" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AP23" s="5" t="n"/>
       <c r="AQ23" s="5" t="n"/>
       <c r="AR23" s="5" t="n"/>
@@ -3812,46 +3787,46 @@
       <c r="CD23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>rotary_encoder</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>STEMMA QT Rotary Encoder</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr"/>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>0x36, 0x37, 0x38, 0x39, 0x3A, 0x3B, 0x3C, 0x3D</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>0x36, 0x37, 0x38, 0x39, 0x3A, 0x3B, 0x3C, 0x3D</t>
-        </is>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>aht20, aht21, am2301b, am2315c, as5600, dht20, max17048, mlx90632b, mlx90632d_ext, mlx90632d_med, pct2075, stemma_soil, tsl2591</t>
-        </is>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t>raw</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>stemma_soil</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>STEMMA Soil Sensor</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>0x36, 0x37, 0x38, 0x39</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0x36, 0x37, 0x38, 0x39</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>aht20, aht21, am2301b, am2315c, as5600, dht20, max17048, pct2075, rotary_encoder, tsl2591</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, raw</t>
         </is>
       </c>
       <c r="K24" s="5" t="n"/>
@@ -3889,18 +3864,10 @@
       <c r="AK24" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AL24" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM24" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO24" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AL24" s="5" t="n"/>
+      <c r="AM24" s="5" t="n"/>
+      <c r="AN24" s="5" t="n"/>
+      <c r="AO24" s="5" t="n"/>
       <c r="AP24" s="5" t="n"/>
       <c r="AQ24" s="5" t="n"/>
       <c r="AR24" s="5" t="n"/>
@@ -3946,12 +3913,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>stemma_soil</t>
+          <t>pct2075</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>STEMMA Soil Sensor</t>
+          <t>PCT2075</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr"/>
@@ -3962,28 +3929,28 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>0x36, 0x37, 0x38, 0x39</t>
+          <t>0x37, 0x36, 0x35, 0x2F, 0x2E, 0x2D, 0x2C, 0x2B, 0x2A, 0x29, 0x28, 0x77, 0x76, 0x75, 0x74, 0x73, 0x72, 0x71, 0x70, 0x4F, 0x4E, 0x4D, 0x4C, 0x4B, 0x4A, 0x49, 0x48</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0x36, 0x37, 0x38, 0x39</t>
+          <t>0x37, 0x36, 0x35, 0x2F, 0x2E, 0x2D, 0x2C, 0x2B, 0x2A, 0x29, 0x28, 0x76, 0x75, 0x74, 0x73, 0x72, 0x70, 0x4F, 0x4E, 0x4D, 0x4C, 0x4B, 0x4A, 0x49, 0x48</t>
         </is>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>aht20, aht21, am2301b, am2315c, as5600, dht20, max17048, pct2075, rotary_encoder, tsl2591</t>
+          <t>adt7410, as5600, as7331, bme280, bme680, bme688, bmp280, bmp388, bmp390, dps310, ltr303, ltr329, max17048, max44009, ms8607, nau7802, qmc5883p, rotary_encoder, shtc3, spa06_003, stemma_soil, tc74a0, tmp117, tmp119, tsl2591, vl53l0x, vl53l1x, vl53l4cd, vl53l4cx, vl6180x</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>ambient-temp, ambient-temp-fahrenheit, raw</t>
+          <t>ambient-temp, ambient-temp-fahrenheit</t>
         </is>
       </c>
       <c r="K25" s="5" t="n"/>
@@ -4000,27 +3967,41 @@
       <c r="V25" s="5" t="n"/>
       <c r="W25" s="5" t="n"/>
       <c r="X25" s="5" t="n"/>
-      <c r="Y25" s="5" t="n"/>
-      <c r="Z25" s="5" t="n"/>
-      <c r="AA25" s="5" t="n"/>
-      <c r="AB25" s="5" t="n"/>
-      <c r="AC25" s="5" t="n"/>
-      <c r="AD25" s="5" t="n"/>
-      <c r="AE25" s="5" t="n"/>
-      <c r="AF25" s="5" t="n"/>
-      <c r="AG25" s="5" t="n"/>
+      <c r="Y25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA25" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG25" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AH25" s="7" t="n">
         <v>5</v>
       </c>
       <c r="AI25" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AJ25" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK25" s="7" t="n">
-        <v>3</v>
-      </c>
+      <c r="AJ25" s="5" t="n"/>
+      <c r="AK25" s="5" t="n"/>
       <c r="AL25" s="5" t="n"/>
       <c r="AM25" s="5" t="n"/>
       <c r="AN25" s="5" t="n"/>
@@ -4031,14 +4012,30 @@
       <c r="AS25" s="5" t="n"/>
       <c r="AT25" s="5" t="n"/>
       <c r="AU25" s="5" t="n"/>
-      <c r="AV25" s="5" t="n"/>
-      <c r="AW25" s="5" t="n"/>
-      <c r="AX25" s="5" t="n"/>
-      <c r="AY25" s="5" t="n"/>
-      <c r="AZ25" s="5" t="n"/>
-      <c r="BA25" s="5" t="n"/>
-      <c r="BB25" s="5" t="n"/>
-      <c r="BC25" s="5" t="n"/>
+      <c r="AV25" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW25" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX25" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY25" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC25" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="BD25" s="5" t="n"/>
       <c r="BE25" s="5" t="n"/>
       <c r="BF25" s="5" t="n"/>
@@ -4058,14 +4055,30 @@
       <c r="BT25" s="5" t="n"/>
       <c r="BU25" s="5" t="n"/>
       <c r="BV25" s="5" t="n"/>
-      <c r="BW25" s="5" t="n"/>
-      <c r="BX25" s="5" t="n"/>
-      <c r="BY25" s="5" t="n"/>
-      <c r="BZ25" s="5" t="n"/>
-      <c r="CA25" s="5" t="n"/>
-      <c r="CB25" s="5" t="n"/>
-      <c r="CC25" s="5" t="n"/>
-      <c r="CD25" s="5" t="n"/>
+      <c r="BW25" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BX25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BZ25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA25" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CB25" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="CC25" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="CD25" s="9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -7084,7 +7097,7 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>0x46, 0x47</t>
+          <t>0x47, 0x46</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
@@ -7092,7 +7105,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>0x46, 0x47</t>
+          <t>0x47, 0x46</t>
         </is>
       </c>
       <c r="H51" s="6" t="inlineStr">
@@ -7204,7 +7217,7 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>0x46, 0x47</t>
+          <t>0x47, 0x46</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
@@ -7212,7 +7225,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>0x46, 0x47</t>
+          <t>0x47, 0x46</t>
         </is>
       </c>
       <c r="H52" s="6" t="inlineStr">
@@ -7324,7 +7337,7 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>0x46, 0x47</t>
+          <t>0x47, 0x46</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
@@ -7332,7 +7345,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>0x46, 0x47</t>
+          <t>0x47, 0x46</t>
         </is>
       </c>
       <c r="H53" s="6" t="inlineStr">
@@ -8986,12 +8999,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>lps22hb</t>
+          <t>lps28dfw</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>LPS22HB</t>
+          <t>LPS28DFW</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr"/>
@@ -9015,7 +9028,7 @@
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>bh1750, lps25hb, lps28dfw, lps33hw, lps35hw</t>
+          <t>bh1750, lps22hb, lps25hb, lps33hw, lps35hw</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
@@ -9106,12 +9119,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>lps25hb</t>
+          <t>lps22hb</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>LPS25HB</t>
+          <t>LPS22HB</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr"/>
@@ -9122,7 +9135,7 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>0x5C, 0x5D</t>
+          <t>0x5D, 0x5C</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
@@ -9130,12 +9143,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>0x5C, 0x5D</t>
+          <t>0x5D, 0x5C</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>bh1750, lps22hb, lps28dfw, lps33hw, lps35hw</t>
+          <t>bh1750, lps25hb, lps28dfw, lps33hw, lps35hw</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
@@ -9226,12 +9239,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>lps28dfw</t>
+          <t>lps25hb</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>LPS28DFW</t>
+          <t>LPS25HB</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr"/>
@@ -9242,7 +9255,7 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>0x5C, 0x5D</t>
+          <t>0x5D, 0x5C</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
@@ -9250,12 +9263,12 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>0x5C, 0x5D</t>
+          <t>0x5D, 0x5C</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>bh1750, lps22hb, lps25hb, lps33hw, lps35hw</t>
+          <t>bh1750, lps22hb, lps28dfw, lps33hw, lps35hw</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
@@ -9362,7 +9375,7 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>0x5C, 0x5D</t>
+          <t>0x5D, 0x5C</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
@@ -9370,7 +9383,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>0x5C, 0x5D</t>
+          <t>0x5D, 0x5C</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
@@ -9482,7 +9495,7 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>0x5C, 0x5D</t>
+          <t>0x5D, 0x5C</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
@@ -9490,7 +9503,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>0x5C, 0x5D</t>
+          <t>0x5D, 0x5C</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
@@ -9702,46 +9715,46 @@
       <c r="CD72" s="5" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="inlineStr">
-        <is>
-          <t>mcp9601</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>MCP9601</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="inlineStr"/>
-      <c r="D73" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>0x60, 0x61, 0x62, 0x63, 0x64, 0x65, 0x66, 0x67</t>
-        </is>
-      </c>
-      <c r="F73" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>0x60, 0x61, 0x62, 0x63, 0x64, 0x65, 0x66, 0x67</t>
-        </is>
-      </c>
-      <c r="H73" s="9" t="inlineStr">
-        <is>
-          <t>mpl115a2, scd30, scd40, vcnl4040</t>
-        </is>
-      </c>
-      <c r="I73" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J73" s="9" t="inlineStr">
-        <is>
-          <t>ambient-temp, ambient-temp-fahrenheit, raw</t>
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>mpl115a2</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>MPL115A2</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr"/>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>0x60</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>0x60</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>mcp9601, vcnl4040</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure</t>
         </is>
       </c>
       <c r="K73" s="5" t="n"/>
@@ -9800,27 +9813,13 @@
       <c r="BL73" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="BM73" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BN73" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS73" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="BM73" s="5" t="n"/>
+      <c r="BN73" s="5" t="n"/>
+      <c r="BO73" s="5" t="n"/>
+      <c r="BP73" s="5" t="n"/>
+      <c r="BQ73" s="5" t="n"/>
+      <c r="BR73" s="5" t="n"/>
+      <c r="BS73" s="5" t="n"/>
       <c r="BT73" s="5" t="n"/>
       <c r="BU73" s="5" t="n"/>
       <c r="BV73" s="5" t="n"/>
@@ -9836,12 +9835,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>mpl115a2</t>
+          <t>vcnl4040</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>MPL115A2</t>
+          <t>VCNL4040</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr"/>
@@ -9865,7 +9864,7 @@
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>mcp9601, vcnl4040</t>
+          <t>mcp9601, mpl115a2</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
@@ -9873,7 +9872,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>ambient-temp, ambient-temp-fahrenheit, pressure</t>
+          <t>light, proximity</t>
         </is>
       </c>
       <c r="K74" s="5" t="n"/>
@@ -9954,12 +9953,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>vcnl4040</t>
+          <t>scd30</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>VCNL4040</t>
+          <t>SCD30</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr"/>
@@ -9970,7 +9969,7 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>0x60</t>
+          <t>0x61</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
@@ -9978,20 +9977,20 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>0x60</t>
+          <t>0x61</t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>mcp9601, mpl115a2</t>
+          <t>mcp9601</t>
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>light, proximity</t>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, co2</t>
         </is>
       </c>
       <c r="K75" s="5" t="n"/>
@@ -10047,10 +10046,10 @@
       <c r="BI75" s="5" t="n"/>
       <c r="BJ75" s="5" t="n"/>
       <c r="BK75" s="5" t="n"/>
-      <c r="BL75" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM75" s="5" t="n"/>
+      <c r="BL75" s="5" t="n"/>
+      <c r="BM75" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="BN75" s="5" t="n"/>
       <c r="BO75" s="5" t="n"/>
       <c r="BP75" s="5" t="n"/>
@@ -10072,12 +10071,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>scd30</t>
+          <t>scd40</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>SCD30</t>
+          <t>SCD40/SCD41</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
@@ -10088,7 +10087,7 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>0x61</t>
+          <t>0x62</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
@@ -10096,7 +10095,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>0x61</t>
+          <t>0x62</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
@@ -10166,10 +10165,10 @@
       <c r="BJ76" s="5" t="n"/>
       <c r="BK76" s="5" t="n"/>
       <c r="BL76" s="5" t="n"/>
-      <c r="BM76" s="7" t="n">
+      <c r="BM76" s="5" t="n"/>
+      <c r="BN76" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="BN76" s="5" t="n"/>
       <c r="BO76" s="5" t="n"/>
       <c r="BP76" s="5" t="n"/>
       <c r="BQ76" s="5" t="n"/>
@@ -10188,46 +10187,46 @@
       <c r="CD76" s="5" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>scd40</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>SCD40/SCD41</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr"/>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>0x62</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>0x62</t>
-        </is>
-      </c>
-      <c r="H77" s="6" t="inlineStr">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>mcp9601</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>ambient-temp, ambient-temp-fahrenheit, humidity, co2</t>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>MCP9601</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr"/>
+      <c r="D77" s="8" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>0x67, 0x66, 0x65, 0x64, 0x63, 0x62, 0x61, 0x60</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G77" s="8" t="inlineStr">
+        <is>
+          <t>0x67, 0x66, 0x65, 0x64, 0x63, 0x62, 0x61, 0x60</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>mpl115a2, scd30, scd40, vcnl4040</t>
+        </is>
+      </c>
+      <c r="I77" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J77" s="8" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, raw</t>
         </is>
       </c>
       <c r="K77" s="5" t="n"/>
@@ -10283,16 +10282,30 @@
       <c r="BI77" s="5" t="n"/>
       <c r="BJ77" s="5" t="n"/>
       <c r="BK77" s="5" t="n"/>
-      <c r="BL77" s="5" t="n"/>
-      <c r="BM77" s="5" t="n"/>
+      <c r="BL77" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM77" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="BN77" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="BO77" s="5" t="n"/>
-      <c r="BP77" s="5" t="n"/>
-      <c r="BQ77" s="5" t="n"/>
-      <c r="BR77" s="5" t="n"/>
-      <c r="BS77" s="5" t="n"/>
+      <c r="BO77" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP77" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ77" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR77" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS77" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="BT77" s="5" t="n"/>
       <c r="BU77" s="5" t="n"/>
       <c r="BV77" s="5" t="n"/>
@@ -10778,44 +10791,44 @@
       <c r="CD81" s="5" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>sen5x</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>SEN5x</t>
         </is>
       </c>
-      <c r="C82" s="9" t="inlineStr"/>
-      <c r="D82" s="9" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr"/>
+      <c r="D82" s="8" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E82" s="9" t="inlineStr">
+      <c r="E82" s="8" t="inlineStr">
         <is>
           <t>0x69</t>
         </is>
       </c>
-      <c r="F82" s="9" t="n">
+      <c r="F82" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G82" s="9" t="inlineStr">
+      <c r="G82" s="8" t="inlineStr">
         <is>
           <t>0x69</t>
         </is>
       </c>
-      <c r="H82" s="9" t="inlineStr">
+      <c r="H82" s="8" t="inlineStr">
         <is>
           <t>sen50, sen54, sen55</t>
         </is>
       </c>
-      <c r="I82" s="9" t="n">
+      <c r="I82" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="J82" s="9" t="inlineStr">
+      <c r="J82" s="8" t="inlineStr">
         <is>
           <t>ambient-temp, ambient-temp-fahrenheit, humidity, pm10-std, pm25-std, pm100-std, voc-index, nox-index</t>
         </is>
@@ -11251,7 +11264,7 @@
       <c r="CC85" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="CD85" s="8" t="n">
+      <c r="CD85" s="9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -11274,7 +11287,7 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>0x76, 0x77</t>
+          <t>0x77, 0x76</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
@@ -11371,7 +11384,7 @@
       <c r="CC86" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="CD86" s="8" t="n">
+      <c r="CD86" s="9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -11394,7 +11407,7 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>0x76, 0x77</t>
+          <t>0x77, 0x76</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
@@ -11491,7 +11504,7 @@
       <c r="CC87" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="CD87" s="8" t="n">
+      <c r="CD87" s="9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -11514,7 +11527,7 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>0x76, 0x77</t>
+          <t>0x77, 0x76</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
@@ -11611,7 +11624,7 @@
       <c r="CC88" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="CD88" s="8" t="n">
+      <c r="CD88" s="9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -11634,7 +11647,7 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>0x76, 0x77</t>
+          <t>0x77, 0x76</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
@@ -11731,7 +11744,7 @@
       <c r="CC89" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="CD89" s="8" t="n">
+      <c r="CD89" s="9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -11754,7 +11767,7 @@
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>0x76, 0x77</t>
+          <t>0x77, 0x76</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
@@ -11851,7 +11864,7 @@
       <c r="CC90" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="CD90" s="8" t="n">
+      <c r="CD90" s="9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -11874,7 +11887,7 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>0x76, 0x77</t>
+          <t>0x77, 0x76</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
@@ -11971,7 +11984,7 @@
       <c r="CC91" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="CD91" s="8" t="n">
+      <c r="CD91" s="9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -11994,7 +12007,7 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>0x76, 0x77</t>
+          <t>0x77, 0x76</t>
         </is>
       </c>
       <c r="F92" s="2" t="n">
@@ -12091,7 +12104,7 @@
       <c r="CC92" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="CD92" s="8" t="n">
+      <c r="CD92" s="9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -12114,7 +12127,7 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>0x76, 0x77</t>
+          <t>0x77, 0x76</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
@@ -12211,7 +12224,7 @@
       <c r="CC93" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="CD93" s="8" t="n">
+      <c r="CD93" s="9" t="n">
         <v>10</v>
       </c>
     </row>
@@ -12227,7 +12240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL118"/>
+  <dimension ref="A1:BN118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12290,9 +12303,11 @@
     <col width="18" customWidth="1" min="59" max="59"/>
     <col width="28" customWidth="1" min="60" max="60"/>
     <col width="14" customWidth="1" min="61" max="61"/>
-    <col width="36" customWidth="1" min="62" max="62"/>
-    <col width="26" customWidth="1" min="63" max="63"/>
-    <col width="9" customWidth="1" min="64" max="64"/>
+    <col width="14" customWidth="1" min="62" max="62"/>
+    <col width="36" customWidth="1" min="63" max="63"/>
+    <col width="26" customWidth="1" min="64" max="64"/>
+    <col width="9" customWidth="1" min="65" max="65"/>
+    <col width="14" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12380,7 +12395,7 @@
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>0x0A, 0x0B, 0x10, 0x12, 0x13, 0x19, 0x23, 0x28, 0x3C, 0x51, 0x58, 0x5F, 0x63, 0x68, 0x6B</t>
+          <t>0x0A, 0x0B, 0x10, 0x12, 0x13, 0x19, 0x23, 0x35, 0x3C, 0x51, 0x58, 0x5F, 0x67, 0x68, 0x6B</t>
         </is>
       </c>
     </row>
@@ -12416,7 +12431,7 @@
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>0x18, 0x29, 0x36, 0x38, 0x3A, 0x40, 0x41, 0x44, 0x45, 0x46, 0x48, 0x52, 0x53, 0x59, 0x5C, 0x5D, 0x60, 0x69, 0x76</t>
+          <t>0x18, 0x29, 0x36, 0x38, 0x3A, 0x40, 0x41, 0x44, 0x45, 0x47, 0x48, 0x52, 0x53, 0x59, 0x5C, 0x5D, 0x60, 0x69, 0x76</t>
         </is>
       </c>
     </row>
@@ -12434,7 +12449,7 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>0x29, 0x38, 0x40, 0x41, 0x44, 0x45, 0x5C, 0x69, 0x76</t>
+          <t>0x29, 0x38, 0x40, 0x41, 0x44, 0x45, 0x5D, 0x69, 0x76</t>
         </is>
       </c>
     </row>
@@ -12804,17 +12819,27 @@
       </c>
       <c r="BJ26" s="1" t="inlineStr">
         <is>
+          <t>Default Address</t>
+        </is>
+      </c>
+      <c r="BK26" s="1" t="inlineStr">
+        <is>
           <t>All Addresses</t>
         </is>
       </c>
-      <c r="BK26" s="1" t="inlineStr">
+      <c r="BL26" s="1" t="inlineStr">
         <is>
           <t>Vendor</t>
         </is>
       </c>
-      <c r="BL26" s="1" t="inlineStr">
+      <c r="BM26" s="1" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="BN26" s="1" t="inlineStr">
+        <is>
+          <t>Non-Default?</t>
         </is>
       </c>
     </row>
@@ -13120,12 +13145,18 @@
           <t>0x0A</t>
         </is>
       </c>
-      <c r="BK27" s="29" t="inlineStr"/>
-      <c r="BL27" s="29" t="inlineStr">
+      <c r="BK27" s="29" t="inlineStr">
+        <is>
+          <t>0x0A</t>
+        </is>
+      </c>
+      <c r="BL27" s="29" t="inlineStr"/>
+      <c r="BM27" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN27" s="29" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -13333,14 +13364,14 @@
           <t>SPA06-003</t>
         </is>
       </c>
-      <c r="AZ28" s="2" t="inlineStr">
+      <c r="AZ28" s="30" t="inlineStr">
         <is>
           <t>0x76</t>
         </is>
       </c>
       <c r="BA28" s="2" t="inlineStr">
         <is>
-          <t>0x76, 0x77</t>
+          <t>0x77, 0x76</t>
         </is>
       </c>
       <c r="BB28" s="2" t="inlineStr"/>
@@ -13375,12 +13406,18 @@
           <t>0x0B</t>
         </is>
       </c>
-      <c r="BK28" s="29" t="inlineStr"/>
-      <c r="BL28" s="29" t="inlineStr">
+      <c r="BK28" s="29" t="inlineStr">
+        <is>
+          <t>0x0B</t>
+        </is>
+      </c>
+      <c r="BL28" s="29" t="inlineStr"/>
+      <c r="BM28" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN28" s="29" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -13540,14 +13577,14 @@
           <t>BMP390</t>
         </is>
       </c>
-      <c r="AN29" s="2" t="inlineStr">
+      <c r="AN29" s="30" t="inlineStr">
         <is>
           <t>0x76</t>
         </is>
       </c>
       <c r="AO29" s="2" t="inlineStr">
         <is>
-          <t>0x76, 0x77</t>
+          <t>0x77, 0x76</t>
         </is>
       </c>
       <c r="AP29" s="2" t="inlineStr"/>
@@ -13564,14 +13601,14 @@
           <t>DPS310</t>
         </is>
       </c>
-      <c r="AT29" s="2" t="inlineStr">
+      <c r="AT29" s="30" t="inlineStr">
         <is>
           <t>0x76</t>
         </is>
       </c>
       <c r="AU29" s="2" t="inlineStr">
         <is>
-          <t>0x76, 0x77</t>
+          <t>0x77, 0x76</t>
         </is>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
@@ -13606,12 +13643,18 @@
           <t>0x10</t>
         </is>
       </c>
-      <c r="BK29" s="29" t="inlineStr"/>
-      <c r="BL29" s="29" t="inlineStr">
+      <c r="BK29" s="29" t="inlineStr">
+        <is>
+          <t>0x10</t>
+        </is>
+      </c>
+      <c r="BL29" s="29" t="inlineStr"/>
+      <c r="BM29" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN29" s="29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -13789,12 +13832,18 @@
           <t>0x12</t>
         </is>
       </c>
-      <c r="BK30" s="29" t="inlineStr"/>
-      <c r="BL30" s="29" t="inlineStr">
+      <c r="BK30" s="29" t="inlineStr">
+        <is>
+          <t>0x12</t>
+        </is>
+      </c>
+      <c r="BL30" s="29" t="inlineStr"/>
+      <c r="BM30" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN30" s="29" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -13882,7 +13931,7 @@
           <t>INA228</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="V31" s="30" t="inlineStr">
         <is>
           <t>0x41</t>
         </is>
@@ -13906,7 +13955,7 @@
           <t>INA238</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
+      <c r="AB31" s="30" t="inlineStr">
         <is>
           <t>0x41</t>
         </is>
@@ -13930,14 +13979,14 @@
           <t>BMP388</t>
         </is>
       </c>
-      <c r="AH31" s="2" t="inlineStr">
+      <c r="AH31" s="30" t="inlineStr">
         <is>
           <t>0x76</t>
         </is>
       </c>
       <c r="AI31" s="2" t="inlineStr">
         <is>
-          <t>0x76, 0x77</t>
+          <t>0x77, 0x76</t>
         </is>
       </c>
       <c r="AJ31" s="2" t="inlineStr"/>
@@ -13972,12 +14021,18 @@
           <t>0x13</t>
         </is>
       </c>
-      <c r="BK31" s="29" t="inlineStr"/>
-      <c r="BL31" s="29" t="inlineStr">
+      <c r="BK31" s="29" t="inlineStr">
+        <is>
+          <t>0x13</t>
+        </is>
+      </c>
+      <c r="BL31" s="29" t="inlineStr"/>
+      <c r="BM31" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN31" s="29" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -14121,20 +14176,30 @@
           <t>MCP9808</t>
         </is>
       </c>
-      <c r="BI32" s="29" t="inlineStr">
+      <c r="BI32" s="30" t="inlineStr">
         <is>
           <t>0x19</t>
         </is>
       </c>
       <c r="BJ32" s="29" t="inlineStr">
         <is>
+          <t>0x18</t>
+        </is>
+      </c>
+      <c r="BK32" s="29" t="inlineStr">
+        <is>
           <t>0x18, 0x19, 0x1A, 0x1B, 0x1C, 0x1D, 0x1E, 0x1F</t>
         </is>
       </c>
-      <c r="BK32" s="29" t="inlineStr"/>
-      <c r="BL32" s="29" t="inlineStr">
+      <c r="BL32" s="29" t="inlineStr"/>
+      <c r="BM32" s="29" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="BN32" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14217,7 @@
           <t>MCP9808</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="30" t="inlineStr">
         <is>
           <t>0x19</t>
         </is>
@@ -14176,7 +14241,7 @@
           <t>STEMMA Soil Sensor</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="J33" s="30" t="inlineStr">
         <is>
           <t>0x37</t>
         </is>
@@ -14224,7 +14289,7 @@
           <t>INA237</t>
         </is>
       </c>
-      <c r="V33" s="2" t="inlineStr">
+      <c r="V33" s="30" t="inlineStr">
         <is>
           <t>0x45</t>
         </is>
@@ -14248,7 +14313,7 @@
           <t>INA260</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
+      <c r="AB33" s="30" t="inlineStr">
         <is>
           <t>0x45</t>
         </is>
@@ -14287,15 +14352,21 @@
       </c>
       <c r="BJ33" s="29" t="inlineStr">
         <is>
+          <t>0x23</t>
+        </is>
+      </c>
+      <c r="BK33" s="29" t="inlineStr">
+        <is>
           <t>0x23, 0x5C</t>
         </is>
       </c>
-      <c r="BK33" s="29" t="inlineStr"/>
-      <c r="BL33" s="29" t="inlineStr">
+      <c r="BL33" s="29" t="inlineStr"/>
+      <c r="BM33" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN33" s="29" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -14359,7 +14430,7 @@
           <t>INA219</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="P34" s="30" t="inlineStr">
         <is>
           <t>0x41</t>
         </is>
@@ -14385,39 +14456,39 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0x5C</t>
+          <t>0x5D</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0x5C, 0x5D</t>
+          <t>0x5D, 0x5C</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr"/>
-      <c r="Y34" s="9" t="n">
+      <c r="Y34" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="Z34" s="9" t="inlineStr">
+      <c r="Z34" s="8" t="inlineStr">
         <is>
           <t>sen5x</t>
         </is>
       </c>
-      <c r="AA34" s="9" t="inlineStr">
+      <c r="AA34" s="8" t="inlineStr">
         <is>
           <t>SEN5x</t>
         </is>
       </c>
-      <c r="AB34" s="9" t="inlineStr">
+      <c r="AB34" s="8" t="inlineStr">
         <is>
           <t>0x69</t>
         </is>
       </c>
-      <c r="AC34" s="9" t="inlineStr">
+      <c r="AC34" s="8" t="inlineStr">
         <is>
           <t>0x69</t>
         </is>
       </c>
-      <c r="AD34" s="9" t="inlineStr"/>
+      <c r="AD34" s="8" t="inlineStr"/>
       <c r="BD34" s="29" t="n">
         <v>8</v>
       </c>
@@ -14439,20 +14510,30 @@
           <t>PCT2075</t>
         </is>
       </c>
-      <c r="BI34" s="29" t="inlineStr">
-        <is>
-          <t>0x28</t>
+      <c r="BI34" s="30" t="inlineStr">
+        <is>
+          <t>0x35</t>
         </is>
       </c>
       <c r="BJ34" s="29" t="inlineStr">
         <is>
-          <t>0x28, 0x29, 0x2A, 0x2B, 0x2C, 0x2D, 0x2E, 0x2F, 0x35, 0x36, 0x37, 0x48, 0x49, 0x4A, 0x4B, 0x4C, 0x4D, 0x4E, 0x4F, 0x70, 0x71, 0x72, 0x73, 0x74, 0x75, 0x76, 0x77</t>
-        </is>
-      </c>
-      <c r="BK34" s="29" t="inlineStr"/>
-      <c r="BL34" s="29" t="inlineStr">
+          <t>0x37</t>
+        </is>
+      </c>
+      <c r="BK34" s="29" t="inlineStr">
+        <is>
+          <t>0x37, 0x36, 0x35, 0x2F, 0x2E, 0x2D, 0x2C, 0x2B, 0x2A, 0x29, 0x28, 0x77, 0x76, 0x75, 0x74, 0x73, 0x72, 0x71, 0x70, 0x4F, 0x4E, 0x4D, 0x4C, 0x4B, 0x4A, 0x49, 0x48</t>
+        </is>
+      </c>
+      <c r="BL34" s="29" t="inlineStr"/>
+      <c r="BM34" s="29" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="BN34" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
         </is>
       </c>
     </row>
@@ -14470,14 +14551,14 @@
           <t>PCT2075</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>0x28</t>
+      <c r="D35" s="30" t="inlineStr">
+        <is>
+          <t>0x35</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0x28, 0x29, 0x2A, 0x2B, 0x2C, 0x2D, 0x2E, 0x2F, 0x35, 0x36, 0x37, 0x48, 0x49, 0x4A, 0x4B, 0x4C, 0x4D, 0x4E, 0x4F, 0x70, 0x71, 0x72, 0x73, 0x74, 0x75, 0x76, 0x77</t>
+          <t>0x37, 0x36, 0x35, 0x2F, 0x2E, 0x2D, 0x2C, 0x2B, 0x2A, 0x29, 0x28, 0x77, 0x76, 0x75, 0x74, 0x73, 0x72, 0x71, 0x70, 0x4F, 0x4E, 0x4D, 0x4C, 0x4B, 0x4A, 0x49, 0x48</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
@@ -14494,7 +14575,7 @@
           <t>TSL2591</t>
         </is>
       </c>
-      <c r="J35" s="2" t="inlineStr">
+      <c r="J35" s="30" t="inlineStr">
         <is>
           <t>0x39</t>
         </is>
@@ -14566,14 +14647,14 @@
           <t>BMP280</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
+      <c r="AB35" s="30" t="inlineStr">
         <is>
           <t>0x76</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>0x76, 0x77</t>
+          <t>0x77, 0x76</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr"/>
@@ -14598,48 +14679,58 @@
           <t>STEMMA QT Rotary Encoder</t>
         </is>
       </c>
-      <c r="BI35" s="29" t="inlineStr">
+      <c r="BI35" s="30" t="inlineStr">
         <is>
           <t>0x3C</t>
         </is>
       </c>
       <c r="BJ35" s="29" t="inlineStr">
         <is>
+          <t>0x36</t>
+        </is>
+      </c>
+      <c r="BK35" s="29" t="inlineStr">
+        <is>
           <t>0x36, 0x37, 0x38, 0x39, 0x3A, 0x3B, 0x3C, 0x3D</t>
         </is>
       </c>
-      <c r="BK35" s="29" t="inlineStr"/>
-      <c r="BL35" s="29" t="inlineStr">
+      <c r="BL35" s="29" t="inlineStr"/>
+      <c r="BM35" s="29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
+      <c r="BN35" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="n">
+      <c r="A36" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>rotary_encoder</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>STEMMA QT Rotary Encoder</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>0x3C</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>0x36, 0x37, 0x38, 0x39, 0x3A, 0x3B, 0x3C, 0x3D</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr"/>
+      <c r="F36" s="8" t="inlineStr"/>
       <c r="G36" s="2" t="n">
         <v>9</v>
       </c>
@@ -14677,7 +14768,7 @@
           <t>HDC302x</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
+      <c r="P36" s="30" t="inlineStr">
         <is>
           <t>0x45</t>
         </is>
@@ -14701,14 +14792,14 @@
           <t>BME688</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="V36" s="30" t="inlineStr">
         <is>
           <t>0x76</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0x76, 0x77</t>
+          <t>0x77, 0x76</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr"/>
@@ -14743,12 +14834,18 @@
           <t>0x51</t>
         </is>
       </c>
-      <c r="BK36" s="29" t="inlineStr"/>
-      <c r="BL36" s="29" t="inlineStr">
+      <c r="BK36" s="29" t="inlineStr">
+        <is>
+          <t>0x51</t>
+        </is>
+      </c>
+      <c r="BL36" s="29" t="inlineStr"/>
+      <c r="BM36" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN36" s="29" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -14788,7 +14885,7 @@
           <t>MLX90632 (Extended Mode)</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="J37" s="30" t="inlineStr">
         <is>
           <t>0x3B</t>
         </is>
@@ -14814,12 +14911,12 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0x46</t>
+          <t>0x47</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0x46, 0x47</t>
+          <t>0x47, 0x46</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr"/>
@@ -14854,12 +14951,18 @@
           <t>0x58</t>
         </is>
       </c>
-      <c r="BK37" s="29" t="inlineStr"/>
-      <c r="BL37" s="29" t="inlineStr">
+      <c r="BK37" s="29" t="inlineStr">
+        <is>
+          <t>0x58</t>
+        </is>
+      </c>
+      <c r="BL37" s="29" t="inlineStr"/>
+      <c r="BM37" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN37" s="29" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -14965,12 +15068,18 @@
           <t>0x5F</t>
         </is>
       </c>
-      <c r="BK38" s="29" t="inlineStr"/>
-      <c r="BL38" s="29" t="inlineStr">
+      <c r="BK38" s="29" t="inlineStr">
+        <is>
+          <t>0x5F</t>
+        </is>
+      </c>
+      <c r="BL38" s="29" t="inlineStr"/>
+      <c r="BM38" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN38" s="29" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -15010,7 +15119,7 @@
           <t>HTU31D</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
+      <c r="J39" s="30" t="inlineStr">
         <is>
           <t>0x41</t>
         </is>
@@ -15068,46 +15177,52 @@
       </c>
       <c r="BI39" s="29" t="inlineStr">
         <is>
-          <t>0x63</t>
+          <t>0x67</t>
         </is>
       </c>
       <c r="BJ39" s="29" t="inlineStr">
         <is>
-          <t>0x60, 0x61, 0x62, 0x63, 0x64, 0x65, 0x66, 0x67</t>
-        </is>
-      </c>
-      <c r="BK39" s="29" t="inlineStr"/>
-      <c r="BL39" s="29" t="inlineStr">
+          <t>0x67</t>
+        </is>
+      </c>
+      <c r="BK39" s="29" t="inlineStr">
+        <is>
+          <t>0x67, 0x66, 0x65, 0x64, 0x63, 0x62, 0x61, 0x60</t>
+        </is>
+      </c>
+      <c r="BL39" s="29" t="inlineStr"/>
+      <c r="BM39" s="29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
+      <c r="BN39" s="29" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="n">
+      <c r="A40" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>mcp9601</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>MCP9601</t>
         </is>
       </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>0x63</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>0x60, 0x61, 0x62, 0x63, 0x64, 0x65, 0x66, 0x67</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr"/>
+      <c r="D40" s="8" t="inlineStr">
+        <is>
+          <t>0x67</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>0x67, 0x66, 0x65, 0x64, 0x63, 0x62, 0x61, 0x60</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr"/>
       <c r="G40" s="2" t="n">
         <v>13</v>
       </c>
@@ -15145,7 +15260,7 @@
           <t>ENS161</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr">
+      <c r="P40" s="30" t="inlineStr">
         <is>
           <t>0x53</t>
         </is>
@@ -15187,12 +15302,18 @@
           <t>0x68</t>
         </is>
       </c>
-      <c r="BK40" s="29" t="inlineStr"/>
-      <c r="BL40" s="29" t="inlineStr">
+      <c r="BK40" s="29" t="inlineStr">
+        <is>
+          <t>0x68</t>
+        </is>
+      </c>
+      <c r="BL40" s="29" t="inlineStr"/>
+      <c r="BM40" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN40" s="29" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -15232,7 +15353,7 @@
           <t>SHT3X</t>
         </is>
       </c>
-      <c r="J41" s="2" t="inlineStr">
+      <c r="J41" s="30" t="inlineStr">
         <is>
           <t>0x45</t>
         </is>
@@ -15298,12 +15419,18 @@
           <t>0x6B</t>
         </is>
       </c>
-      <c r="BK41" s="29" t="inlineStr"/>
-      <c r="BL41" s="29" t="inlineStr">
+      <c r="BK41" s="29" t="inlineStr">
+        <is>
+          <t>0x6B</t>
+        </is>
+      </c>
+      <c r="BL41" s="29" t="inlineStr"/>
+      <c r="BM41" s="29" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN41" s="29" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -15335,22 +15462,22 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>bmp580</t>
+          <t>bmp581</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>BMP580</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
+          <t>BMP581</t>
+        </is>
+      </c>
+      <c r="J42" s="30" t="inlineStr">
         <is>
           <t>0x46</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0x46, 0x47</t>
+          <t>0x47, 0x46</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr"/>
@@ -15378,43 +15505,49 @@
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr"/>
-      <c r="BD42" s="30" t="n">
+      <c r="BD42" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="BE42" s="30" t="n">
+      <c r="BE42" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF42" s="30" t="inlineStr">
+      <c r="BF42" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG42" s="30" t="inlineStr">
+      <c r="BG42" s="31" t="inlineStr">
         <is>
           <t>ds2484</t>
         </is>
       </c>
-      <c r="BH42" s="30" t="inlineStr">
+      <c r="BH42" s="31" t="inlineStr">
         <is>
           <t>DS2484</t>
         </is>
       </c>
-      <c r="BI42" s="30" t="inlineStr">
+      <c r="BI42" s="31" t="inlineStr">
         <is>
           <t>0x18</t>
         </is>
       </c>
-      <c r="BJ42" s="30" t="inlineStr">
+      <c r="BJ42" s="31" t="inlineStr">
         <is>
           <t>0x18</t>
         </is>
       </c>
-      <c r="BK42" s="30" t="inlineStr"/>
-      <c r="BL42" s="30" t="inlineStr">
+      <c r="BK42" s="31" t="inlineStr">
+        <is>
+          <t>0x18</t>
+        </is>
+      </c>
+      <c r="BL42" s="31" t="inlineStr"/>
+      <c r="BM42" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN42" s="31" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="G43" s="2" t="n">
@@ -15422,12 +15555,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>bmp581</t>
+          <t>bmp580</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>BMP581</t>
+          <t>BMP580</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15437,7 +15570,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0x46, 0x47</t>
+          <t>0x47, 0x46</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr"/>
@@ -15461,47 +15594,53 @@
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>0x5C, 0x5D</t>
+          <t>0x5D, 0x5C</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr"/>
-      <c r="BD43" s="30" t="n">
+      <c r="BD43" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="BE43" s="30" t="n">
+      <c r="BE43" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF43" s="30" t="inlineStr">
+      <c r="BF43" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG43" s="30" t="inlineStr">
+      <c r="BG43" s="31" t="inlineStr">
         <is>
           <t>ltr303</t>
         </is>
       </c>
-      <c r="BH43" s="30" t="inlineStr">
+      <c r="BH43" s="31" t="inlineStr">
         <is>
           <t>LTR-303</t>
         </is>
       </c>
-      <c r="BI43" s="30" t="inlineStr">
+      <c r="BI43" s="31" t="inlineStr">
         <is>
           <t>0x29</t>
         </is>
       </c>
-      <c r="BJ43" s="30" t="inlineStr">
+      <c r="BJ43" s="31" t="inlineStr">
         <is>
           <t>0x29</t>
         </is>
       </c>
-      <c r="BK43" s="30" t="inlineStr"/>
-      <c r="BL43" s="30" t="inlineStr">
+      <c r="BK43" s="31" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="BL43" s="31" t="inlineStr"/>
+      <c r="BM43" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN43" s="31" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="G44" s="2" t="n">
@@ -15552,43 +15691,49 @@
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr"/>
-      <c r="BD44" s="30" t="n">
+      <c r="BD44" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="BE44" s="30" t="n">
+      <c r="BE44" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF44" s="30" t="inlineStr">
+      <c r="BF44" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG44" s="30" t="inlineStr">
+      <c r="BG44" s="31" t="inlineStr">
         <is>
           <t>nau7802</t>
         </is>
       </c>
-      <c r="BH44" s="30" t="inlineStr">
+      <c r="BH44" s="31" t="inlineStr">
         <is>
           <t>NAU7802</t>
         </is>
       </c>
-      <c r="BI44" s="30" t="inlineStr">
+      <c r="BI44" s="31" t="inlineStr">
         <is>
           <t>0x2A</t>
         </is>
       </c>
-      <c r="BJ44" s="30" t="inlineStr">
+      <c r="BJ44" s="31" t="inlineStr">
         <is>
           <t>0x2A</t>
         </is>
       </c>
-      <c r="BK44" s="30" t="inlineStr"/>
-      <c r="BL44" s="30" t="inlineStr">
+      <c r="BK44" s="31" t="inlineStr">
+        <is>
+          <t>0x2A</t>
+        </is>
+      </c>
+      <c r="BL44" s="31" t="inlineStr"/>
+      <c r="BM44" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN44" s="31" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="G45" s="2" t="n">
@@ -15604,7 +15749,7 @@
           <t>ADT7410</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="J45" s="30" t="inlineStr">
         <is>
           <t>0x49</t>
         </is>
@@ -15639,43 +15784,49 @@
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr"/>
-      <c r="BD45" s="30" t="n">
+      <c r="BD45" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="BE45" s="30" t="n">
+      <c r="BE45" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF45" s="30" t="inlineStr">
+      <c r="BF45" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG45" s="30" t="inlineStr">
+      <c r="BG45" s="31" t="inlineStr">
         <is>
           <t>qmc5883p</t>
         </is>
       </c>
-      <c r="BH45" s="30" t="inlineStr">
+      <c r="BH45" s="31" t="inlineStr">
         <is>
           <t>QMC5883P</t>
         </is>
       </c>
-      <c r="BI45" s="30" t="inlineStr">
+      <c r="BI45" s="31" t="inlineStr">
         <is>
           <t>0x2C</t>
         </is>
       </c>
-      <c r="BJ45" s="30" t="inlineStr">
+      <c r="BJ45" s="31" t="inlineStr">
         <is>
           <t>0x2C</t>
         </is>
       </c>
-      <c r="BK45" s="30" t="inlineStr"/>
-      <c r="BL45" s="30" t="inlineStr">
+      <c r="BK45" s="31" t="inlineStr">
+        <is>
+          <t>0x2C</t>
+        </is>
+      </c>
+      <c r="BL45" s="31" t="inlineStr"/>
+      <c r="BM45" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN45" s="31" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="G46" s="2" t="n">
@@ -15715,54 +15866,60 @@
           <t>BME680</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
+      <c r="P46" s="30" t="inlineStr">
         <is>
           <t>0x76</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>0x76, 0x77</t>
+          <t>0x77, 0x76</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr"/>
-      <c r="BD46" s="30" t="n">
+      <c r="BD46" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="BE46" s="30" t="n">
+      <c r="BE46" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF46" s="30" t="inlineStr">
+      <c r="BF46" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG46" s="30" t="inlineStr">
+      <c r="BG46" s="31" t="inlineStr">
         <is>
           <t>as5600</t>
         </is>
       </c>
-      <c r="BH46" s="30" t="inlineStr">
+      <c r="BH46" s="31" t="inlineStr">
         <is>
           <t>AS5600 Magnetic Angle</t>
         </is>
       </c>
-      <c r="BI46" s="30" t="inlineStr">
+      <c r="BI46" s="31" t="inlineStr">
         <is>
           <t>0x36</t>
         </is>
       </c>
-      <c r="BJ46" s="30" t="inlineStr">
+      <c r="BJ46" s="31" t="inlineStr">
         <is>
           <t>0x36</t>
         </is>
       </c>
-      <c r="BK46" s="30" t="inlineStr"/>
-      <c r="BL46" s="30" t="inlineStr">
+      <c r="BK46" s="31" t="inlineStr">
+        <is>
+          <t>0x36</t>
+        </is>
+      </c>
+      <c r="BL46" s="31" t="inlineStr"/>
+      <c r="BM46" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN46" s="31" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="G47" s="2" t="n">
@@ -15778,7 +15935,7 @@
           <t>TMP117</t>
         </is>
       </c>
-      <c r="J47" s="2" t="inlineStr">
+      <c r="J47" s="30" t="inlineStr">
         <is>
           <t>0x4B</t>
         </is>
@@ -15789,23 +15946,23 @@
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr"/>
-      <c r="BD47" s="30" t="n">
+      <c r="BD47" s="31" t="n">
         <v>21</v>
       </c>
-      <c r="BE47" s="30" t="n">
+      <c r="BE47" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF47" s="30" t="inlineStr">
+      <c r="BF47" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG47" s="30" t="inlineStr">
+      <c r="BG47" s="31" t="inlineStr">
         <is>
           <t>stemma_soil</t>
         </is>
       </c>
-      <c r="BH47" s="30" t="inlineStr">
+      <c r="BH47" s="31" t="inlineStr">
         <is>
           <t>STEMMA Soil Sensor</t>
         </is>
@@ -15815,15 +15972,25 @@
           <t>0x37</t>
         </is>
       </c>
-      <c r="BJ47" s="30" t="inlineStr">
+      <c r="BJ47" s="31" t="inlineStr">
+        <is>
+          <t>0x36</t>
+        </is>
+      </c>
+      <c r="BK47" s="31" t="inlineStr">
         <is>
           <t>0x36, 0x37, 0x38, 0x39</t>
         </is>
       </c>
-      <c r="BK47" s="30" t="inlineStr"/>
-      <c r="BL47" s="30" t="inlineStr">
+      <c r="BL47" s="31" t="inlineStr"/>
+      <c r="BM47" s="31" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="BN47" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
         </is>
       </c>
     </row>
@@ -15852,43 +16019,49 @@
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr"/>
-      <c r="BD48" s="30" t="n">
+      <c r="BD48" s="31" t="n">
         <v>22</v>
       </c>
-      <c r="BE48" s="30" t="n">
+      <c r="BE48" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF48" s="30" t="inlineStr">
+      <c r="BF48" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG48" s="30" t="inlineStr">
+      <c r="BG48" s="31" t="inlineStr">
         <is>
           <t>aht20</t>
         </is>
       </c>
-      <c r="BH48" s="30" t="inlineStr">
+      <c r="BH48" s="31" t="inlineStr">
         <is>
           <t>AHT20</t>
         </is>
       </c>
-      <c r="BI48" s="30" t="inlineStr">
+      <c r="BI48" s="31" t="inlineStr">
         <is>
           <t>0x38</t>
         </is>
       </c>
-      <c r="BJ48" s="30" t="inlineStr">
+      <c r="BJ48" s="31" t="inlineStr">
         <is>
           <t>0x38</t>
         </is>
       </c>
-      <c r="BK48" s="30" t="inlineStr"/>
-      <c r="BL48" s="30" t="inlineStr">
+      <c r="BK48" s="31" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="BL48" s="31" t="inlineStr"/>
+      <c r="BM48" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN48" s="31" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="G49" s="2" t="n">
@@ -15915,23 +16088,23 @@
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr"/>
-      <c r="BD49" s="30" t="n">
+      <c r="BD49" s="31" t="n">
         <v>23</v>
       </c>
-      <c r="BE49" s="30" t="n">
+      <c r="BE49" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF49" s="30" t="inlineStr">
+      <c r="BF49" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG49" s="30" t="inlineStr">
+      <c r="BG49" s="31" t="inlineStr">
         <is>
           <t>tsl2591</t>
         </is>
       </c>
-      <c r="BH49" s="30" t="inlineStr">
+      <c r="BH49" s="31" t="inlineStr">
         <is>
           <t>TSL2591</t>
         </is>
@@ -15941,15 +16114,25 @@
           <t>0x39</t>
         </is>
       </c>
-      <c r="BJ49" s="30" t="inlineStr">
+      <c r="BJ49" s="31" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="BK49" s="31" t="inlineStr">
         <is>
           <t>0x29, 0x39, 0x49</t>
         </is>
       </c>
-      <c r="BK49" s="30" t="inlineStr"/>
-      <c r="BL49" s="30" t="inlineStr">
+      <c r="BL49" s="31" t="inlineStr"/>
+      <c r="BM49" s="31" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="BN49" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
         </is>
       </c>
     </row>
@@ -15978,43 +16161,49 @@
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr"/>
-      <c r="BD50" s="30" t="n">
+      <c r="BD50" s="31" t="n">
         <v>24</v>
       </c>
-      <c r="BE50" s="30" t="n">
+      <c r="BE50" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF50" s="30" t="inlineStr">
+      <c r="BF50" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG50" s="30" t="inlineStr">
+      <c r="BG50" s="31" t="inlineStr">
         <is>
           <t>mlx90632b</t>
         </is>
       </c>
-      <c r="BH50" s="30" t="inlineStr">
+      <c r="BH50" s="31" t="inlineStr">
         <is>
           <t>MLX90632-B (Standard)</t>
         </is>
       </c>
-      <c r="BI50" s="30" t="inlineStr">
+      <c r="BI50" s="31" t="inlineStr">
         <is>
           <t>0x3A</t>
         </is>
       </c>
-      <c r="BJ50" s="30" t="inlineStr">
+      <c r="BJ50" s="31" t="inlineStr">
+        <is>
+          <t>0x3A</t>
+        </is>
+      </c>
+      <c r="BK50" s="31" t="inlineStr">
         <is>
           <t>0x3A, 0x3B</t>
         </is>
       </c>
-      <c r="BK50" s="30" t="inlineStr"/>
-      <c r="BL50" s="30" t="inlineStr">
+      <c r="BL50" s="31" t="inlineStr"/>
+      <c r="BM50" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN50" s="31" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="G51" s="2" t="n">
@@ -16022,42 +16211,42 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>lps22hb</t>
+          <t>lps25hb</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>LPS22HB</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
+          <t>LPS25HB</t>
+        </is>
+      </c>
+      <c r="J51" s="30" t="inlineStr">
         <is>
           <t>0x5C</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0x5C, 0x5D</t>
+          <t>0x5D, 0x5C</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr"/>
-      <c r="BD51" s="30" t="n">
+      <c r="BD51" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="BE51" s="30" t="n">
+      <c r="BE51" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF51" s="30" t="inlineStr">
+      <c r="BF51" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG51" s="30" t="inlineStr">
+      <c r="BG51" s="31" t="inlineStr">
         <is>
           <t>mlx90632d_ext</t>
         </is>
       </c>
-      <c r="BH51" s="30" t="inlineStr">
+      <c r="BH51" s="31" t="inlineStr">
         <is>
           <t>MLX90632 (Extended Mode)</t>
         </is>
@@ -16067,15 +16256,25 @@
           <t>0x3B</t>
         </is>
       </c>
-      <c r="BJ51" s="30" t="inlineStr">
+      <c r="BJ51" s="31" t="inlineStr">
+        <is>
+          <t>0x3A</t>
+        </is>
+      </c>
+      <c r="BK51" s="31" t="inlineStr">
         <is>
           <t>0x3A, 0x3B</t>
         </is>
       </c>
-      <c r="BK51" s="30" t="inlineStr"/>
-      <c r="BL51" s="30" t="inlineStr">
+      <c r="BL51" s="31" t="inlineStr"/>
+      <c r="BM51" s="31" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="BN51" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
         </is>
       </c>
     </row>
@@ -16085,12 +16284,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>lps25hb</t>
+          <t>lps22hb</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>LPS25HB</t>
+          <t>LPS22HB</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -16100,47 +16299,53 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0x5C, 0x5D</t>
+          <t>0x5D, 0x5C</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr"/>
-      <c r="BD52" s="30" t="n">
+      <c r="BD52" s="31" t="n">
         <v>26</v>
       </c>
-      <c r="BE52" s="30" t="n">
+      <c r="BE52" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF52" s="30" t="inlineStr">
+      <c r="BF52" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG52" s="30" t="inlineStr">
+      <c r="BG52" s="31" t="inlineStr">
         <is>
           <t>htu21d</t>
         </is>
       </c>
-      <c r="BH52" s="30" t="inlineStr">
+      <c r="BH52" s="31" t="inlineStr">
         <is>
           <t>HTU21D</t>
         </is>
       </c>
-      <c r="BI52" s="30" t="inlineStr">
+      <c r="BI52" s="31" t="inlineStr">
         <is>
           <t>0x40</t>
         </is>
       </c>
-      <c r="BJ52" s="30" t="inlineStr">
+      <c r="BJ52" s="31" t="inlineStr">
         <is>
           <t>0x40</t>
         </is>
       </c>
-      <c r="BK52" s="30" t="inlineStr"/>
-      <c r="BL52" s="30" t="inlineStr">
+      <c r="BK52" s="31" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="BL52" s="31" t="inlineStr"/>
+      <c r="BM52" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN52" s="31" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="G53" s="2" t="n">
@@ -16167,23 +16372,23 @@
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr"/>
-      <c r="BD53" s="30" t="n">
+      <c r="BD53" s="31" t="n">
         <v>27</v>
       </c>
-      <c r="BE53" s="30" t="n">
+      <c r="BE53" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF53" s="30" t="inlineStr">
+      <c r="BF53" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG53" s="30" t="inlineStr">
+      <c r="BG53" s="31" t="inlineStr">
         <is>
           <t>htu31d</t>
         </is>
       </c>
-      <c r="BH53" s="30" t="inlineStr">
+      <c r="BH53" s="31" t="inlineStr">
         <is>
           <t>HTU31D</t>
         </is>
@@ -16193,15 +16398,25 @@
           <t>0x41</t>
         </is>
       </c>
-      <c r="BJ53" s="30" t="inlineStr">
+      <c r="BJ53" s="31" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="BK53" s="31" t="inlineStr">
         <is>
           <t>0x40, 0x41</t>
         </is>
       </c>
-      <c r="BK53" s="30" t="inlineStr"/>
-      <c r="BL53" s="30" t="inlineStr">
+      <c r="BL53" s="31" t="inlineStr"/>
+      <c r="BM53" s="31" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="BN53" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
         </is>
       </c>
     </row>
@@ -16230,43 +16445,49 @@
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr"/>
-      <c r="BD54" s="30" t="n">
+      <c r="BD54" s="31" t="n">
         <v>28</v>
       </c>
-      <c r="BE54" s="30" t="n">
+      <c r="BE54" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF54" s="30" t="inlineStr">
+      <c r="BF54" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG54" s="30" t="inlineStr">
+      <c r="BG54" s="31" t="inlineStr">
         <is>
           <t>sht30_mesh</t>
         </is>
       </c>
-      <c r="BH54" s="30" t="inlineStr">
+      <c r="BH54" s="31" t="inlineStr">
         <is>
           <t>Weatherproof SHT30</t>
         </is>
       </c>
-      <c r="BI54" s="30" t="inlineStr">
+      <c r="BI54" s="31" t="inlineStr">
         <is>
           <t>0x44</t>
         </is>
       </c>
-      <c r="BJ54" s="30" t="inlineStr">
+      <c r="BJ54" s="31" t="inlineStr">
         <is>
           <t>0x44</t>
         </is>
       </c>
-      <c r="BK54" s="30" t="inlineStr"/>
-      <c r="BL54" s="30" t="inlineStr">
+      <c r="BK54" s="31" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="BL54" s="31" t="inlineStr"/>
+      <c r="BM54" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN54" s="31" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="G55" s="2" t="n">
@@ -16293,23 +16514,23 @@
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr"/>
-      <c r="BD55" s="30" t="n">
+      <c r="BD55" s="31" t="n">
         <v>29</v>
       </c>
-      <c r="BE55" s="30" t="n">
+      <c r="BE55" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF55" s="30" t="inlineStr">
+      <c r="BF55" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG55" s="30" t="inlineStr">
+      <c r="BG55" s="31" t="inlineStr">
         <is>
           <t>sht3x</t>
         </is>
       </c>
-      <c r="BH55" s="30" t="inlineStr">
+      <c r="BH55" s="31" t="inlineStr">
         <is>
           <t>SHT3X</t>
         </is>
@@ -16319,15 +16540,25 @@
           <t>0x45</t>
         </is>
       </c>
-      <c r="BJ55" s="30" t="inlineStr">
+      <c r="BJ55" s="31" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="BK55" s="31" t="inlineStr">
         <is>
           <t>0x44, 0x45</t>
         </is>
       </c>
-      <c r="BK55" s="30" t="inlineStr"/>
-      <c r="BL55" s="30" t="inlineStr">
+      <c r="BL55" s="31" t="inlineStr"/>
+      <c r="BM55" s="31" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="BN55" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
         </is>
       </c>
     </row>
@@ -16356,25 +16587,25 @@
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr"/>
-      <c r="BD56" s="30" t="n">
+      <c r="BD56" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="BE56" s="30" t="n">
+      <c r="BE56" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF56" s="30" t="inlineStr">
+      <c r="BF56" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG56" s="30" t="inlineStr">
-        <is>
-          <t>bmp580</t>
-        </is>
-      </c>
-      <c r="BH56" s="30" t="inlineStr">
-        <is>
-          <t>BMP580</t>
+      <c r="BG56" s="31" t="inlineStr">
+        <is>
+          <t>bmp581</t>
+        </is>
+      </c>
+      <c r="BH56" s="31" t="inlineStr">
+        <is>
+          <t>BMP581</t>
         </is>
       </c>
       <c r="BI56" s="30" t="inlineStr">
@@ -16382,15 +16613,25 @@
           <t>0x46</t>
         </is>
       </c>
-      <c r="BJ56" s="30" t="inlineStr">
-        <is>
-          <t>0x46, 0x47</t>
-        </is>
-      </c>
-      <c r="BK56" s="30" t="inlineStr"/>
-      <c r="BL56" s="30" t="inlineStr">
+      <c r="BJ56" s="31" t="inlineStr">
+        <is>
+          <t>0x47</t>
+        </is>
+      </c>
+      <c r="BK56" s="31" t="inlineStr">
+        <is>
+          <t>0x47, 0x46</t>
+        </is>
+      </c>
+      <c r="BL56" s="31" t="inlineStr"/>
+      <c r="BM56" s="31" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="BN56" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
         </is>
       </c>
     </row>
@@ -16419,43 +16660,49 @@
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr"/>
-      <c r="BD57" s="30" t="n">
+      <c r="BD57" s="31" t="n">
         <v>31</v>
       </c>
-      <c r="BE57" s="30" t="n">
+      <c r="BE57" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF57" s="30" t="inlineStr">
+      <c r="BF57" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG57" s="30" t="inlineStr">
-        <is>
-          <t>bmp581</t>
-        </is>
-      </c>
-      <c r="BH57" s="30" t="inlineStr">
-        <is>
-          <t>BMP581</t>
-        </is>
-      </c>
-      <c r="BI57" s="30" t="inlineStr">
+      <c r="BG57" s="31" t="inlineStr">
+        <is>
+          <t>bmp580</t>
+        </is>
+      </c>
+      <c r="BH57" s="31" t="inlineStr">
+        <is>
+          <t>BMP580</t>
+        </is>
+      </c>
+      <c r="BI57" s="31" t="inlineStr">
         <is>
           <t>0x47</t>
         </is>
       </c>
-      <c r="BJ57" s="30" t="inlineStr">
-        <is>
-          <t>0x46, 0x47</t>
-        </is>
-      </c>
-      <c r="BK57" s="30" t="inlineStr"/>
-      <c r="BL57" s="30" t="inlineStr">
+      <c r="BJ57" s="31" t="inlineStr">
+        <is>
+          <t>0x47</t>
+        </is>
+      </c>
+      <c r="BK57" s="31" t="inlineStr">
+        <is>
+          <t>0x47, 0x46</t>
+        </is>
+      </c>
+      <c r="BL57" s="31" t="inlineStr"/>
+      <c r="BM57" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN57" s="31" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="G58" s="2" t="n">
@@ -16482,43 +16729,49 @@
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr"/>
-      <c r="BD58" s="30" t="n">
+      <c r="BD58" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="BE58" s="30" t="n">
+      <c r="BE58" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF58" s="30" t="inlineStr">
+      <c r="BF58" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG58" s="30" t="inlineStr">
+      <c r="BG58" s="31" t="inlineStr">
         <is>
           <t>tc74a0</t>
         </is>
       </c>
-      <c r="BH58" s="30" t="inlineStr">
+      <c r="BH58" s="31" t="inlineStr">
         <is>
           <t>TC74A0</t>
         </is>
       </c>
-      <c r="BI58" s="30" t="inlineStr">
+      <c r="BI58" s="31" t="inlineStr">
         <is>
           <t>0x48</t>
         </is>
       </c>
-      <c r="BJ58" s="30" t="inlineStr">
+      <c r="BJ58" s="31" t="inlineStr">
         <is>
           <t>0x48</t>
         </is>
       </c>
-      <c r="BK58" s="30" t="inlineStr"/>
-      <c r="BL58" s="30" t="inlineStr">
+      <c r="BK58" s="31" t="inlineStr">
+        <is>
+          <t>0x48</t>
+        </is>
+      </c>
+      <c r="BL58" s="31" t="inlineStr"/>
+      <c r="BM58" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN58" s="31" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="G59" s="2" t="n">
@@ -16534,34 +16787,34 @@
           <t>BME280</t>
         </is>
       </c>
-      <c r="J59" s="2" t="inlineStr">
+      <c r="J59" s="30" t="inlineStr">
         <is>
           <t>0x76</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0x76, 0x77</t>
+          <t>0x77, 0x76</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr"/>
-      <c r="BD59" s="30" t="n">
+      <c r="BD59" s="31" t="n">
         <v>33</v>
       </c>
-      <c r="BE59" s="30" t="n">
+      <c r="BE59" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF59" s="30" t="inlineStr">
+      <c r="BF59" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG59" s="30" t="inlineStr">
+      <c r="BG59" s="31" t="inlineStr">
         <is>
           <t>adt7410</t>
         </is>
       </c>
-      <c r="BH59" s="30" t="inlineStr">
+      <c r="BH59" s="31" t="inlineStr">
         <is>
           <t>ADT7410</t>
         </is>
@@ -16571,75 +16824,91 @@
           <t>0x49</t>
         </is>
       </c>
-      <c r="BJ59" s="30" t="inlineStr">
+      <c r="BJ59" s="31" t="inlineStr">
+        <is>
+          <t>0x48</t>
+        </is>
+      </c>
+      <c r="BK59" s="31" t="inlineStr">
         <is>
           <t>0x48, 0x49, 0x4A, 0x4B</t>
         </is>
       </c>
-      <c r="BK59" s="30" t="inlineStr"/>
-      <c r="BL59" s="30" t="inlineStr">
+      <c r="BL59" s="31" t="inlineStr"/>
+      <c r="BM59" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN59" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="BD60" s="30" t="n">
+      <c r="BD60" s="31" t="n">
         <v>34</v>
       </c>
-      <c r="BE60" s="30" t="n">
+      <c r="BE60" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF60" s="30" t="inlineStr">
+      <c r="BF60" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG60" s="30" t="inlineStr">
+      <c r="BG60" s="31" t="inlineStr">
         <is>
           <t>max44009</t>
         </is>
       </c>
-      <c r="BH60" s="30" t="inlineStr">
+      <c r="BH60" s="31" t="inlineStr">
         <is>
           <t>MAX44009</t>
         </is>
       </c>
-      <c r="BI60" s="30" t="inlineStr">
+      <c r="BI60" s="31" t="inlineStr">
         <is>
           <t>0x4A</t>
         </is>
       </c>
-      <c r="BJ60" s="30" t="inlineStr">
+      <c r="BJ60" s="31" t="inlineStr">
+        <is>
+          <t>0x4A</t>
+        </is>
+      </c>
+      <c r="BK60" s="31" t="inlineStr">
         <is>
           <t>0x4A, 0x4B</t>
         </is>
       </c>
-      <c r="BK60" s="30" t="inlineStr"/>
-      <c r="BL60" s="30" t="inlineStr">
+      <c r="BL60" s="31" t="inlineStr"/>
+      <c r="BM60" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN60" s="31" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="BD61" s="30" t="n">
+      <c r="BD61" s="31" t="n">
         <v>35</v>
       </c>
-      <c r="BE61" s="30" t="n">
+      <c r="BE61" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF61" s="30" t="inlineStr">
+      <c r="BF61" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG61" s="30" t="inlineStr">
+      <c r="BG61" s="31" t="inlineStr">
         <is>
           <t>tmp117</t>
         </is>
       </c>
-      <c r="BH61" s="30" t="inlineStr">
+      <c r="BH61" s="31" t="inlineStr">
         <is>
           <t>TMP117</t>
         </is>
@@ -16649,2238 +16918,2654 @@
           <t>0x4B</t>
         </is>
       </c>
-      <c r="BJ61" s="30" t="inlineStr">
+      <c r="BJ61" s="31" t="inlineStr">
+        <is>
+          <t>0x48</t>
+        </is>
+      </c>
+      <c r="BK61" s="31" t="inlineStr">
         <is>
           <t>0x48, 0x49, 0x4A, 0x4B</t>
         </is>
       </c>
-      <c r="BK61" s="30" t="inlineStr"/>
-      <c r="BL61" s="30" t="inlineStr">
+      <c r="BL61" s="31" t="inlineStr"/>
+      <c r="BM61" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN61" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="BD62" s="30" t="n">
+      <c r="BD62" s="31" t="n">
         <v>36</v>
       </c>
-      <c r="BE62" s="30" t="n">
+      <c r="BE62" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF62" s="30" t="inlineStr">
+      <c r="BF62" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG62" s="30" t="inlineStr">
+      <c r="BG62" s="31" t="inlineStr">
         <is>
           <t>apds9999</t>
         </is>
       </c>
-      <c r="BH62" s="30" t="inlineStr">
+      <c r="BH62" s="31" t="inlineStr">
         <is>
           <t>APDS9999</t>
         </is>
       </c>
-      <c r="BI62" s="30" t="inlineStr">
+      <c r="BI62" s="31" t="inlineStr">
         <is>
           <t>0x52</t>
         </is>
       </c>
-      <c r="BJ62" s="30" t="inlineStr">
+      <c r="BJ62" s="31" t="inlineStr">
         <is>
           <t>0x52</t>
         </is>
       </c>
-      <c r="BK62" s="30" t="inlineStr"/>
-      <c r="BL62" s="30" t="inlineStr">
+      <c r="BK62" s="31" t="inlineStr">
+        <is>
+          <t>0x52</t>
+        </is>
+      </c>
+      <c r="BL62" s="31" t="inlineStr"/>
+      <c r="BM62" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN62" s="31" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="BD63" s="30" t="n">
+      <c r="BD63" s="31" t="n">
         <v>37</v>
       </c>
-      <c r="BE63" s="30" t="n">
+      <c r="BE63" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF63" s="30" t="inlineStr">
+      <c r="BF63" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG63" s="30" t="inlineStr">
+      <c r="BG63" s="31" t="inlineStr">
         <is>
           <t>ltr390</t>
         </is>
       </c>
-      <c r="BH63" s="30" t="inlineStr">
+      <c r="BH63" s="31" t="inlineStr">
         <is>
           <t>LTR-390</t>
         </is>
       </c>
-      <c r="BI63" s="30" t="inlineStr">
+      <c r="BI63" s="31" t="inlineStr">
         <is>
           <t>0x53</t>
         </is>
       </c>
-      <c r="BJ63" s="30" t="inlineStr">
+      <c r="BJ63" s="31" t="inlineStr">
         <is>
           <t>0x53</t>
         </is>
       </c>
-      <c r="BK63" s="30" t="inlineStr"/>
-      <c r="BL63" s="30" t="inlineStr">
+      <c r="BK63" s="31" t="inlineStr">
+        <is>
+          <t>0x53</t>
+        </is>
+      </c>
+      <c r="BL63" s="31" t="inlineStr"/>
+      <c r="BM63" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN63" s="31" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="BD64" s="30" t="n">
+      <c r="BD64" s="31" t="n">
         <v>38</v>
       </c>
-      <c r="BE64" s="30" t="n">
+      <c r="BE64" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF64" s="30" t="inlineStr">
+      <c r="BF64" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG64" s="30" t="inlineStr">
+      <c r="BG64" s="31" t="inlineStr">
         <is>
           <t>sgp40</t>
         </is>
       </c>
-      <c r="BH64" s="30" t="inlineStr">
+      <c r="BH64" s="31" t="inlineStr">
         <is>
           <t>SGP40</t>
         </is>
       </c>
-      <c r="BI64" s="30" t="inlineStr">
+      <c r="BI64" s="31" t="inlineStr">
         <is>
           <t>0x59</t>
         </is>
       </c>
-      <c r="BJ64" s="30" t="inlineStr">
+      <c r="BJ64" s="31" t="inlineStr">
         <is>
           <t>0x59</t>
         </is>
       </c>
-      <c r="BK64" s="30" t="inlineStr"/>
-      <c r="BL64" s="30" t="inlineStr">
+      <c r="BK64" s="31" t="inlineStr">
+        <is>
+          <t>0x59</t>
+        </is>
+      </c>
+      <c r="BL64" s="31" t="inlineStr"/>
+      <c r="BM64" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="BN64" s="31" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="BD65" s="30" t="n">
+      <c r="BD65" s="31" t="n">
         <v>39</v>
       </c>
-      <c r="BE65" s="30" t="n">
+      <c r="BE65" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="BF65" s="30" t="inlineStr">
+      <c r="BF65" s="31" t="inlineStr">
         <is>
           <t>8ch_mux_ch0</t>
         </is>
       </c>
-      <c r="BG65" s="30" t="inlineStr">
+      <c r="BG65" s="31" t="inlineStr">
+        <is>
+          <t>lps25hb</t>
+        </is>
+      </c>
+      <c r="BH65" s="31" t="inlineStr">
+        <is>
+          <t>LPS25HB</t>
+        </is>
+      </c>
+      <c r="BI65" s="30" t="inlineStr">
+        <is>
+          <t>0x5C</t>
+        </is>
+      </c>
+      <c r="BJ65" s="31" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+      <c r="BK65" s="31" t="inlineStr">
+        <is>
+          <t>0x5D, 0x5C</t>
+        </is>
+      </c>
+      <c r="BL65" s="31" t="inlineStr"/>
+      <c r="BM65" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN65" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="BD66" s="31" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE66" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF66" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch0</t>
+        </is>
+      </c>
+      <c r="BG66" s="31" t="inlineStr">
         <is>
           <t>lps22hb</t>
         </is>
       </c>
-      <c r="BH65" s="30" t="inlineStr">
+      <c r="BH66" s="31" t="inlineStr">
         <is>
           <t>LPS22HB</t>
         </is>
       </c>
-      <c r="BI65" s="30" t="inlineStr">
+      <c r="BI66" s="31" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+      <c r="BJ66" s="31" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+      <c r="BK66" s="31" t="inlineStr">
+        <is>
+          <t>0x5D, 0x5C</t>
+        </is>
+      </c>
+      <c r="BL66" s="31" t="inlineStr"/>
+      <c r="BM66" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN66" s="31" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="BD67" s="31" t="n">
+        <v>41</v>
+      </c>
+      <c r="BE67" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF67" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch0</t>
+        </is>
+      </c>
+      <c r="BG67" s="31" t="inlineStr">
+        <is>
+          <t>mpl115a2</t>
+        </is>
+      </c>
+      <c r="BH67" s="31" t="inlineStr">
+        <is>
+          <t>MPL115A2</t>
+        </is>
+      </c>
+      <c r="BI67" s="31" t="inlineStr">
+        <is>
+          <t>0x60</t>
+        </is>
+      </c>
+      <c r="BJ67" s="31" t="inlineStr">
+        <is>
+          <t>0x60</t>
+        </is>
+      </c>
+      <c r="BK67" s="31" t="inlineStr">
+        <is>
+          <t>0x60</t>
+        </is>
+      </c>
+      <c r="BL67" s="31" t="inlineStr"/>
+      <c r="BM67" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN67" s="31" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="BD68" s="31" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE68" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF68" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch0</t>
+        </is>
+      </c>
+      <c r="BG68" s="31" t="inlineStr">
+        <is>
+          <t>scd30</t>
+        </is>
+      </c>
+      <c r="BH68" s="31" t="inlineStr">
+        <is>
+          <t>SCD30</t>
+        </is>
+      </c>
+      <c r="BI68" s="31" t="inlineStr">
+        <is>
+          <t>0x61</t>
+        </is>
+      </c>
+      <c r="BJ68" s="31" t="inlineStr">
+        <is>
+          <t>0x61</t>
+        </is>
+      </c>
+      <c r="BK68" s="31" t="inlineStr">
+        <is>
+          <t>0x61</t>
+        </is>
+      </c>
+      <c r="BL68" s="31" t="inlineStr"/>
+      <c r="BM68" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN68" s="31" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="BD69" s="31" t="n">
+        <v>43</v>
+      </c>
+      <c r="BE69" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF69" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch0</t>
+        </is>
+      </c>
+      <c r="BG69" s="31" t="inlineStr">
+        <is>
+          <t>scd40</t>
+        </is>
+      </c>
+      <c r="BH69" s="31" t="inlineStr">
+        <is>
+          <t>SCD40/SCD41</t>
+        </is>
+      </c>
+      <c r="BI69" s="31" t="inlineStr">
+        <is>
+          <t>0x62</t>
+        </is>
+      </c>
+      <c r="BJ69" s="31" t="inlineStr">
+        <is>
+          <t>0x62</t>
+        </is>
+      </c>
+      <c r="BK69" s="31" t="inlineStr">
+        <is>
+          <t>0x62</t>
+        </is>
+      </c>
+      <c r="BL69" s="31" t="inlineStr"/>
+      <c r="BM69" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN69" s="31" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="BD70" s="31" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE70" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF70" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch0</t>
+        </is>
+      </c>
+      <c r="BG70" s="31" t="inlineStr">
+        <is>
+          <t>sen50</t>
+        </is>
+      </c>
+      <c r="BH70" s="31" t="inlineStr">
+        <is>
+          <t>SEN50</t>
+        </is>
+      </c>
+      <c r="BI70" s="31" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="BJ70" s="31" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="BK70" s="31" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="BL70" s="31" t="inlineStr"/>
+      <c r="BM70" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN70" s="31" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="BD71" s="31" t="n">
+        <v>45</v>
+      </c>
+      <c r="BE71" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF71" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch0</t>
+        </is>
+      </c>
+      <c r="BG71" s="31" t="inlineStr">
+        <is>
+          <t>shtc3</t>
+        </is>
+      </c>
+      <c r="BH71" s="31" t="inlineStr">
+        <is>
+          <t>SHTC3</t>
+        </is>
+      </c>
+      <c r="BI71" s="31" t="inlineStr">
+        <is>
+          <t>0x70</t>
+        </is>
+      </c>
+      <c r="BJ71" s="31" t="inlineStr">
+        <is>
+          <t>0x70</t>
+        </is>
+      </c>
+      <c r="BK71" s="31" t="inlineStr">
+        <is>
+          <t>0x70</t>
+        </is>
+      </c>
+      <c r="BL71" s="31" t="inlineStr"/>
+      <c r="BM71" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN71" s="31" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="BD72" s="31" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE72" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF72" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch0</t>
+        </is>
+      </c>
+      <c r="BG72" s="31" t="inlineStr">
+        <is>
+          <t>as7331</t>
+        </is>
+      </c>
+      <c r="BH72" s="31" t="inlineStr">
+        <is>
+          <t>AS7331</t>
+        </is>
+      </c>
+      <c r="BI72" s="31" t="inlineStr">
+        <is>
+          <t>0x74</t>
+        </is>
+      </c>
+      <c r="BJ72" s="31" t="inlineStr">
+        <is>
+          <t>0x74</t>
+        </is>
+      </c>
+      <c r="BK72" s="31" t="inlineStr">
+        <is>
+          <t>0x74, 0x75, 0x76, 0x77</t>
+        </is>
+      </c>
+      <c r="BL72" s="31" t="inlineStr"/>
+      <c r="BM72" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN72" s="31" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="BD73" s="31" t="n">
+        <v>47</v>
+      </c>
+      <c r="BE73" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF73" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch0</t>
+        </is>
+      </c>
+      <c r="BG73" s="31" t="inlineStr">
+        <is>
+          <t>bme280</t>
+        </is>
+      </c>
+      <c r="BH73" s="31" t="inlineStr">
+        <is>
+          <t>BME280</t>
+        </is>
+      </c>
+      <c r="BI73" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="BJ73" s="31" t="inlineStr">
+        <is>
+          <t>0x77</t>
+        </is>
+      </c>
+      <c r="BK73" s="31" t="inlineStr">
+        <is>
+          <t>0x77, 0x76</t>
+        </is>
+      </c>
+      <c r="BL73" s="31" t="inlineStr"/>
+      <c r="BM73" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN73" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="BD74" s="32" t="n">
+        <v>48</v>
+      </c>
+      <c r="BE74" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF74" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG74" s="32" t="inlineStr">
+        <is>
+          <t>mprls</t>
+        </is>
+      </c>
+      <c r="BH74" s="32" t="inlineStr">
+        <is>
+          <t>MPRLS</t>
+        </is>
+      </c>
+      <c r="BI74" s="32" t="inlineStr">
+        <is>
+          <t>0x18</t>
+        </is>
+      </c>
+      <c r="BJ74" s="32" t="inlineStr">
+        <is>
+          <t>0x18</t>
+        </is>
+      </c>
+      <c r="BK74" s="32" t="inlineStr">
+        <is>
+          <t>0x18</t>
+        </is>
+      </c>
+      <c r="BL74" s="32" t="inlineStr"/>
+      <c r="BM74" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN74" s="32" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="BD75" s="32" t="n">
+        <v>49</v>
+      </c>
+      <c r="BE75" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF75" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG75" s="32" t="inlineStr">
+        <is>
+          <t>ltr329</t>
+        </is>
+      </c>
+      <c r="BH75" s="32" t="inlineStr">
+        <is>
+          <t>LTR-329</t>
+        </is>
+      </c>
+      <c r="BI75" s="32" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="BJ75" s="32" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="BK75" s="32" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="BL75" s="32" t="inlineStr"/>
+      <c r="BM75" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN75" s="32" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="BD76" s="32" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE76" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF76" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG76" s="32" t="inlineStr">
+        <is>
+          <t>max17048</t>
+        </is>
+      </c>
+      <c r="BH76" s="32" t="inlineStr">
+        <is>
+          <t>MAX17048/MAX17049</t>
+        </is>
+      </c>
+      <c r="BI76" s="32" t="inlineStr">
+        <is>
+          <t>0x36</t>
+        </is>
+      </c>
+      <c r="BJ76" s="32" t="inlineStr">
+        <is>
+          <t>0x36</t>
+        </is>
+      </c>
+      <c r="BK76" s="32" t="inlineStr">
+        <is>
+          <t>0x36</t>
+        </is>
+      </c>
+      <c r="BL76" s="32" t="inlineStr"/>
+      <c r="BM76" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN76" s="32" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="BD77" s="32" t="n">
+        <v>51</v>
+      </c>
+      <c r="BE77" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF77" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG77" s="32" t="inlineStr">
+        <is>
+          <t>aht21</t>
+        </is>
+      </c>
+      <c r="BH77" s="32" t="inlineStr">
+        <is>
+          <t>AHT21</t>
+        </is>
+      </c>
+      <c r="BI77" s="32" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="BJ77" s="32" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="BK77" s="32" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="BL77" s="32" t="inlineStr"/>
+      <c r="BM77" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN77" s="32" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="BD78" s="32" t="n">
+        <v>52</v>
+      </c>
+      <c r="BE78" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF78" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG78" s="32" t="inlineStr">
+        <is>
+          <t>mlx90632d_med</t>
+        </is>
+      </c>
+      <c r="BH78" s="32" t="inlineStr">
+        <is>
+          <t>MLX90632</t>
+        </is>
+      </c>
+      <c r="BI78" s="32" t="inlineStr">
+        <is>
+          <t>0x3A</t>
+        </is>
+      </c>
+      <c r="BJ78" s="32" t="inlineStr">
+        <is>
+          <t>0x3A</t>
+        </is>
+      </c>
+      <c r="BK78" s="32" t="inlineStr">
+        <is>
+          <t>0x3A, 0x3B</t>
+        </is>
+      </c>
+      <c r="BL78" s="32" t="inlineStr"/>
+      <c r="BM78" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN78" s="32" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="BD79" s="32" t="n">
+        <v>53</v>
+      </c>
+      <c r="BE79" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF79" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG79" s="32" t="inlineStr">
+        <is>
+          <t>sht20</t>
+        </is>
+      </c>
+      <c r="BH79" s="32" t="inlineStr">
+        <is>
+          <t>SHT20</t>
+        </is>
+      </c>
+      <c r="BI79" s="32" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="BJ79" s="32" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="BK79" s="32" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="BL79" s="32" t="inlineStr"/>
+      <c r="BM79" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN79" s="32" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="BD80" s="32" t="n">
+        <v>54</v>
+      </c>
+      <c r="BE80" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF80" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG80" s="32" t="inlineStr">
+        <is>
+          <t>ina219</t>
+        </is>
+      </c>
+      <c r="BH80" s="32" t="inlineStr">
+        <is>
+          <t>INA219</t>
+        </is>
+      </c>
+      <c r="BI80" s="30" t="inlineStr">
+        <is>
+          <t>0x41</t>
+        </is>
+      </c>
+      <c r="BJ80" s="32" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="BK80" s="32" t="inlineStr">
+        <is>
+          <t>0x40, 0x41, 0x44, 0x45</t>
+        </is>
+      </c>
+      <c r="BL80" s="32" t="inlineStr"/>
+      <c r="BM80" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN80" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="BD81" s="32" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE81" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF81" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG81" s="32" t="inlineStr">
+        <is>
+          <t>sht30_shell</t>
+        </is>
+      </c>
+      <c r="BH81" s="32" t="inlineStr">
+        <is>
+          <t>Enclosed SHT30</t>
+        </is>
+      </c>
+      <c r="BI81" s="32" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="BJ81" s="32" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="BK81" s="32" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="BL81" s="32" t="inlineStr"/>
+      <c r="BM81" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN81" s="32" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="BD82" s="32" t="n">
+        <v>56</v>
+      </c>
+      <c r="BE82" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF82" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG82" s="32" t="inlineStr">
+        <is>
+          <t>hdc302x</t>
+        </is>
+      </c>
+      <c r="BH82" s="32" t="inlineStr">
+        <is>
+          <t>HDC302x</t>
+        </is>
+      </c>
+      <c r="BI82" s="30" t="inlineStr">
+        <is>
+          <t>0x45</t>
+        </is>
+      </c>
+      <c r="BJ82" s="32" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="BK82" s="32" t="inlineStr">
+        <is>
+          <t>0x44, 0x45, 0x46, 0x47</t>
+        </is>
+      </c>
+      <c r="BL82" s="32" t="inlineStr"/>
+      <c r="BM82" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN82" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="BD83" s="32" t="n">
+        <v>57</v>
+      </c>
+      <c r="BE83" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF83" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG83" s="32" t="inlineStr">
+        <is>
+          <t>bmp585</t>
+        </is>
+      </c>
+      <c r="BH83" s="32" t="inlineStr">
+        <is>
+          <t>BMP585</t>
+        </is>
+      </c>
+      <c r="BI83" s="32" t="inlineStr">
+        <is>
+          <t>0x47</t>
+        </is>
+      </c>
+      <c r="BJ83" s="32" t="inlineStr">
+        <is>
+          <t>0x47</t>
+        </is>
+      </c>
+      <c r="BK83" s="32" t="inlineStr">
+        <is>
+          <t>0x47, 0x46</t>
+        </is>
+      </c>
+      <c r="BL83" s="32" t="inlineStr"/>
+      <c r="BM83" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN83" s="32" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="BD84" s="32" t="n">
+        <v>58</v>
+      </c>
+      <c r="BE84" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF84" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG84" s="32" t="inlineStr">
+        <is>
+          <t>tmp119</t>
+        </is>
+      </c>
+      <c r="BH84" s="32" t="inlineStr">
+        <is>
+          <t>TMP119</t>
+        </is>
+      </c>
+      <c r="BI84" s="32" t="inlineStr">
+        <is>
+          <t>0x48</t>
+        </is>
+      </c>
+      <c r="BJ84" s="32" t="inlineStr">
+        <is>
+          <t>0x48</t>
+        </is>
+      </c>
+      <c r="BK84" s="32" t="inlineStr">
+        <is>
+          <t>0x48, 0x49, 0x4A, 0x4B</t>
+        </is>
+      </c>
+      <c r="BL84" s="32" t="inlineStr"/>
+      <c r="BM84" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN84" s="32" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="BD85" s="32" t="n">
+        <v>59</v>
+      </c>
+      <c r="BE85" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF85" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG85" s="32" t="inlineStr">
+        <is>
+          <t>ens160</t>
+        </is>
+      </c>
+      <c r="BH85" s="32" t="inlineStr">
+        <is>
+          <t>ENS160</t>
+        </is>
+      </c>
+      <c r="BI85" s="32" t="inlineStr">
+        <is>
+          <t>0x52</t>
+        </is>
+      </c>
+      <c r="BJ85" s="32" t="inlineStr">
+        <is>
+          <t>0x52</t>
+        </is>
+      </c>
+      <c r="BK85" s="32" t="inlineStr">
+        <is>
+          <t>0x52, 0x53</t>
+        </is>
+      </c>
+      <c r="BL85" s="32" t="inlineStr"/>
+      <c r="BM85" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN85" s="32" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="BD86" s="32" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE86" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF86" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG86" s="32" t="inlineStr">
+        <is>
+          <t>ens161</t>
+        </is>
+      </c>
+      <c r="BH86" s="32" t="inlineStr">
+        <is>
+          <t>ENS161</t>
+        </is>
+      </c>
+      <c r="BI86" s="30" t="inlineStr">
+        <is>
+          <t>0x53</t>
+        </is>
+      </c>
+      <c r="BJ86" s="32" t="inlineStr">
+        <is>
+          <t>0x52</t>
+        </is>
+      </c>
+      <c r="BK86" s="32" t="inlineStr">
+        <is>
+          <t>0x52, 0x53</t>
+        </is>
+      </c>
+      <c r="BL86" s="32" t="inlineStr"/>
+      <c r="BM86" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN86" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="BD87" s="32" t="n">
+        <v>61</v>
+      </c>
+      <c r="BE87" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF87" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG87" s="32" t="inlineStr">
+        <is>
+          <t>sgp41</t>
+        </is>
+      </c>
+      <c r="BH87" s="32" t="inlineStr">
+        <is>
+          <t>SGP41</t>
+        </is>
+      </c>
+      <c r="BI87" s="32" t="inlineStr">
+        <is>
+          <t>0x59</t>
+        </is>
+      </c>
+      <c r="BJ87" s="32" t="inlineStr">
+        <is>
+          <t>0x59</t>
+        </is>
+      </c>
+      <c r="BK87" s="32" t="inlineStr">
+        <is>
+          <t>0x59</t>
+        </is>
+      </c>
+      <c r="BL87" s="32" t="inlineStr"/>
+      <c r="BM87" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN87" s="32" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="BD88" s="32" t="n">
+        <v>62</v>
+      </c>
+      <c r="BE88" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF88" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG88" s="32" t="inlineStr">
+        <is>
+          <t>lps28dfw</t>
+        </is>
+      </c>
+      <c r="BH88" s="32" t="inlineStr">
+        <is>
+          <t>LPS28DFW</t>
+        </is>
+      </c>
+      <c r="BI88" s="32" t="inlineStr">
         <is>
           <t>0x5C</t>
         </is>
       </c>
-      <c r="BJ65" s="30" t="inlineStr">
+      <c r="BJ88" s="32" t="inlineStr">
+        <is>
+          <t>0x5C</t>
+        </is>
+      </c>
+      <c r="BK88" s="32" t="inlineStr">
         <is>
           <t>0x5C, 0x5D</t>
         </is>
       </c>
-      <c r="BK65" s="30" t="inlineStr"/>
-      <c r="BL65" s="30" t="inlineStr">
+      <c r="BL88" s="32" t="inlineStr"/>
+      <c r="BM88" s="32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="66">
-      <c r="BD66" s="30" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE66" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF66" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch0</t>
-        </is>
-      </c>
-      <c r="BG66" s="30" t="inlineStr">
-        <is>
-          <t>lps25hb</t>
-        </is>
-      </c>
-      <c r="BH66" s="30" t="inlineStr">
-        <is>
-          <t>LPS25HB</t>
-        </is>
-      </c>
-      <c r="BI66" s="30" t="inlineStr">
+      <c r="BN88" s="32" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="BD89" s="32" t="n">
+        <v>63</v>
+      </c>
+      <c r="BE89" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF89" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG89" s="32" t="inlineStr">
+        <is>
+          <t>lps33hw</t>
+        </is>
+      </c>
+      <c r="BH89" s="32" t="inlineStr">
+        <is>
+          <t>LPS33HW</t>
+        </is>
+      </c>
+      <c r="BI89" s="32" t="inlineStr">
         <is>
           <t>0x5D</t>
         </is>
       </c>
-      <c r="BJ66" s="30" t="inlineStr">
-        <is>
-          <t>0x5C, 0x5D</t>
-        </is>
-      </c>
-      <c r="BK66" s="30" t="inlineStr"/>
-      <c r="BL66" s="30" t="inlineStr">
+      <c r="BJ89" s="32" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+      <c r="BK89" s="32" t="inlineStr">
+        <is>
+          <t>0x5D, 0x5C</t>
+        </is>
+      </c>
+      <c r="BL89" s="32" t="inlineStr"/>
+      <c r="BM89" s="32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="67">
-      <c r="BD67" s="30" t="n">
-        <v>41</v>
-      </c>
-      <c r="BE67" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF67" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch0</t>
-        </is>
-      </c>
-      <c r="BG67" s="30" t="inlineStr">
-        <is>
-          <t>mpl115a2</t>
-        </is>
-      </c>
-      <c r="BH67" s="30" t="inlineStr">
-        <is>
-          <t>MPL115A2</t>
-        </is>
-      </c>
-      <c r="BI67" s="30" t="inlineStr">
+      <c r="BN89" s="32" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="BD90" s="32" t="n">
+        <v>64</v>
+      </c>
+      <c r="BE90" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF90" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG90" s="32" t="inlineStr">
+        <is>
+          <t>vcnl4040</t>
+        </is>
+      </c>
+      <c r="BH90" s="32" t="inlineStr">
+        <is>
+          <t>VCNL4040</t>
+        </is>
+      </c>
+      <c r="BI90" s="32" t="inlineStr">
         <is>
           <t>0x60</t>
         </is>
       </c>
-      <c r="BJ67" s="30" t="inlineStr">
+      <c r="BJ90" s="32" t="inlineStr">
         <is>
           <t>0x60</t>
         </is>
       </c>
-      <c r="BK67" s="30" t="inlineStr"/>
-      <c r="BL67" s="30" t="inlineStr">
+      <c r="BK90" s="32" t="inlineStr">
+        <is>
+          <t>0x60</t>
+        </is>
+      </c>
+      <c r="BL90" s="32" t="inlineStr"/>
+      <c r="BM90" s="32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="68">
-      <c r="BD68" s="30" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE68" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF68" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch0</t>
-        </is>
-      </c>
-      <c r="BG68" s="30" t="inlineStr">
-        <is>
-          <t>scd30</t>
-        </is>
-      </c>
-      <c r="BH68" s="30" t="inlineStr">
-        <is>
-          <t>SCD30</t>
-        </is>
-      </c>
-      <c r="BI68" s="30" t="inlineStr">
-        <is>
-          <t>0x61</t>
-        </is>
-      </c>
-      <c r="BJ68" s="30" t="inlineStr">
-        <is>
-          <t>0x61</t>
-        </is>
-      </c>
-      <c r="BK68" s="30" t="inlineStr"/>
-      <c r="BL68" s="30" t="inlineStr">
+      <c r="BN90" s="32" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="BD91" s="32" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE91" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF91" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG91" s="32" t="inlineStr">
+        <is>
+          <t>sen54</t>
+        </is>
+      </c>
+      <c r="BH91" s="32" t="inlineStr">
+        <is>
+          <t>SEN54</t>
+        </is>
+      </c>
+      <c r="BI91" s="32" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="BJ91" s="32" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="BK91" s="32" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="BL91" s="32" t="inlineStr"/>
+      <c r="BM91" s="32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="69">
-      <c r="BD69" s="30" t="n">
-        <v>43</v>
-      </c>
-      <c r="BE69" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF69" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch0</t>
-        </is>
-      </c>
-      <c r="BG69" s="30" t="inlineStr">
-        <is>
-          <t>scd40</t>
-        </is>
-      </c>
-      <c r="BH69" s="30" t="inlineStr">
-        <is>
-          <t>SCD40/SCD41</t>
-        </is>
-      </c>
-      <c r="BI69" s="30" t="inlineStr">
-        <is>
-          <t>0x62</t>
-        </is>
-      </c>
-      <c r="BJ69" s="30" t="inlineStr">
-        <is>
-          <t>0x62</t>
-        </is>
-      </c>
-      <c r="BK69" s="30" t="inlineStr"/>
-      <c r="BL69" s="30" t="inlineStr">
+      <c r="BN91" s="32" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="BD92" s="32" t="n">
+        <v>66</v>
+      </c>
+      <c r="BE92" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF92" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch1</t>
+        </is>
+      </c>
+      <c r="BG92" s="32" t="inlineStr">
+        <is>
+          <t>bme680</t>
+        </is>
+      </c>
+      <c r="BH92" s="32" t="inlineStr">
+        <is>
+          <t>BME680</t>
+        </is>
+      </c>
+      <c r="BI92" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="BJ92" s="32" t="inlineStr">
+        <is>
+          <t>0x77</t>
+        </is>
+      </c>
+      <c r="BK92" s="32" t="inlineStr">
+        <is>
+          <t>0x77, 0x76</t>
+        </is>
+      </c>
+      <c r="BL92" s="32" t="inlineStr"/>
+      <c r="BM92" s="32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="70">
-      <c r="BD70" s="30" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE70" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF70" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch0</t>
-        </is>
-      </c>
-      <c r="BG70" s="30" t="inlineStr">
-        <is>
-          <t>sen50</t>
-        </is>
-      </c>
-      <c r="BH70" s="30" t="inlineStr">
-        <is>
-          <t>SEN50</t>
-        </is>
-      </c>
-      <c r="BI70" s="30" t="inlineStr">
+      <c r="BN92" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="BD93" s="31" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE93" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF93" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch2</t>
+        </is>
+      </c>
+      <c r="BG93" s="31" t="inlineStr">
+        <is>
+          <t>vl53l0x</t>
+        </is>
+      </c>
+      <c r="BH93" s="31" t="inlineStr">
+        <is>
+          <t>VL53L0X</t>
+        </is>
+      </c>
+      <c r="BI93" s="31" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="BJ93" s="31" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="BK93" s="31" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="BL93" s="31" t="inlineStr"/>
+      <c r="BM93" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN93" s="31" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="BD94" s="31" t="n">
+        <v>68</v>
+      </c>
+      <c r="BE94" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF94" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch2</t>
+        </is>
+      </c>
+      <c r="BG94" s="31" t="inlineStr">
+        <is>
+          <t>am2301b</t>
+        </is>
+      </c>
+      <c r="BH94" s="31" t="inlineStr">
+        <is>
+          <t>AM2301B</t>
+        </is>
+      </c>
+      <c r="BI94" s="31" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="BJ94" s="31" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="BK94" s="31" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="BL94" s="31" t="inlineStr"/>
+      <c r="BM94" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN94" s="31" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="BD95" s="31" t="n">
+        <v>69</v>
+      </c>
+      <c r="BE95" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF95" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch2</t>
+        </is>
+      </c>
+      <c r="BG95" s="31" t="inlineStr">
+        <is>
+          <t>si7021</t>
+        </is>
+      </c>
+      <c r="BH95" s="31" t="inlineStr">
+        <is>
+          <t>Si7021</t>
+        </is>
+      </c>
+      <c r="BI95" s="31" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="BJ95" s="31" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="BK95" s="31" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="BL95" s="31" t="inlineStr"/>
+      <c r="BM95" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN95" s="31" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="BD96" s="31" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE96" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF96" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch2</t>
+        </is>
+      </c>
+      <c r="BG96" s="31" t="inlineStr">
+        <is>
+          <t>ina228</t>
+        </is>
+      </c>
+      <c r="BH96" s="31" t="inlineStr">
+        <is>
+          <t>INA228</t>
+        </is>
+      </c>
+      <c r="BI96" s="30" t="inlineStr">
+        <is>
+          <t>0x41</t>
+        </is>
+      </c>
+      <c r="BJ96" s="31" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="BK96" s="31" t="inlineStr">
+        <is>
+          <t>0x40, 0x41, 0x44, 0x45</t>
+        </is>
+      </c>
+      <c r="BL96" s="31" t="inlineStr"/>
+      <c r="BM96" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN96" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="BD97" s="31" t="n">
+        <v>71</v>
+      </c>
+      <c r="BE97" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF97" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch2</t>
+        </is>
+      </c>
+      <c r="BG97" s="31" t="inlineStr">
+        <is>
+          <t>sht40</t>
+        </is>
+      </c>
+      <c r="BH97" s="31" t="inlineStr">
+        <is>
+          <t>SHT40</t>
+        </is>
+      </c>
+      <c r="BI97" s="31" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="BJ97" s="31" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="BK97" s="31" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="BL97" s="31" t="inlineStr"/>
+      <c r="BM97" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN97" s="31" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="BD98" s="31" t="n">
+        <v>72</v>
+      </c>
+      <c r="BE98" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF98" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch2</t>
+        </is>
+      </c>
+      <c r="BG98" s="31" t="inlineStr">
+        <is>
+          <t>ina237</t>
+        </is>
+      </c>
+      <c r="BH98" s="31" t="inlineStr">
+        <is>
+          <t>INA237</t>
+        </is>
+      </c>
+      <c r="BI98" s="30" t="inlineStr">
+        <is>
+          <t>0x45</t>
+        </is>
+      </c>
+      <c r="BJ98" s="31" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="BK98" s="31" t="inlineStr">
+        <is>
+          <t>0x40, 0x41, 0x44, 0x45</t>
+        </is>
+      </c>
+      <c r="BL98" s="31" t="inlineStr"/>
+      <c r="BM98" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN98" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="BD99" s="31" t="n">
+        <v>73</v>
+      </c>
+      <c r="BE99" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF99" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch2</t>
+        </is>
+      </c>
+      <c r="BG99" s="31" t="inlineStr">
+        <is>
+          <t>lps35hw</t>
+        </is>
+      </c>
+      <c r="BH99" s="31" t="inlineStr">
+        <is>
+          <t>LPS35HW</t>
+        </is>
+      </c>
+      <c r="BI99" s="31" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+      <c r="BJ99" s="31" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+      <c r="BK99" s="31" t="inlineStr">
+        <is>
+          <t>0x5D, 0x5C</t>
+        </is>
+      </c>
+      <c r="BL99" s="31" t="inlineStr"/>
+      <c r="BM99" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN99" s="31" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="BD100" s="31" t="n">
+        <v>74</v>
+      </c>
+      <c r="BE100" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF100" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch2</t>
+        </is>
+      </c>
+      <c r="BG100" s="31" t="inlineStr">
+        <is>
+          <t>sen55</t>
+        </is>
+      </c>
+      <c r="BH100" s="31" t="inlineStr">
+        <is>
+          <t>SEN55</t>
+        </is>
+      </c>
+      <c r="BI100" s="31" t="inlineStr">
         <is>
           <t>0x69</t>
         </is>
       </c>
-      <c r="BJ70" s="30" t="inlineStr">
+      <c r="BJ100" s="31" t="inlineStr">
         <is>
           <t>0x69</t>
         </is>
       </c>
-      <c r="BK70" s="30" t="inlineStr"/>
-      <c r="BL70" s="30" t="inlineStr">
+      <c r="BK100" s="31" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="BL100" s="31" t="inlineStr"/>
+      <c r="BM100" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="71">
-      <c r="BD71" s="30" t="n">
-        <v>45</v>
-      </c>
-      <c r="BE71" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF71" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch0</t>
-        </is>
-      </c>
-      <c r="BG71" s="30" t="inlineStr">
-        <is>
-          <t>shtc3</t>
-        </is>
-      </c>
-      <c r="BH71" s="30" t="inlineStr">
-        <is>
-          <t>SHTC3</t>
-        </is>
-      </c>
-      <c r="BI71" s="30" t="inlineStr">
-        <is>
-          <t>0x70</t>
-        </is>
-      </c>
-      <c r="BJ71" s="30" t="inlineStr">
-        <is>
-          <t>0x70</t>
-        </is>
-      </c>
-      <c r="BK71" s="30" t="inlineStr"/>
-      <c r="BL71" s="30" t="inlineStr">
+      <c r="BN100" s="31" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="BD101" s="31" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE101" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF101" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch2</t>
+        </is>
+      </c>
+      <c r="BG101" s="31" t="inlineStr">
+        <is>
+          <t>bme688</t>
+        </is>
+      </c>
+      <c r="BH101" s="31" t="inlineStr">
+        <is>
+          <t>BME688</t>
+        </is>
+      </c>
+      <c r="BI101" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="BJ101" s="31" t="inlineStr">
+        <is>
+          <t>0x77</t>
+        </is>
+      </c>
+      <c r="BK101" s="31" t="inlineStr">
+        <is>
+          <t>0x77, 0x76</t>
+        </is>
+      </c>
+      <c r="BL101" s="31" t="inlineStr"/>
+      <c r="BM101" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="72">
-      <c r="BD72" s="30" t="n">
-        <v>46</v>
-      </c>
-      <c r="BE72" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF72" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch0</t>
-        </is>
-      </c>
-      <c r="BG72" s="30" t="inlineStr">
-        <is>
-          <t>as7331</t>
-        </is>
-      </c>
-      <c r="BH72" s="30" t="inlineStr">
-        <is>
-          <t>AS7331</t>
-        </is>
-      </c>
-      <c r="BI72" s="30" t="inlineStr">
-        <is>
-          <t>0x74</t>
-        </is>
-      </c>
-      <c r="BJ72" s="30" t="inlineStr">
-        <is>
-          <t>0x74, 0x75, 0x76, 0x77</t>
-        </is>
-      </c>
-      <c r="BK72" s="30" t="inlineStr"/>
-      <c r="BL72" s="30" t="inlineStr">
+      <c r="BN101" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="BD102" s="32" t="n">
+        <v>76</v>
+      </c>
+      <c r="BE102" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF102" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch3</t>
+        </is>
+      </c>
+      <c r="BG102" s="32" t="inlineStr">
+        <is>
+          <t>vl53l1x</t>
+        </is>
+      </c>
+      <c r="BH102" s="32" t="inlineStr">
+        <is>
+          <t>VL53L1X</t>
+        </is>
+      </c>
+      <c r="BI102" s="32" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="BJ102" s="32" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="BK102" s="32" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="BL102" s="32" t="inlineStr"/>
+      <c r="BM102" s="32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="73">
-      <c r="BD73" s="30" t="n">
-        <v>47</v>
-      </c>
-      <c r="BE73" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF73" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch0</t>
-        </is>
-      </c>
-      <c r="BG73" s="30" t="inlineStr">
-        <is>
-          <t>bme280</t>
-        </is>
-      </c>
-      <c r="BH73" s="30" t="inlineStr">
-        <is>
-          <t>BME280</t>
-        </is>
-      </c>
-      <c r="BI73" s="30" t="inlineStr">
+      <c r="BN102" s="32" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="BD103" s="32" t="n">
+        <v>77</v>
+      </c>
+      <c r="BE103" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF103" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch3</t>
+        </is>
+      </c>
+      <c r="BG103" s="32" t="inlineStr">
+        <is>
+          <t>am2315c</t>
+        </is>
+      </c>
+      <c r="BH103" s="32" t="inlineStr">
+        <is>
+          <t>AM2315C</t>
+        </is>
+      </c>
+      <c r="BI103" s="32" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="BJ103" s="32" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="BK103" s="32" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="BL103" s="32" t="inlineStr"/>
+      <c r="BM103" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN103" s="32" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="BD104" s="32" t="n">
+        <v>78</v>
+      </c>
+      <c r="BE104" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF104" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch3</t>
+        </is>
+      </c>
+      <c r="BG104" s="32" t="inlineStr">
+        <is>
+          <t>ms8607</t>
+        </is>
+      </c>
+      <c r="BH104" s="32" t="inlineStr">
+        <is>
+          <t>MS8607</t>
+        </is>
+      </c>
+      <c r="BI104" s="32" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="BJ104" s="32" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="BK104" s="32" t="inlineStr">
+        <is>
+          <t>0x40, 0x76</t>
+        </is>
+      </c>
+      <c r="BL104" s="32" t="inlineStr"/>
+      <c r="BM104" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN104" s="32" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="BD105" s="32" t="n">
+        <v>79</v>
+      </c>
+      <c r="BE105" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF105" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch3</t>
+        </is>
+      </c>
+      <c r="BG105" s="32" t="inlineStr">
+        <is>
+          <t>ina238</t>
+        </is>
+      </c>
+      <c r="BH105" s="32" t="inlineStr">
+        <is>
+          <t>INA238</t>
+        </is>
+      </c>
+      <c r="BI105" s="30" t="inlineStr">
+        <is>
+          <t>0x41</t>
+        </is>
+      </c>
+      <c r="BJ105" s="32" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="BK105" s="32" t="inlineStr">
+        <is>
+          <t>0x40, 0x41, 0x44, 0x45</t>
+        </is>
+      </c>
+      <c r="BL105" s="32" t="inlineStr"/>
+      <c r="BM105" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN105" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="BD106" s="32" t="n">
+        <v>80</v>
+      </c>
+      <c r="BE106" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF106" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch3</t>
+        </is>
+      </c>
+      <c r="BG106" s="32" t="inlineStr">
+        <is>
+          <t>sht41</t>
+        </is>
+      </c>
+      <c r="BH106" s="32" t="inlineStr">
+        <is>
+          <t>SHT41</t>
+        </is>
+      </c>
+      <c r="BI106" s="32" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="BJ106" s="32" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="BK106" s="32" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="BL106" s="32" t="inlineStr"/>
+      <c r="BM106" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN106" s="32" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="BD107" s="32" t="n">
+        <v>81</v>
+      </c>
+      <c r="BE107" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF107" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch3</t>
+        </is>
+      </c>
+      <c r="BG107" s="32" t="inlineStr">
+        <is>
+          <t>ina260</t>
+        </is>
+      </c>
+      <c r="BH107" s="32" t="inlineStr">
+        <is>
+          <t>INA260</t>
+        </is>
+      </c>
+      <c r="BI107" s="30" t="inlineStr">
+        <is>
+          <t>0x45</t>
+        </is>
+      </c>
+      <c r="BJ107" s="32" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="BK107" s="32" t="inlineStr">
+        <is>
+          <t>0x40, 0x41, 0x44, 0x45</t>
+        </is>
+      </c>
+      <c r="BL107" s="32" t="inlineStr"/>
+      <c r="BM107" s="32" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN107" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="BD108" s="32" t="n">
+        <v>82</v>
+      </c>
+      <c r="BE108" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF108" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch3</t>
+        </is>
+      </c>
+      <c r="BG108" s="32" t="inlineStr">
+        <is>
+          <t>sen5x</t>
+        </is>
+      </c>
+      <c r="BH108" s="32" t="inlineStr">
+        <is>
+          <t>SEN5x</t>
+        </is>
+      </c>
+      <c r="BI108" s="32" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="BJ108" s="32" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="BK108" s="32" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="BL108" s="32" t="inlineStr"/>
+      <c r="BM108" s="32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="BN108" s="32" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="BD109" s="32" t="n">
+        <v>83</v>
+      </c>
+      <c r="BE109" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF109" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch3</t>
+        </is>
+      </c>
+      <c r="BG109" s="32" t="inlineStr">
+        <is>
+          <t>bmp280</t>
+        </is>
+      </c>
+      <c r="BH109" s="32" t="inlineStr">
+        <is>
+          <t>BMP280</t>
+        </is>
+      </c>
+      <c r="BI109" s="30" t="inlineStr">
         <is>
           <t>0x76</t>
         </is>
       </c>
-      <c r="BJ73" s="30" t="inlineStr">
-        <is>
-          <t>0x76, 0x77</t>
-        </is>
-      </c>
-      <c r="BK73" s="30" t="inlineStr"/>
-      <c r="BL73" s="30" t="inlineStr">
+      <c r="BJ109" s="32" t="inlineStr">
+        <is>
+          <t>0x77</t>
+        </is>
+      </c>
+      <c r="BK109" s="32" t="inlineStr">
+        <is>
+          <t>0x77, 0x76</t>
+        </is>
+      </c>
+      <c r="BL109" s="32" t="inlineStr"/>
+      <c r="BM109" s="32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="74">
-      <c r="BD74" s="31" t="n">
-        <v>48</v>
-      </c>
-      <c r="BE74" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF74" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG74" s="31" t="inlineStr">
-        <is>
-          <t>mprls</t>
-        </is>
-      </c>
-      <c r="BH74" s="31" t="inlineStr">
-        <is>
-          <t>MPRLS</t>
-        </is>
-      </c>
-      <c r="BI74" s="31" t="inlineStr">
-        <is>
-          <t>0x18</t>
-        </is>
-      </c>
-      <c r="BJ74" s="31" t="inlineStr">
-        <is>
-          <t>0x18</t>
-        </is>
-      </c>
-      <c r="BK74" s="31" t="inlineStr"/>
-      <c r="BL74" s="31" t="inlineStr">
+      <c r="BN109" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="BD110" s="31" t="n">
+        <v>84</v>
+      </c>
+      <c r="BE110" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF110" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch4</t>
+        </is>
+      </c>
+      <c r="BG110" s="31" t="inlineStr">
+        <is>
+          <t>vl53l4cd</t>
+        </is>
+      </c>
+      <c r="BH110" s="31" t="inlineStr">
+        <is>
+          <t>VL53L4CD</t>
+        </is>
+      </c>
+      <c r="BI110" s="31" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="BJ110" s="31" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="BK110" s="31" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="BL110" s="31" t="inlineStr"/>
+      <c r="BM110" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="75">
-      <c r="BD75" s="31" t="n">
-        <v>49</v>
-      </c>
-      <c r="BE75" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF75" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG75" s="31" t="inlineStr">
-        <is>
-          <t>ltr329</t>
-        </is>
-      </c>
-      <c r="BH75" s="31" t="inlineStr">
-        <is>
-          <t>LTR-329</t>
-        </is>
-      </c>
-      <c r="BI75" s="31" t="inlineStr">
+      <c r="BN110" s="31" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="BD111" s="31" t="n">
+        <v>85</v>
+      </c>
+      <c r="BE111" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF111" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch4</t>
+        </is>
+      </c>
+      <c r="BG111" s="31" t="inlineStr">
+        <is>
+          <t>dht20</t>
+        </is>
+      </c>
+      <c r="BH111" s="31" t="inlineStr">
+        <is>
+          <t>DHT20</t>
+        </is>
+      </c>
+      <c r="BI111" s="31" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="BJ111" s="31" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="BK111" s="31" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="BL111" s="31" t="inlineStr"/>
+      <c r="BM111" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN111" s="31" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="BD112" s="31" t="n">
+        <v>86</v>
+      </c>
+      <c r="BE112" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF112" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch4</t>
+        </is>
+      </c>
+      <c r="BG112" s="31" t="inlineStr">
+        <is>
+          <t>sht45</t>
+        </is>
+      </c>
+      <c r="BH112" s="31" t="inlineStr">
+        <is>
+          <t>SHT45</t>
+        </is>
+      </c>
+      <c r="BI112" s="31" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="BJ112" s="31" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="BK112" s="31" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="BL112" s="31" t="inlineStr"/>
+      <c r="BM112" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN112" s="31" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="BD113" s="31" t="n">
+        <v>87</v>
+      </c>
+      <c r="BE113" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF113" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch4</t>
+        </is>
+      </c>
+      <c r="BG113" s="31" t="inlineStr">
+        <is>
+          <t>bmp388</t>
+        </is>
+      </c>
+      <c r="BH113" s="31" t="inlineStr">
+        <is>
+          <t>BMP388</t>
+        </is>
+      </c>
+      <c r="BI113" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="BJ113" s="31" t="inlineStr">
+        <is>
+          <t>0x77</t>
+        </is>
+      </c>
+      <c r="BK113" s="31" t="inlineStr">
+        <is>
+          <t>0x77, 0x76</t>
+        </is>
+      </c>
+      <c r="BL113" s="31" t="inlineStr"/>
+      <c r="BM113" s="31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BN113" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="BD114" s="32" t="n">
+        <v>88</v>
+      </c>
+      <c r="BE114" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF114" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch5</t>
+        </is>
+      </c>
+      <c r="BG114" s="32" t="inlineStr">
+        <is>
+          <t>vl53l4cx</t>
+        </is>
+      </c>
+      <c r="BH114" s="32" t="inlineStr">
+        <is>
+          <t>VL53L4CX</t>
+        </is>
+      </c>
+      <c r="BI114" s="32" t="inlineStr">
         <is>
           <t>0x29</t>
         </is>
       </c>
-      <c r="BJ75" s="31" t="inlineStr">
+      <c r="BJ114" s="32" t="inlineStr">
         <is>
           <t>0x29</t>
         </is>
       </c>
-      <c r="BK75" s="31" t="inlineStr"/>
-      <c r="BL75" s="31" t="inlineStr">
+      <c r="BK114" s="32" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="BL114" s="32" t="inlineStr"/>
+      <c r="BM114" s="32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="76">
-      <c r="BD76" s="31" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE76" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF76" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG76" s="31" t="inlineStr">
-        <is>
-          <t>max17048</t>
-        </is>
-      </c>
-      <c r="BH76" s="31" t="inlineStr">
-        <is>
-          <t>MAX17048/MAX17049</t>
-        </is>
-      </c>
-      <c r="BI76" s="31" t="inlineStr">
-        <is>
-          <t>0x36</t>
-        </is>
-      </c>
-      <c r="BJ76" s="31" t="inlineStr">
-        <is>
-          <t>0x36</t>
-        </is>
-      </c>
-      <c r="BK76" s="31" t="inlineStr"/>
-      <c r="BL76" s="31" t="inlineStr">
+      <c r="BN114" s="32" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="BD115" s="32" t="n">
+        <v>89</v>
+      </c>
+      <c r="BE115" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF115" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch5</t>
+        </is>
+      </c>
+      <c r="BG115" s="32" t="inlineStr">
+        <is>
+          <t>bmp390</t>
+        </is>
+      </c>
+      <c r="BH115" s="32" t="inlineStr">
+        <is>
+          <t>BMP390</t>
+        </is>
+      </c>
+      <c r="BI115" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="BJ115" s="32" t="inlineStr">
+        <is>
+          <t>0x77</t>
+        </is>
+      </c>
+      <c r="BK115" s="32" t="inlineStr">
+        <is>
+          <t>0x77, 0x76</t>
+        </is>
+      </c>
+      <c r="BL115" s="32" t="inlineStr"/>
+      <c r="BM115" s="32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="77">
-      <c r="BD77" s="31" t="n">
-        <v>51</v>
-      </c>
-      <c r="BE77" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF77" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG77" s="31" t="inlineStr">
-        <is>
-          <t>aht21</t>
-        </is>
-      </c>
-      <c r="BH77" s="31" t="inlineStr">
-        <is>
-          <t>AHT21</t>
-        </is>
-      </c>
-      <c r="BI77" s="31" t="inlineStr">
-        <is>
-          <t>0x38</t>
-        </is>
-      </c>
-      <c r="BJ77" s="31" t="inlineStr">
-        <is>
-          <t>0x38</t>
-        </is>
-      </c>
-      <c r="BK77" s="31" t="inlineStr"/>
-      <c r="BL77" s="31" t="inlineStr">
+      <c r="BN115" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="BD116" s="31" t="n">
+        <v>90</v>
+      </c>
+      <c r="BE116" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF116" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch6</t>
+        </is>
+      </c>
+      <c r="BG116" s="31" t="inlineStr">
+        <is>
+          <t>vl6180x</t>
+        </is>
+      </c>
+      <c r="BH116" s="31" t="inlineStr">
+        <is>
+          <t>VL6180X</t>
+        </is>
+      </c>
+      <c r="BI116" s="31" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="BJ116" s="31" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="BK116" s="31" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="BL116" s="31" t="inlineStr"/>
+      <c r="BM116" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="78">
-      <c r="BD78" s="31" t="n">
-        <v>52</v>
-      </c>
-      <c r="BE78" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF78" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG78" s="31" t="inlineStr">
-        <is>
-          <t>mlx90632d_med</t>
-        </is>
-      </c>
-      <c r="BH78" s="31" t="inlineStr">
-        <is>
-          <t>MLX90632</t>
-        </is>
-      </c>
-      <c r="BI78" s="31" t="inlineStr">
-        <is>
-          <t>0x3A</t>
-        </is>
-      </c>
-      <c r="BJ78" s="31" t="inlineStr">
-        <is>
-          <t>0x3A, 0x3B</t>
-        </is>
-      </c>
-      <c r="BK78" s="31" t="inlineStr"/>
-      <c r="BL78" s="31" t="inlineStr">
+      <c r="BN116" s="31" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="BD117" s="31" t="n">
+        <v>91</v>
+      </c>
+      <c r="BE117" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF117" s="31" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch6</t>
+        </is>
+      </c>
+      <c r="BG117" s="31" t="inlineStr">
+        <is>
+          <t>dps310</t>
+        </is>
+      </c>
+      <c r="BH117" s="31" t="inlineStr">
+        <is>
+          <t>DPS310</t>
+        </is>
+      </c>
+      <c r="BI117" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="BJ117" s="31" t="inlineStr">
+        <is>
+          <t>0x77</t>
+        </is>
+      </c>
+      <c r="BK117" s="31" t="inlineStr">
+        <is>
+          <t>0x77, 0x76</t>
+        </is>
+      </c>
+      <c r="BL117" s="31" t="inlineStr"/>
+      <c r="BM117" s="31" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="79">
-      <c r="BD79" s="31" t="n">
-        <v>53</v>
-      </c>
-      <c r="BE79" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF79" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG79" s="31" t="inlineStr">
-        <is>
-          <t>sht20</t>
-        </is>
-      </c>
-      <c r="BH79" s="31" t="inlineStr">
-        <is>
-          <t>SHT20</t>
-        </is>
-      </c>
-      <c r="BI79" s="31" t="inlineStr">
-        <is>
-          <t>0x40</t>
-        </is>
-      </c>
-      <c r="BJ79" s="31" t="inlineStr">
-        <is>
-          <t>0x40</t>
-        </is>
-      </c>
-      <c r="BK79" s="31" t="inlineStr"/>
-      <c r="BL79" s="31" t="inlineStr">
+      <c r="BN117" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="BD118" s="32" t="n">
+        <v>92</v>
+      </c>
+      <c r="BE118" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF118" s="32" t="inlineStr">
+        <is>
+          <t>8ch_mux_ch7</t>
+        </is>
+      </c>
+      <c r="BG118" s="32" t="inlineStr">
+        <is>
+          <t>spa06_003</t>
+        </is>
+      </c>
+      <c r="BH118" s="32" t="inlineStr">
+        <is>
+          <t>SPA06-003</t>
+        </is>
+      </c>
+      <c r="BI118" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="BJ118" s="32" t="inlineStr">
+        <is>
+          <t>0x77</t>
+        </is>
+      </c>
+      <c r="BK118" s="32" t="inlineStr">
+        <is>
+          <t>0x77, 0x76</t>
+        </is>
+      </c>
+      <c r="BL118" s="32" t="inlineStr"/>
+      <c r="BM118" s="32" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-    </row>
-    <row r="80">
-      <c r="BD80" s="31" t="n">
-        <v>54</v>
-      </c>
-      <c r="BE80" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF80" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG80" s="31" t="inlineStr">
-        <is>
-          <t>ina219</t>
-        </is>
-      </c>
-      <c r="BH80" s="31" t="inlineStr">
-        <is>
-          <t>INA219</t>
-        </is>
-      </c>
-      <c r="BI80" s="31" t="inlineStr">
-        <is>
-          <t>0x41</t>
-        </is>
-      </c>
-      <c r="BJ80" s="31" t="inlineStr">
-        <is>
-          <t>0x40, 0x41, 0x44, 0x45</t>
-        </is>
-      </c>
-      <c r="BK80" s="31" t="inlineStr"/>
-      <c r="BL80" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="BD81" s="31" t="n">
-        <v>55</v>
-      </c>
-      <c r="BE81" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF81" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG81" s="31" t="inlineStr">
-        <is>
-          <t>sht30_shell</t>
-        </is>
-      </c>
-      <c r="BH81" s="31" t="inlineStr">
-        <is>
-          <t>Enclosed SHT30</t>
-        </is>
-      </c>
-      <c r="BI81" s="31" t="inlineStr">
-        <is>
-          <t>0x44</t>
-        </is>
-      </c>
-      <c r="BJ81" s="31" t="inlineStr">
-        <is>
-          <t>0x44</t>
-        </is>
-      </c>
-      <c r="BK81" s="31" t="inlineStr"/>
-      <c r="BL81" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="BD82" s="31" t="n">
-        <v>56</v>
-      </c>
-      <c r="BE82" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF82" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG82" s="31" t="inlineStr">
-        <is>
-          <t>hdc302x</t>
-        </is>
-      </c>
-      <c r="BH82" s="31" t="inlineStr">
-        <is>
-          <t>HDC302x</t>
-        </is>
-      </c>
-      <c r="BI82" s="31" t="inlineStr">
-        <is>
-          <t>0x45</t>
-        </is>
-      </c>
-      <c r="BJ82" s="31" t="inlineStr">
-        <is>
-          <t>0x44, 0x45, 0x46, 0x47</t>
-        </is>
-      </c>
-      <c r="BK82" s="31" t="inlineStr"/>
-      <c r="BL82" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="BD83" s="31" t="n">
-        <v>57</v>
-      </c>
-      <c r="BE83" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF83" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG83" s="31" t="inlineStr">
-        <is>
-          <t>bmp585</t>
-        </is>
-      </c>
-      <c r="BH83" s="31" t="inlineStr">
-        <is>
-          <t>BMP585</t>
-        </is>
-      </c>
-      <c r="BI83" s="31" t="inlineStr">
-        <is>
-          <t>0x46</t>
-        </is>
-      </c>
-      <c r="BJ83" s="31" t="inlineStr">
-        <is>
-          <t>0x46, 0x47</t>
-        </is>
-      </c>
-      <c r="BK83" s="31" t="inlineStr"/>
-      <c r="BL83" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="BD84" s="31" t="n">
-        <v>58</v>
-      </c>
-      <c r="BE84" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF84" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG84" s="31" t="inlineStr">
-        <is>
-          <t>tmp119</t>
-        </is>
-      </c>
-      <c r="BH84" s="31" t="inlineStr">
-        <is>
-          <t>TMP119</t>
-        </is>
-      </c>
-      <c r="BI84" s="31" t="inlineStr">
-        <is>
-          <t>0x48</t>
-        </is>
-      </c>
-      <c r="BJ84" s="31" t="inlineStr">
-        <is>
-          <t>0x48, 0x49, 0x4A, 0x4B</t>
-        </is>
-      </c>
-      <c r="BK84" s="31" t="inlineStr"/>
-      <c r="BL84" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="BD85" s="31" t="n">
-        <v>59</v>
-      </c>
-      <c r="BE85" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF85" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG85" s="31" t="inlineStr">
-        <is>
-          <t>ens160</t>
-        </is>
-      </c>
-      <c r="BH85" s="31" t="inlineStr">
-        <is>
-          <t>ENS160</t>
-        </is>
-      </c>
-      <c r="BI85" s="31" t="inlineStr">
-        <is>
-          <t>0x52</t>
-        </is>
-      </c>
-      <c r="BJ85" s="31" t="inlineStr">
-        <is>
-          <t>0x52, 0x53</t>
-        </is>
-      </c>
-      <c r="BK85" s="31" t="inlineStr"/>
-      <c r="BL85" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="BD86" s="31" t="n">
-        <v>60</v>
-      </c>
-      <c r="BE86" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF86" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG86" s="31" t="inlineStr">
-        <is>
-          <t>ens161</t>
-        </is>
-      </c>
-      <c r="BH86" s="31" t="inlineStr">
-        <is>
-          <t>ENS161</t>
-        </is>
-      </c>
-      <c r="BI86" s="31" t="inlineStr">
-        <is>
-          <t>0x53</t>
-        </is>
-      </c>
-      <c r="BJ86" s="31" t="inlineStr">
-        <is>
-          <t>0x52, 0x53</t>
-        </is>
-      </c>
-      <c r="BK86" s="31" t="inlineStr"/>
-      <c r="BL86" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="BD87" s="31" t="n">
-        <v>61</v>
-      </c>
-      <c r="BE87" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF87" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG87" s="31" t="inlineStr">
-        <is>
-          <t>sgp41</t>
-        </is>
-      </c>
-      <c r="BH87" s="31" t="inlineStr">
-        <is>
-          <t>SGP41</t>
-        </is>
-      </c>
-      <c r="BI87" s="31" t="inlineStr">
-        <is>
-          <t>0x59</t>
-        </is>
-      </c>
-      <c r="BJ87" s="31" t="inlineStr">
-        <is>
-          <t>0x59</t>
-        </is>
-      </c>
-      <c r="BK87" s="31" t="inlineStr"/>
-      <c r="BL87" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="BD88" s="31" t="n">
-        <v>62</v>
-      </c>
-      <c r="BE88" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF88" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG88" s="31" t="inlineStr">
-        <is>
-          <t>lps28dfw</t>
-        </is>
-      </c>
-      <c r="BH88" s="31" t="inlineStr">
-        <is>
-          <t>LPS28DFW</t>
-        </is>
-      </c>
-      <c r="BI88" s="31" t="inlineStr">
-        <is>
-          <t>0x5C</t>
-        </is>
-      </c>
-      <c r="BJ88" s="31" t="inlineStr">
-        <is>
-          <t>0x5C, 0x5D</t>
-        </is>
-      </c>
-      <c r="BK88" s="31" t="inlineStr"/>
-      <c r="BL88" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="BD89" s="31" t="n">
-        <v>63</v>
-      </c>
-      <c r="BE89" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF89" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG89" s="31" t="inlineStr">
-        <is>
-          <t>lps33hw</t>
-        </is>
-      </c>
-      <c r="BH89" s="31" t="inlineStr">
-        <is>
-          <t>LPS33HW</t>
-        </is>
-      </c>
-      <c r="BI89" s="31" t="inlineStr">
-        <is>
-          <t>0x5D</t>
-        </is>
-      </c>
-      <c r="BJ89" s="31" t="inlineStr">
-        <is>
-          <t>0x5C, 0x5D</t>
-        </is>
-      </c>
-      <c r="BK89" s="31" t="inlineStr"/>
-      <c r="BL89" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="BD90" s="31" t="n">
-        <v>64</v>
-      </c>
-      <c r="BE90" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF90" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG90" s="31" t="inlineStr">
-        <is>
-          <t>vcnl4040</t>
-        </is>
-      </c>
-      <c r="BH90" s="31" t="inlineStr">
-        <is>
-          <t>VCNL4040</t>
-        </is>
-      </c>
-      <c r="BI90" s="31" t="inlineStr">
-        <is>
-          <t>0x60</t>
-        </is>
-      </c>
-      <c r="BJ90" s="31" t="inlineStr">
-        <is>
-          <t>0x60</t>
-        </is>
-      </c>
-      <c r="BK90" s="31" t="inlineStr"/>
-      <c r="BL90" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="BD91" s="31" t="n">
-        <v>65</v>
-      </c>
-      <c r="BE91" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF91" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG91" s="31" t="inlineStr">
-        <is>
-          <t>sen54</t>
-        </is>
-      </c>
-      <c r="BH91" s="31" t="inlineStr">
-        <is>
-          <t>SEN54</t>
-        </is>
-      </c>
-      <c r="BI91" s="31" t="inlineStr">
-        <is>
-          <t>0x69</t>
-        </is>
-      </c>
-      <c r="BJ91" s="31" t="inlineStr">
-        <is>
-          <t>0x69</t>
-        </is>
-      </c>
-      <c r="BK91" s="31" t="inlineStr"/>
-      <c r="BL91" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="BD92" s="31" t="n">
-        <v>66</v>
-      </c>
-      <c r="BE92" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF92" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch1</t>
-        </is>
-      </c>
-      <c r="BG92" s="31" t="inlineStr">
-        <is>
-          <t>bme680</t>
-        </is>
-      </c>
-      <c r="BH92" s="31" t="inlineStr">
-        <is>
-          <t>BME680</t>
-        </is>
-      </c>
-      <c r="BI92" s="31" t="inlineStr">
-        <is>
-          <t>0x76</t>
-        </is>
-      </c>
-      <c r="BJ92" s="31" t="inlineStr">
-        <is>
-          <t>0x76, 0x77</t>
-        </is>
-      </c>
-      <c r="BK92" s="31" t="inlineStr"/>
-      <c r="BL92" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="BD93" s="30" t="n">
-        <v>67</v>
-      </c>
-      <c r="BE93" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF93" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch2</t>
-        </is>
-      </c>
-      <c r="BG93" s="30" t="inlineStr">
-        <is>
-          <t>vl53l0x</t>
-        </is>
-      </c>
-      <c r="BH93" s="30" t="inlineStr">
-        <is>
-          <t>VL53L0X</t>
-        </is>
-      </c>
-      <c r="BI93" s="30" t="inlineStr">
-        <is>
-          <t>0x29</t>
-        </is>
-      </c>
-      <c r="BJ93" s="30" t="inlineStr">
-        <is>
-          <t>0x29</t>
-        </is>
-      </c>
-      <c r="BK93" s="30" t="inlineStr"/>
-      <c r="BL93" s="30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="BD94" s="30" t="n">
-        <v>68</v>
-      </c>
-      <c r="BE94" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF94" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch2</t>
-        </is>
-      </c>
-      <c r="BG94" s="30" t="inlineStr">
-        <is>
-          <t>am2301b</t>
-        </is>
-      </c>
-      <c r="BH94" s="30" t="inlineStr">
-        <is>
-          <t>AM2301B</t>
-        </is>
-      </c>
-      <c r="BI94" s="30" t="inlineStr">
-        <is>
-          <t>0x38</t>
-        </is>
-      </c>
-      <c r="BJ94" s="30" t="inlineStr">
-        <is>
-          <t>0x38</t>
-        </is>
-      </c>
-      <c r="BK94" s="30" t="inlineStr"/>
-      <c r="BL94" s="30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="BD95" s="30" t="n">
-        <v>69</v>
-      </c>
-      <c r="BE95" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF95" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch2</t>
-        </is>
-      </c>
-      <c r="BG95" s="30" t="inlineStr">
-        <is>
-          <t>si7021</t>
-        </is>
-      </c>
-      <c r="BH95" s="30" t="inlineStr">
-        <is>
-          <t>Si7021</t>
-        </is>
-      </c>
-      <c r="BI95" s="30" t="inlineStr">
-        <is>
-          <t>0x40</t>
-        </is>
-      </c>
-      <c r="BJ95" s="30" t="inlineStr">
-        <is>
-          <t>0x40</t>
-        </is>
-      </c>
-      <c r="BK95" s="30" t="inlineStr"/>
-      <c r="BL95" s="30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="BD96" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="BE96" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF96" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch2</t>
-        </is>
-      </c>
-      <c r="BG96" s="30" t="inlineStr">
-        <is>
-          <t>ina228</t>
-        </is>
-      </c>
-      <c r="BH96" s="30" t="inlineStr">
-        <is>
-          <t>INA228</t>
-        </is>
-      </c>
-      <c r="BI96" s="30" t="inlineStr">
-        <is>
-          <t>0x41</t>
-        </is>
-      </c>
-      <c r="BJ96" s="30" t="inlineStr">
-        <is>
-          <t>0x40, 0x41, 0x44, 0x45</t>
-        </is>
-      </c>
-      <c r="BK96" s="30" t="inlineStr"/>
-      <c r="BL96" s="30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="BD97" s="30" t="n">
-        <v>71</v>
-      </c>
-      <c r="BE97" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF97" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch2</t>
-        </is>
-      </c>
-      <c r="BG97" s="30" t="inlineStr">
-        <is>
-          <t>sht40</t>
-        </is>
-      </c>
-      <c r="BH97" s="30" t="inlineStr">
-        <is>
-          <t>SHT40</t>
-        </is>
-      </c>
-      <c r="BI97" s="30" t="inlineStr">
-        <is>
-          <t>0x44</t>
-        </is>
-      </c>
-      <c r="BJ97" s="30" t="inlineStr">
-        <is>
-          <t>0x44</t>
-        </is>
-      </c>
-      <c r="BK97" s="30" t="inlineStr"/>
-      <c r="BL97" s="30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="BD98" s="30" t="n">
-        <v>72</v>
-      </c>
-      <c r="BE98" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF98" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch2</t>
-        </is>
-      </c>
-      <c r="BG98" s="30" t="inlineStr">
-        <is>
-          <t>ina237</t>
-        </is>
-      </c>
-      <c r="BH98" s="30" t="inlineStr">
-        <is>
-          <t>INA237</t>
-        </is>
-      </c>
-      <c r="BI98" s="30" t="inlineStr">
-        <is>
-          <t>0x45</t>
-        </is>
-      </c>
-      <c r="BJ98" s="30" t="inlineStr">
-        <is>
-          <t>0x40, 0x41, 0x44, 0x45</t>
-        </is>
-      </c>
-      <c r="BK98" s="30" t="inlineStr"/>
-      <c r="BL98" s="30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="BD99" s="30" t="n">
-        <v>73</v>
-      </c>
-      <c r="BE99" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF99" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch2</t>
-        </is>
-      </c>
-      <c r="BG99" s="30" t="inlineStr">
-        <is>
-          <t>lps35hw</t>
-        </is>
-      </c>
-      <c r="BH99" s="30" t="inlineStr">
-        <is>
-          <t>LPS35HW</t>
-        </is>
-      </c>
-      <c r="BI99" s="30" t="inlineStr">
-        <is>
-          <t>0x5C</t>
-        </is>
-      </c>
-      <c r="BJ99" s="30" t="inlineStr">
-        <is>
-          <t>0x5C, 0x5D</t>
-        </is>
-      </c>
-      <c r="BK99" s="30" t="inlineStr"/>
-      <c r="BL99" s="30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="BD100" s="30" t="n">
-        <v>74</v>
-      </c>
-      <c r="BE100" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF100" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch2</t>
-        </is>
-      </c>
-      <c r="BG100" s="30" t="inlineStr">
-        <is>
-          <t>sen55</t>
-        </is>
-      </c>
-      <c r="BH100" s="30" t="inlineStr">
-        <is>
-          <t>SEN55</t>
-        </is>
-      </c>
-      <c r="BI100" s="30" t="inlineStr">
-        <is>
-          <t>0x69</t>
-        </is>
-      </c>
-      <c r="BJ100" s="30" t="inlineStr">
-        <is>
-          <t>0x69</t>
-        </is>
-      </c>
-      <c r="BK100" s="30" t="inlineStr"/>
-      <c r="BL100" s="30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="BD101" s="30" t="n">
-        <v>75</v>
-      </c>
-      <c r="BE101" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF101" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch2</t>
-        </is>
-      </c>
-      <c r="BG101" s="30" t="inlineStr">
-        <is>
-          <t>bme688</t>
-        </is>
-      </c>
-      <c r="BH101" s="30" t="inlineStr">
-        <is>
-          <t>BME688</t>
-        </is>
-      </c>
-      <c r="BI101" s="30" t="inlineStr">
-        <is>
-          <t>0x76</t>
-        </is>
-      </c>
-      <c r="BJ101" s="30" t="inlineStr">
-        <is>
-          <t>0x76, 0x77</t>
-        </is>
-      </c>
-      <c r="BK101" s="30" t="inlineStr"/>
-      <c r="BL101" s="30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="BD102" s="31" t="n">
-        <v>76</v>
-      </c>
-      <c r="BE102" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF102" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch3</t>
-        </is>
-      </c>
-      <c r="BG102" s="31" t="inlineStr">
-        <is>
-          <t>vl53l1x</t>
-        </is>
-      </c>
-      <c r="BH102" s="31" t="inlineStr">
-        <is>
-          <t>VL53L1X</t>
-        </is>
-      </c>
-      <c r="BI102" s="31" t="inlineStr">
-        <is>
-          <t>0x29</t>
-        </is>
-      </c>
-      <c r="BJ102" s="31" t="inlineStr">
-        <is>
-          <t>0x29</t>
-        </is>
-      </c>
-      <c r="BK102" s="31" t="inlineStr"/>
-      <c r="BL102" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="BD103" s="31" t="n">
-        <v>77</v>
-      </c>
-      <c r="BE103" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF103" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch3</t>
-        </is>
-      </c>
-      <c r="BG103" s="31" t="inlineStr">
-        <is>
-          <t>am2315c</t>
-        </is>
-      </c>
-      <c r="BH103" s="31" t="inlineStr">
-        <is>
-          <t>AM2315C</t>
-        </is>
-      </c>
-      <c r="BI103" s="31" t="inlineStr">
-        <is>
-          <t>0x38</t>
-        </is>
-      </c>
-      <c r="BJ103" s="31" t="inlineStr">
-        <is>
-          <t>0x38</t>
-        </is>
-      </c>
-      <c r="BK103" s="31" t="inlineStr"/>
-      <c r="BL103" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="BD104" s="31" t="n">
-        <v>78</v>
-      </c>
-      <c r="BE104" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF104" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch3</t>
-        </is>
-      </c>
-      <c r="BG104" s="31" t="inlineStr">
-        <is>
-          <t>ms8607</t>
-        </is>
-      </c>
-      <c r="BH104" s="31" t="inlineStr">
-        <is>
-          <t>MS8607</t>
-        </is>
-      </c>
-      <c r="BI104" s="31" t="inlineStr">
-        <is>
-          <t>0x40</t>
-        </is>
-      </c>
-      <c r="BJ104" s="31" t="inlineStr">
-        <is>
-          <t>0x40, 0x76</t>
-        </is>
-      </c>
-      <c r="BK104" s="31" t="inlineStr"/>
-      <c r="BL104" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="BD105" s="31" t="n">
-        <v>79</v>
-      </c>
-      <c r="BE105" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF105" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch3</t>
-        </is>
-      </c>
-      <c r="BG105" s="31" t="inlineStr">
-        <is>
-          <t>ina238</t>
-        </is>
-      </c>
-      <c r="BH105" s="31" t="inlineStr">
-        <is>
-          <t>INA238</t>
-        </is>
-      </c>
-      <c r="BI105" s="31" t="inlineStr">
-        <is>
-          <t>0x41</t>
-        </is>
-      </c>
-      <c r="BJ105" s="31" t="inlineStr">
-        <is>
-          <t>0x40, 0x41, 0x44, 0x45</t>
-        </is>
-      </c>
-      <c r="BK105" s="31" t="inlineStr"/>
-      <c r="BL105" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="BD106" s="31" t="n">
-        <v>80</v>
-      </c>
-      <c r="BE106" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF106" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch3</t>
-        </is>
-      </c>
-      <c r="BG106" s="31" t="inlineStr">
-        <is>
-          <t>sht41</t>
-        </is>
-      </c>
-      <c r="BH106" s="31" t="inlineStr">
-        <is>
-          <t>SHT41</t>
-        </is>
-      </c>
-      <c r="BI106" s="31" t="inlineStr">
-        <is>
-          <t>0x44</t>
-        </is>
-      </c>
-      <c r="BJ106" s="31" t="inlineStr">
-        <is>
-          <t>0x44</t>
-        </is>
-      </c>
-      <c r="BK106" s="31" t="inlineStr"/>
-      <c r="BL106" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="BD107" s="31" t="n">
-        <v>81</v>
-      </c>
-      <c r="BE107" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF107" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch3</t>
-        </is>
-      </c>
-      <c r="BG107" s="31" t="inlineStr">
-        <is>
-          <t>ina260</t>
-        </is>
-      </c>
-      <c r="BH107" s="31" t="inlineStr">
-        <is>
-          <t>INA260</t>
-        </is>
-      </c>
-      <c r="BI107" s="31" t="inlineStr">
-        <is>
-          <t>0x45</t>
-        </is>
-      </c>
-      <c r="BJ107" s="31" t="inlineStr">
-        <is>
-          <t>0x40, 0x41, 0x44, 0x45</t>
-        </is>
-      </c>
-      <c r="BK107" s="31" t="inlineStr"/>
-      <c r="BL107" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="BD108" s="31" t="n">
-        <v>82</v>
-      </c>
-      <c r="BE108" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF108" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch3</t>
-        </is>
-      </c>
-      <c r="BG108" s="31" t="inlineStr">
-        <is>
-          <t>sen5x</t>
-        </is>
-      </c>
-      <c r="BH108" s="31" t="inlineStr">
-        <is>
-          <t>SEN5x</t>
-        </is>
-      </c>
-      <c r="BI108" s="31" t="inlineStr">
-        <is>
-          <t>0x69</t>
-        </is>
-      </c>
-      <c r="BJ108" s="31" t="inlineStr">
-        <is>
-          <t>0x69</t>
-        </is>
-      </c>
-      <c r="BK108" s="31" t="inlineStr"/>
-      <c r="BL108" s="31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="BD109" s="31" t="n">
-        <v>83</v>
-      </c>
-      <c r="BE109" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF109" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch3</t>
-        </is>
-      </c>
-      <c r="BG109" s="31" t="inlineStr">
-        <is>
-          <t>bmp280</t>
-        </is>
-      </c>
-      <c r="BH109" s="31" t="inlineStr">
-        <is>
-          <t>BMP280</t>
-        </is>
-      </c>
-      <c r="BI109" s="31" t="inlineStr">
-        <is>
-          <t>0x76</t>
-        </is>
-      </c>
-      <c r="BJ109" s="31" t="inlineStr">
-        <is>
-          <t>0x76, 0x77</t>
-        </is>
-      </c>
-      <c r="BK109" s="31" t="inlineStr"/>
-      <c r="BL109" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="BD110" s="30" t="n">
-        <v>84</v>
-      </c>
-      <c r="BE110" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF110" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch4</t>
-        </is>
-      </c>
-      <c r="BG110" s="30" t="inlineStr">
-        <is>
-          <t>vl53l4cd</t>
-        </is>
-      </c>
-      <c r="BH110" s="30" t="inlineStr">
-        <is>
-          <t>VL53L4CD</t>
-        </is>
-      </c>
-      <c r="BI110" s="30" t="inlineStr">
-        <is>
-          <t>0x29</t>
-        </is>
-      </c>
-      <c r="BJ110" s="30" t="inlineStr">
-        <is>
-          <t>0x29</t>
-        </is>
-      </c>
-      <c r="BK110" s="30" t="inlineStr"/>
-      <c r="BL110" s="30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="BD111" s="30" t="n">
-        <v>85</v>
-      </c>
-      <c r="BE111" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF111" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch4</t>
-        </is>
-      </c>
-      <c r="BG111" s="30" t="inlineStr">
-        <is>
-          <t>dht20</t>
-        </is>
-      </c>
-      <c r="BH111" s="30" t="inlineStr">
-        <is>
-          <t>DHT20</t>
-        </is>
-      </c>
-      <c r="BI111" s="30" t="inlineStr">
-        <is>
-          <t>0x38</t>
-        </is>
-      </c>
-      <c r="BJ111" s="30" t="inlineStr">
-        <is>
-          <t>0x38</t>
-        </is>
-      </c>
-      <c r="BK111" s="30" t="inlineStr"/>
-      <c r="BL111" s="30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="BD112" s="30" t="n">
-        <v>86</v>
-      </c>
-      <c r="BE112" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF112" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch4</t>
-        </is>
-      </c>
-      <c r="BG112" s="30" t="inlineStr">
-        <is>
-          <t>sht45</t>
-        </is>
-      </c>
-      <c r="BH112" s="30" t="inlineStr">
-        <is>
-          <t>SHT45</t>
-        </is>
-      </c>
-      <c r="BI112" s="30" t="inlineStr">
-        <is>
-          <t>0x44</t>
-        </is>
-      </c>
-      <c r="BJ112" s="30" t="inlineStr">
-        <is>
-          <t>0x44</t>
-        </is>
-      </c>
-      <c r="BK112" s="30" t="inlineStr"/>
-      <c r="BL112" s="30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="BD113" s="30" t="n">
-        <v>87</v>
-      </c>
-      <c r="BE113" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF113" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch4</t>
-        </is>
-      </c>
-      <c r="BG113" s="30" t="inlineStr">
-        <is>
-          <t>bmp388</t>
-        </is>
-      </c>
-      <c r="BH113" s="30" t="inlineStr">
-        <is>
-          <t>BMP388</t>
-        </is>
-      </c>
-      <c r="BI113" s="30" t="inlineStr">
-        <is>
-          <t>0x76</t>
-        </is>
-      </c>
-      <c r="BJ113" s="30" t="inlineStr">
-        <is>
-          <t>0x76, 0x77</t>
-        </is>
-      </c>
-      <c r="BK113" s="30" t="inlineStr"/>
-      <c r="BL113" s="30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="BD114" s="31" t="n">
-        <v>88</v>
-      </c>
-      <c r="BE114" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF114" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch5</t>
-        </is>
-      </c>
-      <c r="BG114" s="31" t="inlineStr">
-        <is>
-          <t>vl53l4cx</t>
-        </is>
-      </c>
-      <c r="BH114" s="31" t="inlineStr">
-        <is>
-          <t>VL53L4CX</t>
-        </is>
-      </c>
-      <c r="BI114" s="31" t="inlineStr">
-        <is>
-          <t>0x29</t>
-        </is>
-      </c>
-      <c r="BJ114" s="31" t="inlineStr">
-        <is>
-          <t>0x29</t>
-        </is>
-      </c>
-      <c r="BK114" s="31" t="inlineStr"/>
-      <c r="BL114" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="BD115" s="31" t="n">
-        <v>89</v>
-      </c>
-      <c r="BE115" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF115" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch5</t>
-        </is>
-      </c>
-      <c r="BG115" s="31" t="inlineStr">
-        <is>
-          <t>bmp390</t>
-        </is>
-      </c>
-      <c r="BH115" s="31" t="inlineStr">
-        <is>
-          <t>BMP390</t>
-        </is>
-      </c>
-      <c r="BI115" s="31" t="inlineStr">
-        <is>
-          <t>0x76</t>
-        </is>
-      </c>
-      <c r="BJ115" s="31" t="inlineStr">
-        <is>
-          <t>0x76, 0x77</t>
-        </is>
-      </c>
-      <c r="BK115" s="31" t="inlineStr"/>
-      <c r="BL115" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="BD116" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="BE116" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF116" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch6</t>
-        </is>
-      </c>
-      <c r="BG116" s="30" t="inlineStr">
-        <is>
-          <t>vl6180x</t>
-        </is>
-      </c>
-      <c r="BH116" s="30" t="inlineStr">
-        <is>
-          <t>VL6180X</t>
-        </is>
-      </c>
-      <c r="BI116" s="30" t="inlineStr">
-        <is>
-          <t>0x29</t>
-        </is>
-      </c>
-      <c r="BJ116" s="30" t="inlineStr">
-        <is>
-          <t>0x29</t>
-        </is>
-      </c>
-      <c r="BK116" s="30" t="inlineStr"/>
-      <c r="BL116" s="30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="BD117" s="30" t="n">
-        <v>91</v>
-      </c>
-      <c r="BE117" s="30" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF117" s="30" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch6</t>
-        </is>
-      </c>
-      <c r="BG117" s="30" t="inlineStr">
-        <is>
-          <t>dps310</t>
-        </is>
-      </c>
-      <c r="BH117" s="30" t="inlineStr">
-        <is>
-          <t>DPS310</t>
-        </is>
-      </c>
-      <c r="BI117" s="30" t="inlineStr">
-        <is>
-          <t>0x76</t>
-        </is>
-      </c>
-      <c r="BJ117" s="30" t="inlineStr">
-        <is>
-          <t>0x76, 0x77</t>
-        </is>
-      </c>
-      <c r="BK117" s="30" t="inlineStr"/>
-      <c r="BL117" s="30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="BD118" s="31" t="n">
-        <v>92</v>
-      </c>
-      <c r="BE118" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF118" s="31" t="inlineStr">
-        <is>
-          <t>8ch_mux_ch7</t>
-        </is>
-      </c>
-      <c r="BG118" s="31" t="inlineStr">
-        <is>
-          <t>spa06_003</t>
-        </is>
-      </c>
-      <c r="BH118" s="31" t="inlineStr">
-        <is>
-          <t>SPA06-003</t>
-        </is>
-      </c>
-      <c r="BI118" s="31" t="inlineStr">
-        <is>
-          <t>0x76</t>
-        </is>
-      </c>
-      <c r="BJ118" s="31" t="inlineStr">
-        <is>
-          <t>0x76, 0x77</t>
-        </is>
-      </c>
-      <c r="BK118" s="31" t="inlineStr"/>
-      <c r="BL118" s="31" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="BN118" s="30" t="inlineStr">
+        <is>
+          <t>NON-DEFAULT</t>
         </is>
       </c>
     </row>
@@ -18925,22 +19610,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="32" t="inlineStr">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="B1" s="32" t="inlineStr">
+      <c r="B1" s="33" t="inlineStr">
         <is>
           <t>Mux?</t>
         </is>
       </c>
-      <c r="C1" s="32" t="inlineStr">
+      <c r="C1" s="33" t="inlineStr">
         <is>
           <t># Components</t>
         </is>
       </c>
-      <c r="D1" s="32" t="inlineStr">
+      <c r="D1" s="33" t="inlineStr">
         <is>
           <t>Components</t>
         </is>
@@ -18952,8 +19637,8 @@
           <t>0x0A</t>
         </is>
       </c>
-      <c r="B2" s="33" t="inlineStr"/>
-      <c r="C2" s="33" t="n">
+      <c r="B2" s="34" t="inlineStr"/>
+      <c r="C2" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -18968,8 +19653,8 @@
           <t>0x0B</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr"/>
-      <c r="C3" s="33" t="n">
+      <c r="B3" s="34" t="inlineStr"/>
+      <c r="C3" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -18984,8 +19669,8 @@
           <t>0x10</t>
         </is>
       </c>
-      <c r="B4" s="33" t="inlineStr"/>
-      <c r="C4" s="33" t="n">
+      <c r="B4" s="34" t="inlineStr"/>
+      <c r="C4" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -19000,8 +19685,8 @@
           <t>0x12</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr"/>
-      <c r="C5" s="33" t="n">
+      <c r="B5" s="34" t="inlineStr"/>
+      <c r="C5" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -19016,8 +19701,8 @@
           <t>0x13</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr"/>
-      <c r="C6" s="33" t="n">
+      <c r="B6" s="34" t="inlineStr"/>
+      <c r="C6" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -19027,13 +19712,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>0x18</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr"/>
-      <c r="C7" s="35" t="n">
+      <c r="B7" s="34" t="inlineStr"/>
+      <c r="C7" s="36" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -19048,8 +19733,8 @@
           <t>0x19</t>
         </is>
       </c>
-      <c r="B8" s="33" t="inlineStr"/>
-      <c r="C8" s="33" t="n">
+      <c r="B8" s="34" t="inlineStr"/>
+      <c r="C8" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -19064,8 +19749,8 @@
           <t>0x1A</t>
         </is>
       </c>
-      <c r="B9" s="33" t="inlineStr"/>
-      <c r="C9" s="33" t="n">
+      <c r="B9" s="34" t="inlineStr"/>
+      <c r="C9" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -19080,8 +19765,8 @@
           <t>0x1B</t>
         </is>
       </c>
-      <c r="B10" s="33" t="inlineStr"/>
-      <c r="C10" s="33" t="n">
+      <c r="B10" s="34" t="inlineStr"/>
+      <c r="C10" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -19096,8 +19781,8 @@
           <t>0x1C</t>
         </is>
       </c>
-      <c r="B11" s="33" t="inlineStr"/>
-      <c r="C11" s="33" t="n">
+      <c r="B11" s="34" t="inlineStr"/>
+      <c r="C11" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -19112,8 +19797,8 @@
           <t>0x1D</t>
         </is>
       </c>
-      <c r="B12" s="33" t="inlineStr"/>
-      <c r="C12" s="33" t="n">
+      <c r="B12" s="34" t="inlineStr"/>
+      <c r="C12" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -19128,8 +19813,8 @@
           <t>0x1E</t>
         </is>
       </c>
-      <c r="B13" s="33" t="inlineStr"/>
-      <c r="C13" s="33" t="n">
+      <c r="B13" s="34" t="inlineStr"/>
+      <c r="C13" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -19144,8 +19829,8 @@
           <t>0x1F</t>
         </is>
       </c>
-      <c r="B14" s="33" t="inlineStr"/>
-      <c r="C14" s="33" t="n">
+      <c r="B14" s="34" t="inlineStr"/>
+      <c r="C14" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -19160,8 +19845,8 @@
           <t>0x23</t>
         </is>
       </c>
-      <c r="B15" s="33" t="inlineStr"/>
-      <c r="C15" s="33" t="n">
+      <c r="B15" s="34" t="inlineStr"/>
+      <c r="C15" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -19176,8 +19861,8 @@
           <t>0x28</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr"/>
-      <c r="C16" s="33" t="n">
+      <c r="B16" s="34" t="inlineStr"/>
+      <c r="C16" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -19187,34 +19872,34 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>0x29</t>
         </is>
       </c>
-      <c r="B17" s="33" t="inlineStr"/>
-      <c r="C17" s="35" t="n">
+      <c r="B17" s="34" t="inlineStr"/>
+      <c r="C17" s="36" t="n">
         <v>9</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>pct2075 (PCT2075), ltr303 (LTR-303), ltr329 (LTR-329), tsl2591 (TSL2591), vl53l0x (VL53L0X), vl53l1x (VL53L1X), vl53l4cd (VL53L4CD), vl53l4cx (VL53L4CX), vl6180x (VL6180X)</t>
+          <t>ltr303 (LTR-303), ltr329 (LTR-329), tsl2591 (TSL2591), vl53l0x (VL53L0X), vl53l1x (VL53L1X), vl53l4cd (VL53L4CD), vl53l4cx (VL53L4CX), vl6180x (VL6180X), pct2075 (PCT2075)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>0x2A</t>
         </is>
       </c>
-      <c r="B18" s="33" t="inlineStr"/>
-      <c r="C18" s="35" t="n">
+      <c r="B18" s="34" t="inlineStr"/>
+      <c r="C18" s="36" t="n">
         <v>2</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>pct2075 (PCT2075), nau7802 (NAU7802)</t>
+          <t>nau7802 (NAU7802), pct2075 (PCT2075)</t>
         </is>
       </c>
     </row>
@@ -19224,8 +19909,8 @@
           <t>0x2B</t>
         </is>
       </c>
-      <c r="B19" s="33" t="inlineStr"/>
-      <c r="C19" s="33" t="n">
+      <c r="B19" s="34" t="inlineStr"/>
+      <c r="C19" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -19235,18 +19920,18 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>0x2C</t>
         </is>
       </c>
-      <c r="B20" s="33" t="inlineStr"/>
-      <c r="C20" s="35" t="n">
+      <c r="B20" s="34" t="inlineStr"/>
+      <c r="C20" s="36" t="n">
         <v>2</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>pct2075 (PCT2075), qmc5883p (QMC5883P)</t>
+          <t>qmc5883p (QMC5883P), pct2075 (PCT2075)</t>
         </is>
       </c>
     </row>
@@ -19256,8 +19941,8 @@
           <t>0x2D</t>
         </is>
       </c>
-      <c r="B21" s="33" t="inlineStr"/>
-      <c r="C21" s="33" t="n">
+      <c r="B21" s="34" t="inlineStr"/>
+      <c r="C21" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -19272,8 +19957,8 @@
           <t>0x2E</t>
         </is>
       </c>
-      <c r="B22" s="33" t="inlineStr"/>
-      <c r="C22" s="33" t="n">
+      <c r="B22" s="34" t="inlineStr"/>
+      <c r="C22" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -19288,8 +19973,8 @@
           <t>0x2F</t>
         </is>
       </c>
-      <c r="B23" s="33" t="inlineStr"/>
-      <c r="C23" s="33" t="n">
+      <c r="B23" s="34" t="inlineStr"/>
+      <c r="C23" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -19304,8 +19989,8 @@
           <t>0x35</t>
         </is>
       </c>
-      <c r="B24" s="33" t="inlineStr"/>
-      <c r="C24" s="33" t="n">
+      <c r="B24" s="34" t="inlineStr"/>
+      <c r="C24" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -19315,45 +20000,45 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>0x36</t>
         </is>
       </c>
-      <c r="B25" s="33" t="inlineStr"/>
-      <c r="C25" s="35" t="n">
+      <c r="B25" s="34" t="inlineStr"/>
+      <c r="C25" s="36" t="n">
         <v>5</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>pct2075 (PCT2075), as5600 (AS5600 Magnetic Angle), max17048 (MAX17048/MAX17049), rotary_encoder (STEMMA QT Rotary Encoder), stemma_soil (STEMMA Soil Sensor)</t>
+          <t>as5600 (AS5600 Magnetic Angle), max17048 (MAX17048/MAX17049), rotary_encoder (STEMMA QT Rotary Encoder), stemma_soil (STEMMA Soil Sensor), pct2075 (PCT2075)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>0x37</t>
         </is>
       </c>
-      <c r="B26" s="33" t="inlineStr"/>
-      <c r="C26" s="35" t="n">
+      <c r="B26" s="34" t="inlineStr"/>
+      <c r="C26" s="36" t="n">
         <v>3</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>pct2075 (PCT2075), rotary_encoder (STEMMA QT Rotary Encoder), stemma_soil (STEMMA Soil Sensor)</t>
+          <t>rotary_encoder (STEMMA QT Rotary Encoder), stemma_soil (STEMMA Soil Sensor), pct2075 (PCT2075)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="34" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>0x38</t>
         </is>
       </c>
-      <c r="B27" s="33" t="inlineStr"/>
-      <c r="C27" s="35" t="n">
+      <c r="B27" s="34" t="inlineStr"/>
+      <c r="C27" s="36" t="n">
         <v>7</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -19363,13 +20048,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="34" t="inlineStr">
+      <c r="A28" s="35" t="inlineStr">
         <is>
           <t>0x39</t>
         </is>
       </c>
-      <c r="B28" s="33" t="inlineStr"/>
-      <c r="C28" s="35" t="n">
+      <c r="B28" s="34" t="inlineStr"/>
+      <c r="C28" s="36" t="n">
         <v>3</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -19379,13 +20064,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="34" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>0x3A</t>
         </is>
       </c>
-      <c r="B29" s="33" t="inlineStr"/>
-      <c r="C29" s="35" t="n">
+      <c r="B29" s="34" t="inlineStr"/>
+      <c r="C29" s="36" t="n">
         <v>4</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -19395,13 +20080,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="34" t="inlineStr">
+      <c r="A30" s="35" t="inlineStr">
         <is>
           <t>0x3B</t>
         </is>
       </c>
-      <c r="B30" s="33" t="inlineStr"/>
-      <c r="C30" s="35" t="n">
+      <c r="B30" s="34" t="inlineStr"/>
+      <c r="C30" s="36" t="n">
         <v>4</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -19416,8 +20101,8 @@
           <t>0x3C</t>
         </is>
       </c>
-      <c r="B31" s="33" t="inlineStr"/>
-      <c r="C31" s="33" t="n">
+      <c r="B31" s="34" t="inlineStr"/>
+      <c r="C31" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -19432,8 +20117,8 @@
           <t>0x3D</t>
         </is>
       </c>
-      <c r="B32" s="33" t="inlineStr"/>
-      <c r="C32" s="33" t="n">
+      <c r="B32" s="34" t="inlineStr"/>
+      <c r="C32" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -19443,13 +20128,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="34" t="inlineStr">
+      <c r="A33" s="35" t="inlineStr">
         <is>
           <t>0x40</t>
         </is>
       </c>
-      <c r="B33" s="33" t="inlineStr"/>
-      <c r="C33" s="35" t="n">
+      <c r="B33" s="34" t="inlineStr"/>
+      <c r="C33" s="36" t="n">
         <v>10</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -19459,13 +20144,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="34" t="inlineStr">
+      <c r="A34" s="35" t="inlineStr">
         <is>
           <t>0x41</t>
         </is>
       </c>
-      <c r="B34" s="33" t="inlineStr"/>
-      <c r="C34" s="35" t="n">
+      <c r="B34" s="34" t="inlineStr"/>
+      <c r="C34" s="36" t="n">
         <v>6</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -19475,13 +20160,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="34" t="inlineStr">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>0x44</t>
         </is>
       </c>
-      <c r="B35" s="33" t="inlineStr"/>
-      <c r="C35" s="35" t="n">
+      <c r="B35" s="34" t="inlineStr"/>
+      <c r="C35" s="36" t="n">
         <v>12</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -19491,13 +20176,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="34" t="inlineStr">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>0x45</t>
         </is>
       </c>
-      <c r="B36" s="33" t="inlineStr"/>
-      <c r="C36" s="35" t="n">
+      <c r="B36" s="34" t="inlineStr"/>
+      <c r="C36" s="36" t="n">
         <v>7</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -19507,13 +20192,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="34" t="inlineStr">
+      <c r="A37" s="35" t="inlineStr">
         <is>
           <t>0x46</t>
         </is>
       </c>
-      <c r="B37" s="33" t="inlineStr"/>
-      <c r="C37" s="35" t="n">
+      <c r="B37" s="34" t="inlineStr"/>
+      <c r="C37" s="36" t="n">
         <v>4</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -19523,13 +20208,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="34" t="inlineStr">
+      <c r="A38" s="35" t="inlineStr">
         <is>
           <t>0x47</t>
         </is>
       </c>
-      <c r="B38" s="33" t="inlineStr"/>
-      <c r="C38" s="35" t="n">
+      <c r="B38" s="34" t="inlineStr"/>
+      <c r="C38" s="36" t="n">
         <v>4</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -19539,13 +20224,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="34" t="inlineStr">
+      <c r="A39" s="35" t="inlineStr">
         <is>
           <t>0x48</t>
         </is>
       </c>
-      <c r="B39" s="33" t="inlineStr"/>
-      <c r="C39" s="35" t="n">
+      <c r="B39" s="34" t="inlineStr"/>
+      <c r="C39" s="36" t="n">
         <v>5</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -19555,29 +20240,29 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="34" t="inlineStr">
+      <c r="A40" s="35" t="inlineStr">
         <is>
           <t>0x49</t>
         </is>
       </c>
-      <c r="B40" s="33" t="inlineStr"/>
-      <c r="C40" s="35" t="n">
+      <c r="B40" s="34" t="inlineStr"/>
+      <c r="C40" s="36" t="n">
         <v>5</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>pct2075 (PCT2075), tsl2591 (TSL2591), adt7410 (ADT7410), tmp117 (TMP117), tmp119 (TMP119)</t>
+          <t>tsl2591 (TSL2591), pct2075 (PCT2075), adt7410 (ADT7410), tmp117 (TMP117), tmp119 (TMP119)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="34" t="inlineStr">
+      <c r="A41" s="35" t="inlineStr">
         <is>
           <t>0x4A</t>
         </is>
       </c>
-      <c r="B41" s="33" t="inlineStr"/>
-      <c r="C41" s="35" t="n">
+      <c r="B41" s="34" t="inlineStr"/>
+      <c r="C41" s="36" t="n">
         <v>5</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -19587,13 +20272,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="34" t="inlineStr">
+      <c r="A42" s="35" t="inlineStr">
         <is>
           <t>0x4B</t>
         </is>
       </c>
-      <c r="B42" s="33" t="inlineStr"/>
-      <c r="C42" s="35" t="n">
+      <c r="B42" s="34" t="inlineStr"/>
+      <c r="C42" s="36" t="n">
         <v>5</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -19608,8 +20293,8 @@
           <t>0x4C</t>
         </is>
       </c>
-      <c r="B43" s="33" t="inlineStr"/>
-      <c r="C43" s="33" t="n">
+      <c r="B43" s="34" t="inlineStr"/>
+      <c r="C43" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -19624,8 +20309,8 @@
           <t>0x4D</t>
         </is>
       </c>
-      <c r="B44" s="33" t="inlineStr"/>
-      <c r="C44" s="33" t="n">
+      <c r="B44" s="34" t="inlineStr"/>
+      <c r="C44" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -19640,8 +20325,8 @@
           <t>0x4E</t>
         </is>
       </c>
-      <c r="B45" s="33" t="inlineStr"/>
-      <c r="C45" s="33" t="n">
+      <c r="B45" s="34" t="inlineStr"/>
+      <c r="C45" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -19656,8 +20341,8 @@
           <t>0x4F</t>
         </is>
       </c>
-      <c r="B46" s="33" t="inlineStr"/>
-      <c r="C46" s="33" t="n">
+      <c r="B46" s="34" t="inlineStr"/>
+      <c r="C46" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -19672,8 +20357,8 @@
           <t>0x51</t>
         </is>
       </c>
-      <c r="B47" s="33" t="inlineStr"/>
-      <c r="C47" s="33" t="n">
+      <c r="B47" s="34" t="inlineStr"/>
+      <c r="C47" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -19683,13 +20368,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="34" t="inlineStr">
+      <c r="A48" s="35" t="inlineStr">
         <is>
           <t>0x52</t>
         </is>
       </c>
-      <c r="B48" s="33" t="inlineStr"/>
-      <c r="C48" s="35" t="n">
+      <c r="B48" s="34" t="inlineStr"/>
+      <c r="C48" s="36" t="n">
         <v>3</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -19699,13 +20384,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="34" t="inlineStr">
+      <c r="A49" s="35" t="inlineStr">
         <is>
           <t>0x53</t>
         </is>
       </c>
-      <c r="B49" s="33" t="inlineStr"/>
-      <c r="C49" s="35" t="n">
+      <c r="B49" s="34" t="inlineStr"/>
+      <c r="C49" s="36" t="n">
         <v>3</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -19720,8 +20405,8 @@
           <t>0x58</t>
         </is>
       </c>
-      <c r="B50" s="33" t="inlineStr"/>
-      <c r="C50" s="33" t="n">
+      <c r="B50" s="34" t="inlineStr"/>
+      <c r="C50" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -19731,13 +20416,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="34" t="inlineStr">
+      <c r="A51" s="35" t="inlineStr">
         <is>
           <t>0x59</t>
         </is>
       </c>
-      <c r="B51" s="33" t="inlineStr"/>
-      <c r="C51" s="35" t="n">
+      <c r="B51" s="34" t="inlineStr"/>
+      <c r="C51" s="36" t="n">
         <v>2</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -19747,34 +20432,34 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="34" t="inlineStr">
+      <c r="A52" s="35" t="inlineStr">
         <is>
           <t>0x5C</t>
         </is>
       </c>
-      <c r="B52" s="33" t="inlineStr"/>
-      <c r="C52" s="35" t="n">
+      <c r="B52" s="34" t="inlineStr"/>
+      <c r="C52" s="36" t="n">
         <v>6</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>bh1750 (BH1750), lps22hb (LPS22HB), lps25hb (LPS25HB), lps28dfw (LPS28DFW), lps33hw (LPS33HW), lps35hw (LPS35HW)</t>
+          <t>bh1750 (BH1750), lps28dfw (LPS28DFW), lps22hb (LPS22HB), lps25hb (LPS25HB), lps33hw (LPS33HW), lps35hw (LPS35HW)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="34" t="inlineStr">
+      <c r="A53" s="35" t="inlineStr">
         <is>
           <t>0x5D</t>
         </is>
       </c>
-      <c r="B53" s="33" t="inlineStr"/>
-      <c r="C53" s="35" t="n">
+      <c r="B53" s="34" t="inlineStr"/>
+      <c r="C53" s="36" t="n">
         <v>5</v>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>lps22hb (LPS22HB), lps25hb (LPS25HB), lps28dfw (LPS28DFW), lps33hw (LPS33HW), lps35hw (LPS35HW)</t>
+          <t>lps28dfw (LPS28DFW), lps22hb (LPS22HB), lps25hb (LPS25HB), lps33hw (LPS33HW), lps35hw (LPS35HW)</t>
         </is>
       </c>
     </row>
@@ -19784,8 +20469,8 @@
           <t>0x5F</t>
         </is>
       </c>
-      <c r="B54" s="33" t="inlineStr"/>
-      <c r="C54" s="33" t="n">
+      <c r="B54" s="34" t="inlineStr"/>
+      <c r="C54" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -19795,50 +20480,50 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="34" t="inlineStr">
+      <c r="A55" s="35" t="inlineStr">
         <is>
           <t>0x60</t>
         </is>
       </c>
-      <c r="B55" s="33" t="inlineStr"/>
-      <c r="C55" s="35" t="n">
+      <c r="B55" s="34" t="inlineStr"/>
+      <c r="C55" s="36" t="n">
         <v>3</v>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>mcp9601 (MCP9601), mpl115a2 (MPL115A2), vcnl4040 (VCNL4040)</t>
+          <t>mpl115a2 (MPL115A2), vcnl4040 (VCNL4040), mcp9601 (MCP9601)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="34" t="inlineStr">
+      <c r="A56" s="35" t="inlineStr">
         <is>
           <t>0x61</t>
         </is>
       </c>
-      <c r="B56" s="33" t="inlineStr"/>
-      <c r="C56" s="35" t="n">
+      <c r="B56" s="34" t="inlineStr"/>
+      <c r="C56" s="36" t="n">
         <v>2</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>mcp9601 (MCP9601), scd30 (SCD30)</t>
+          <t>scd30 (SCD30), mcp9601 (MCP9601)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="34" t="inlineStr">
+      <c r="A57" s="35" t="inlineStr">
         <is>
           <t>0x62</t>
         </is>
       </c>
-      <c r="B57" s="33" t="inlineStr"/>
-      <c r="C57" s="35" t="n">
+      <c r="B57" s="34" t="inlineStr"/>
+      <c r="C57" s="36" t="n">
         <v>2</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>mcp9601 (MCP9601), scd40 (SCD40/SCD41)</t>
+          <t>scd40 (SCD40/SCD41), mcp9601 (MCP9601)</t>
         </is>
       </c>
     </row>
@@ -19848,8 +20533,8 @@
           <t>0x63</t>
         </is>
       </c>
-      <c r="B58" s="33" t="inlineStr"/>
-      <c r="C58" s="33" t="n">
+      <c r="B58" s="34" t="inlineStr"/>
+      <c r="C58" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -19864,8 +20549,8 @@
           <t>0x64</t>
         </is>
       </c>
-      <c r="B59" s="33" t="inlineStr"/>
-      <c r="C59" s="33" t="n">
+      <c r="B59" s="34" t="inlineStr"/>
+      <c r="C59" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -19880,8 +20565,8 @@
           <t>0x65</t>
         </is>
       </c>
-      <c r="B60" s="33" t="inlineStr"/>
-      <c r="C60" s="33" t="n">
+      <c r="B60" s="34" t="inlineStr"/>
+      <c r="C60" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -19896,8 +20581,8 @@
           <t>0x66</t>
         </is>
       </c>
-      <c r="B61" s="33" t="inlineStr"/>
-      <c r="C61" s="33" t="n">
+      <c r="B61" s="34" t="inlineStr"/>
+      <c r="C61" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -19912,8 +20597,8 @@
           <t>0x67</t>
         </is>
       </c>
-      <c r="B62" s="33" t="inlineStr"/>
-      <c r="C62" s="33" t="n">
+      <c r="B62" s="34" t="inlineStr"/>
+      <c r="C62" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -19928,8 +20613,8 @@
           <t>0x68</t>
         </is>
       </c>
-      <c r="B63" s="33" t="inlineStr"/>
-      <c r="C63" s="33" t="n">
+      <c r="B63" s="34" t="inlineStr"/>
+      <c r="C63" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -19939,13 +20624,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="34" t="inlineStr">
+      <c r="A64" s="35" t="inlineStr">
         <is>
           <t>0x69</t>
         </is>
       </c>
-      <c r="B64" s="33" t="inlineStr"/>
-      <c r="C64" s="35" t="n">
+      <c r="B64" s="34" t="inlineStr"/>
+      <c r="C64" s="36" t="n">
         <v>4</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -19960,8 +20645,8 @@
           <t>0x6B</t>
         </is>
       </c>
-      <c r="B65" s="33" t="inlineStr"/>
-      <c r="C65" s="33" t="n">
+      <c r="B65" s="34" t="inlineStr"/>
+      <c r="C65" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -19971,13 +20656,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="34" t="inlineStr">
+      <c r="A66" s="35" t="inlineStr">
         <is>
           <t>0x70</t>
         </is>
       </c>
-      <c r="B66" s="33" t="inlineStr"/>
-      <c r="C66" s="35" t="n">
+      <c r="B66" s="34" t="inlineStr"/>
+      <c r="C66" s="36" t="n">
         <v>2</v>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -19987,20 +20672,20 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="36" t="inlineStr">
+      <c r="A67" s="37" t="inlineStr">
         <is>
           <t>0x71</t>
         </is>
       </c>
-      <c r="B67" s="37" t="inlineStr">
+      <c r="B67" s="38" t="inlineStr">
         <is>
           <t>MUX</t>
         </is>
       </c>
-      <c r="C67" s="36" t="n">
+      <c r="C67" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D67" s="38" t="inlineStr">
+      <c r="D67" s="39" t="inlineStr">
         <is>
           <t>pct2075 (PCT2075)</t>
         </is>
@@ -20012,8 +20697,8 @@
           <t>0x72</t>
         </is>
       </c>
-      <c r="B68" s="33" t="inlineStr"/>
-      <c r="C68" s="33" t="n">
+      <c r="B68" s="34" t="inlineStr"/>
+      <c r="C68" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -20028,8 +20713,8 @@
           <t>0x73</t>
         </is>
       </c>
-      <c r="B69" s="33" t="inlineStr"/>
-      <c r="C69" s="33" t="n">
+      <c r="B69" s="34" t="inlineStr"/>
+      <c r="C69" s="34" t="n">
         <v>1</v>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -20039,13 +20724,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="34" t="inlineStr">
+      <c r="A70" s="35" t="inlineStr">
         <is>
           <t>0x74</t>
         </is>
       </c>
-      <c r="B70" s="33" t="inlineStr"/>
-      <c r="C70" s="35" t="n">
+      <c r="B70" s="34" t="inlineStr"/>
+      <c r="C70" s="36" t="n">
         <v>2</v>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -20055,13 +20740,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="34" t="inlineStr">
+      <c r="A71" s="35" t="inlineStr">
         <is>
           <t>0x75</t>
         </is>
       </c>
-      <c r="B71" s="33" t="inlineStr"/>
-      <c r="C71" s="35" t="n">
+      <c r="B71" s="34" t="inlineStr"/>
+      <c r="C71" s="36" t="n">
         <v>2</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -20071,13 +20756,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="34" t="inlineStr">
+      <c r="A72" s="35" t="inlineStr">
         <is>
           <t>0x76</t>
         </is>
       </c>
-      <c r="B72" s="33" t="inlineStr"/>
-      <c r="C72" s="35" t="n">
+      <c r="B72" s="34" t="inlineStr"/>
+      <c r="C72" s="36" t="n">
         <v>11</v>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -20087,20 +20772,20 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="36" t="inlineStr">
+      <c r="A73" s="37" t="inlineStr">
         <is>
           <t>0x77</t>
         </is>
       </c>
-      <c r="B73" s="37" t="inlineStr">
+      <c r="B73" s="38" t="inlineStr">
         <is>
           <t>MUX</t>
         </is>
       </c>
-      <c r="C73" s="36" t="n">
+      <c r="C73" s="37" t="n">
         <v>10</v>
       </c>
-      <c r="D73" s="38" t="inlineStr">
+      <c r="D73" s="39" t="inlineStr">
         <is>
           <t>pct2075 (PCT2075), as7331 (AS7331), bme280 (BME280), bme680 (BME680), bme688 (BME688), bmp280 (BMP280), bmp388 (BMP388), bmp390 (BMP390), dps310 (DPS310), spa06_003 (SPA06-003)</t>
         </is>

--- a/hil_i2c_components.xlsx
+++ b/hil_i2c_components.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Component Matrix" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HIL Mux Layout" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Address Conflicts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Fixtures" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Component Matrix'!$A$1:$CG$93</definedName>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,8 +81,17 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -166,6 +176,66 @@
         <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
+        <bgColor rgb="00FFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCE5FF"/>
+        <bgColor rgb="00CCE5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9FFD9"/>
+        <bgColor rgb="00D9FFD9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5CCFF"/>
+        <bgColor rgb="00E5CCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFCC"/>
+        <bgColor rgb="00FFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CCF2FF"/>
+        <bgColor rgb="00CCF2FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE5CC"/>
+        <bgColor rgb="00FFE5CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6E6E6"/>
+        <bgColor rgb="00E6E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD9CC"/>
+        <bgColor rgb="00FFD9CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F0F0"/>
+        <bgColor rgb="00F0F0F0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -213,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -291,6 +361,88 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -23809,4 +23961,7770 @@
   <autoFilter ref="A1:D73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G285"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Test Fixtures by Measured Phenomenon</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Phenomenon</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t># Components</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Suggested Test Fixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>Temperature</t>
+        </is>
+      </c>
+      <c r="B4" s="40" t="n">
+        <v>55</v>
+      </c>
+      <c r="C4" s="40" t="inlineStr">
+        <is>
+          <t>Heat source / Peltier module for warming and cooling; thermally isolated enclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="41" t="inlineStr">
+        <is>
+          <t>Humidity</t>
+        </is>
+      </c>
+      <c r="B5" s="41" t="n">
+        <v>28</v>
+      </c>
+      <c r="C5" s="41" t="inlineStr">
+        <is>
+          <t>Sealed enclosure with wet sponge / desiccant; or ultrasonic humidifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="42" t="inlineStr">
+        <is>
+          <t>Gas / Air Quality</t>
+        </is>
+      </c>
+      <c r="B6" s="42" t="n">
+        <v>25</v>
+      </c>
+      <c r="C6" s="42" t="inlineStr">
+        <is>
+          <t>Sealed chamber with known VOC source (e.g. isopropyl alcohol swab); clean air baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Pressure</t>
+        </is>
+      </c>
+      <c r="B7" s="43" t="n">
+        <v>19</v>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>Sealed chamber with hand pump or syringe for pressure changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="44" t="inlineStr">
+        <is>
+          <t>Light</t>
+        </is>
+      </c>
+      <c r="B8" s="44" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t>Dimmable LED or lamp with known lux levels; light-tight enclosure for dark baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="45" t="inlineStr">
+        <is>
+          <t>Proximity / ToF</t>
+        </is>
+      </c>
+      <c r="B9" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" s="45" t="inlineStr">
+        <is>
+          <t>Servo-driven target at known distances; flat reflective surface</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="46" t="inlineStr">
+        <is>
+          <t>Current / Voltage</t>
+        </is>
+      </c>
+      <c r="B10" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" s="46" t="inlineStr">
+        <is>
+          <t>Programmable power supply or known resistive load; DAC for voltage reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="47" t="inlineStr">
+        <is>
+          <t>Particulate Matter</t>
+        </is>
+      </c>
+      <c r="B11" s="47" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="47" t="inlineStr">
+        <is>
+          <t>Sealed chamber with smoke/dust source; HEPA-filtered clean air baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="48" t="inlineStr">
+        <is>
+          <t>Temperature (IR)</t>
+        </is>
+      </c>
+      <c r="B12" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="48" t="inlineStr">
+        <is>
+          <t>IR heat lamp or warm object at known distance; background target for baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="49" t="inlineStr">
+        <is>
+          <t>Other (Percent)</t>
+        </is>
+      </c>
+      <c r="B13" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="49" t="inlineStr">
+        <is>
+          <t>Depends on specific sensor (e.g. soil moisture probe in wet/dry soil)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Multi-Phenomenon Sensors (need multiple fixtures)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>Display Name</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>Phenomena</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>bme680</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>BME680</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Gas / Air Quality, Humidity, Pressure, Temperature</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>bme688</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>BME688</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Gas / Air Quality, Humidity, Pressure, Temperature</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>sen54</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SEN54</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Gas / Air Quality, Humidity, Particulate Matter, Temperature</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>sen55</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SEN55</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Gas / Air Quality, Humidity, Particulate Matter, Temperature</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>sen5x</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SEN5x</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Gas / Air Quality, Humidity, Particulate Matter, Temperature</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>sen66</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SEN66</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Gas / Air Quality, Humidity, Particulate Matter, Temperature</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0x6B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>bme280</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>BME280</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Pressure, Temperature</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ms8607</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>MS8607</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Pressure, Temperature</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>scd30</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SCD30</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Gas / Air Quality, Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0x61</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>scd40</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SCD40/SCD41</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Gas / Air Quality, Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0x62</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>aht20</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>AHT20</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>aht21</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>AHT21</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>am2301b</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>AM2301B</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>am2315c</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>AM2315C</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>apds9999</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>APDS9999</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Light, Proximity / ToF</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>0x52</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>bmp280</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>BMP280</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Pressure, Temperature</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>bmp388</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>BMP388</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Pressure, Temperature</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch4</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>bmp390</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>BMP390</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Pressure, Temperature</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch5</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>bmp580</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>BMP580</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Pressure, Temperature</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>0x47</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>bmp581</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>BMP581</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Pressure, Temperature</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>0x46</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>bmp585</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>BMP585</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Pressure, Temperature</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>0x47</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>d6t1a</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>D6T-1A Thermal Sensor</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Temperature, Temperature (IR)</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>0x0A</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>dht20</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>DHT20</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch4</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>dps310</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>DPS310</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Pressure, Temperature</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch6</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>hdc302x</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>HDC302x</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>0x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>hts221</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>HTS221</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>0x5F</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>htu21d</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>HTU21D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>htu31d</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>HTU31D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>0x41</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>lc709203f</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>LC709203F</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Current / Voltage, Other (Percent)</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>0x0B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>lps22hb</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>LPS22HB</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Pressure, Temperature</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>lps25hb</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>LPS25HB</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Pressure, Temperature</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>0x5C</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>lps28dfw</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>LPS28DFW</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Pressure, Temperature</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>0x5C</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>lps33hw</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>LPS33HW</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Pressure, Temperature</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>lps35hw</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>LPS35HW</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Pressure, Temperature</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>ltr303</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>LTR-303</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Gas / Air Quality, Light</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>ltr329</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>LTR-329</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Gas / Air Quality, Light</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>ltr390</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>LTR-390</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Gas / Air Quality, Light</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>0x53</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>max17048</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>MAX17048/MAX17049</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Current / Voltage, Other (Percent)</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>0x36</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>mcp9601</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>MCP9601</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Gas / Air Quality, Temperature</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>0x67</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>mlx90632b</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>MLX90632-B (Standard)</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Temperature, Temperature (IR)</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>0x3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>mlx90632d_ext</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>MLX90632 (Extended Mode)</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Temperature, Temperature (IR)</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>0x3B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>mlx90632d_med</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>MLX90632</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Temperature, Temperature (IR)</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>0x3A</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>mpl115a2</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>MPL115A2</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Pressure, Temperature</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>0x60</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>sht20</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SHT20</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>sht30_mesh</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Weatherproof SHT30</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>sht30_shell</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Enclosed SHT30</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>sht3x</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SHT3X</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>0x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>sht40</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SHT40</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>sht41</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SHT41</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>sht45</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SHT45</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch4</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>shtc3</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SHTC3</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>0x70</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>si7021</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Si7021</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Humidity, Temperature</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>spa06_003</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SPA06-003</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Pressure, Temperature</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch7</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>stemma_soil</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>STEMMA Soil Sensor</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Gas / Air Quality, Temperature</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>0x37</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>vcnl4020</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>VCNL4020</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Light, Proximity / ToF</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>0x13</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>vcnl4040</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>VCNL4040</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Light, Proximity / ToF</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>0x60</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>vcnl4200</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>VCNL4200</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Light, Proximity / ToF</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>0x51</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>vl53l4cx</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>VL53L4CX</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Gas / Air Quality, Proximity / ToF</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch5</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>vl6180x</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>VL6180X</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Light, Proximity / ToF</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch6</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="50" t="inlineStr">
+        <is>
+          <t>Components by Phenomenon</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="51" t="inlineStr">
+        <is>
+          <t>Temperature  (55 components)</t>
+        </is>
+      </c>
+      <c r="B80" s="52" t="n"/>
+      <c r="C80" s="52" t="n"/>
+      <c r="D80" s="52" t="n"/>
+      <c r="E80" s="52" t="n"/>
+      <c r="F80" s="52" t="n"/>
+      <c r="G80" s="52" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="53" t="inlineStr">
+        <is>
+          <t>Fixture: Heat source / Peltier module for warming and cooling; thermally isolated enclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="54" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B82" s="54" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C82" s="54" t="inlineStr">
+        <is>
+          <t>Display Name</t>
+        </is>
+      </c>
+      <c r="D82" s="54" t="inlineStr">
+        <is>
+          <t>Sensor Types</t>
+        </is>
+      </c>
+      <c r="E82" s="54" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F82" s="54" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="G82" s="54" t="inlineStr">
+        <is>
+          <t>Jumper Setting</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>d6t1a</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>D6T-1A Thermal Sensor</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, object-temp, object-temp-fahrenheit</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>0x0A</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>hts221</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>HTS221</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>0x5F</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>mcp9601</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>MCP9601</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, raw</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>0x67</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>mcp9808</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>MCP9808</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F86" s="30" t="inlineStr">
+        <is>
+          <t>0x19</t>
+        </is>
+      </c>
+      <c r="G86" s="30" t="inlineStr">
+        <is>
+          <t>A0:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>pct2075</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>PCT2075</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F87" s="30" t="inlineStr">
+        <is>
+          <t>0x35</t>
+        </is>
+      </c>
+      <c r="G87" s="30" t="inlineStr">
+        <is>
+          <t>various</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>sen66</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>SEN66</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pm10-std, pm25-std, pm100-std, voc-index, nox-index, co2</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>0x6B</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>adt7410</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>ADT7410</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F89" s="30" t="inlineStr">
+        <is>
+          <t>0x49</t>
+        </is>
+      </c>
+      <c r="G89" s="30" t="inlineStr">
+        <is>
+          <t>A0:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>aht20</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>AHT20</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>bme280</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>BME280</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pressure, altitude</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F91" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G91" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>bmp580</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>BMP580</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure, altitude</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>0x47</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>bmp581</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>BMP581</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure, altitude</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F93" s="30" t="inlineStr">
+        <is>
+          <t>0x46</t>
+        </is>
+      </c>
+      <c r="G93" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>ds2484</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>DS2484</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>0x18</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>htu21d</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>HTU21D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>htu31d</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>HTU31D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F96" s="30" t="inlineStr">
+        <is>
+          <t>0x41</t>
+        </is>
+      </c>
+      <c r="G96" s="30" t="inlineStr">
+        <is>
+          <t>ADDR:VDD</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>lps22hb</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>LPS22HB</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>lps25hb</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>LPS25HB</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F98" s="30" t="inlineStr">
+        <is>
+          <t>0x5C</t>
+        </is>
+      </c>
+      <c r="G98" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>mlx90632b</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>MLX90632-B (Standard)</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, object-temp, object-temp-fahrenheit</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>0x3A</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>mlx90632d_ext</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>MLX90632 (Extended Mode)</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, object-temp, object-temp-fahrenheit</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F100" s="30" t="inlineStr">
+        <is>
+          <t>0x3B</t>
+        </is>
+      </c>
+      <c r="G100" s="30" t="inlineStr">
+        <is>
+          <t>alternate</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>mpl115a2</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>MPL115A2</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>0x60</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>scd30</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>SCD30</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, co2</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>0x61</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>scd40</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>SCD40/SCD41</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, co2</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>0x62</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>sht30_mesh</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Weatherproof SHT30</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>sht3x</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>SHT3X</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F105" s="30" t="inlineStr">
+        <is>
+          <t>0x45</t>
+        </is>
+      </c>
+      <c r="G105" s="30" t="inlineStr">
+        <is>
+          <t>ADR:VDD</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>shtc3</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>SHTC3</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>0x70</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>stemma_soil</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>STEMMA Soil Sensor</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, raw</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F107" s="30" t="inlineStr">
+        <is>
+          <t>0x37</t>
+        </is>
+      </c>
+      <c r="G107" s="30" t="inlineStr">
+        <is>
+          <t>AD0:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>tc74a0</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>TC74A0</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>0x48</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>tmp117</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>TMP117</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F109" s="30" t="inlineStr">
+        <is>
+          <t>0x4B</t>
+        </is>
+      </c>
+      <c r="G109" s="30" t="inlineStr">
+        <is>
+          <t>ADDR/AD0 solder jumper on back. Default (open/pin ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>aht21</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>AHT21</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>bme680</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>BME680</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pressure, altitude, gas-resistance</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F111" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G111" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>bmp585</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>BMP585</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure, altitude</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>0x47</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>hdc302x</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>HDC302x</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F113" s="30" t="inlineStr">
+        <is>
+          <t>0x45</t>
+        </is>
+      </c>
+      <c r="G113" s="30" t="inlineStr">
+        <is>
+          <t>A0:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>lps28dfw</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>LPS28DFW</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>0x5C</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>lps33hw</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>LPS33HW</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>mlx90632d_med</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>MLX90632</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, object-temp, object-temp-fahrenheit</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>0x3A</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>sen54</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>SEN54</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pm10-std, pm25-std, pm100-std, voc-index</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>sht20</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>SHT20</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>sht30_shell</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Enclosed SHT30</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>tmp119</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>TMP119</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>0x48</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>am2301b</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>AM2301B</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>bme688</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>BME688</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pressure, altitude, gas-resistance</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F122" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G122" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>lps35hw</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>LPS35HW</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>sen55</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>SEN55</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pm10-std, pm25-std, pm100-std, voc-index, nox-index</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>sht40</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>SHT40</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>si7021</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Si7021</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>am2315c</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>AM2315C</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>bmp280</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>BMP280</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure, altitude</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="F128" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G128" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>ms8607</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>MS8607</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pressure</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>sen5x</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>SEN5x</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pm10-std, pm25-std, pm100-std, voc-index, nox-index</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>sht41</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>SHT41</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>bmp388</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>BMP388</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure, altitude</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch4</t>
+        </is>
+      </c>
+      <c r="F132" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G132" s="30" t="inlineStr">
+        <is>
+          <t>ADDR:closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>dht20</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>DHT20</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch4</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>sht45</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>SHT45</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch4</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>bmp390</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>BMP390</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure, altitude</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch5</t>
+        </is>
+      </c>
+      <c r="F135" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G135" s="30" t="inlineStr">
+        <is>
+          <t>ADDR:closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>dps310</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>DPS310</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch6</t>
+        </is>
+      </c>
+      <c r="F136" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G136" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>spa06_003</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>SPA06-003</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch7</t>
+        </is>
+      </c>
+      <c r="F137" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G137" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="55" t="inlineStr">
+        <is>
+          <t>Humidity  (28 components)</t>
+        </is>
+      </c>
+      <c r="B139" s="56" t="n"/>
+      <c r="C139" s="56" t="n"/>
+      <c r="D139" s="56" t="n"/>
+      <c r="E139" s="56" t="n"/>
+      <c r="F139" s="56" t="n"/>
+      <c r="G139" s="56" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="53" t="inlineStr">
+        <is>
+          <t>Fixture: Sealed enclosure with wet sponge / desiccant; or ultrasonic humidifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="57" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B141" s="57" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C141" s="57" t="inlineStr">
+        <is>
+          <t>Display Name</t>
+        </is>
+      </c>
+      <c r="D141" s="57" t="inlineStr">
+        <is>
+          <t>Sensor Types</t>
+        </is>
+      </c>
+      <c r="E141" s="57" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F141" s="57" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="G141" s="57" t="inlineStr">
+        <is>
+          <t>Jumper Setting</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>hts221</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>HTS221</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>0x5F</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>sen66</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>SEN66</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pm10-std, pm25-std, pm100-std, voc-index, nox-index, co2</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>0x6B</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>aht20</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>AHT20</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>bme280</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>BME280</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pressure, altitude</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F145" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G145" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>htu21d</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>HTU21D</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>htu31d</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>HTU31D</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F147" s="30" t="inlineStr">
+        <is>
+          <t>0x41</t>
+        </is>
+      </c>
+      <c r="G147" s="30" t="inlineStr">
+        <is>
+          <t>ADDR:VDD</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>scd30</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>SCD30</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, co2</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>0x61</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>scd40</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>SCD40/SCD41</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, co2</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>0x62</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>sht30_mesh</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Weatherproof SHT30</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>sht3x</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>SHT3X</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F151" s="30" t="inlineStr">
+        <is>
+          <t>0x45</t>
+        </is>
+      </c>
+      <c r="G151" s="30" t="inlineStr">
+        <is>
+          <t>ADR:VDD</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>shtc3</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>SHTC3</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>0x70</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>aht21</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>AHT21</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>bme680</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>BME680</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pressure, altitude, gas-resistance</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F154" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G154" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>hdc302x</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>HDC302x</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F155" s="30" t="inlineStr">
+        <is>
+          <t>0x45</t>
+        </is>
+      </c>
+      <c r="G155" s="30" t="inlineStr">
+        <is>
+          <t>A0:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>sen54</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>SEN54</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pm10-std, pm25-std, pm100-std, voc-index</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>sht20</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>SHT20</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>sht30_shell</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Enclosed SHT30</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>am2301b</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>AM2301B</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>bme688</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>BME688</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pressure, altitude, gas-resistance</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F160" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G160" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>sen55</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>SEN55</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pm10-std, pm25-std, pm100-std, voc-index, nox-index</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>sht40</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>SHT40</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>si7021</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Si7021</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>am2315c</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>AM2315C</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>ms8607</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>MS8607</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pressure</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>sen5x</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>SEN5x</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pm10-std, pm25-std, pm100-std, voc-index, nox-index</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>sht41</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>SHT41</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>dht20</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>DHT20</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch4</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>0x38</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>sht45</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>SHT45</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch4</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>0x44</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="58" t="inlineStr">
+        <is>
+          <t>Gas / Air Quality  (25 components)</t>
+        </is>
+      </c>
+      <c r="B171" s="59" t="n"/>
+      <c r="C171" s="59" t="n"/>
+      <c r="D171" s="59" t="n"/>
+      <c r="E171" s="59" t="n"/>
+      <c r="F171" s="59" t="n"/>
+      <c r="G171" s="59" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="53" t="inlineStr">
+        <is>
+          <t>Fixture: Sealed chamber with known VOC source (e.g. isopropyl alcohol swab); clean air baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="60" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B173" s="60" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C173" s="60" t="inlineStr">
+        <is>
+          <t>Display Name</t>
+        </is>
+      </c>
+      <c r="D173" s="60" t="inlineStr">
+        <is>
+          <t>Sensor Types</t>
+        </is>
+      </c>
+      <c r="E173" s="60" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F173" s="60" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="G173" s="60" t="inlineStr">
+        <is>
+          <t>Jumper Setting</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>mcp3421</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>MCP3421</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>0x68</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>mcp9601</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>MCP9601</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, raw</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>0x67</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>rotary_encoder</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>STEMMA QT Rotary Encoder</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F176" s="30" t="inlineStr">
+        <is>
+          <t>0x3C</t>
+        </is>
+      </c>
+      <c r="G176" s="30" t="inlineStr">
+        <is>
+          <t>A1:1 A2:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>sen66</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>SEN66</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pm10-std, pm25-std, pm100-std, voc-index, nox-index, co2</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>0x6B</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>sgp30</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>SGP30</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>eco2, tvoc</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>0x58</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>as5600</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>AS5600 Magnetic Angle</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>0x36</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>as7331</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>AS7331</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>0x74</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>ltr303</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>LTR-303</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>light, raw</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>ltr390</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>LTR-390</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>light, raw</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>0x53</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>nau7802</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>NAU7802</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>0x2A</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>qmc5883p</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>QMC5883P</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>0x2C</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>scd30</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>SCD30</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, co2</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>0x61</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>scd40</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>SCD40/SCD41</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, co2</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>0x62</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>sgp40</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>SGP40</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>voc-index, raw</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>0x59</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>stemma_soil</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>STEMMA Soil Sensor</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, raw</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F188" s="30" t="inlineStr">
+        <is>
+          <t>0x37</t>
+        </is>
+      </c>
+      <c r="G188" s="30" t="inlineStr">
+        <is>
+          <t>AD0:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>bme680</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>BME680</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pressure, altitude, gas-resistance</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F189" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G189" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>ens160</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>ENS160</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>tvoc, eco2, raw</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>0x52</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>ens161</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>ENS161</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>tvoc, eco2, raw</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F191" s="30" t="inlineStr">
+        <is>
+          <t>0x53</t>
+        </is>
+      </c>
+      <c r="G191" s="30" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>ltr329</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>LTR-329</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>light, raw</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>sen54</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>SEN54</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pm10-std, pm25-std, pm100-std, voc-index</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>sgp41</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>SGP41</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>voc-index, nox-index, raw</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>0x59</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>bme688</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>BME688</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pressure, altitude, gas-resistance</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F195" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G195" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>sen55</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>SEN55</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pm10-std, pm25-std, pm100-std, voc-index, nox-index</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>sen5x</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>SEN5x</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pm10-std, pm25-std, pm100-std, voc-index, nox-index</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>vl53l4cx</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>VL53L4CX</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>proximity, raw</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch5</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="61" t="inlineStr">
+        <is>
+          <t>Pressure  (19 components)</t>
+        </is>
+      </c>
+      <c r="B200" s="62" t="n"/>
+      <c r="C200" s="62" t="n"/>
+      <c r="D200" s="62" t="n"/>
+      <c r="E200" s="62" t="n"/>
+      <c r="F200" s="62" t="n"/>
+      <c r="G200" s="62" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="53" t="inlineStr">
+        <is>
+          <t>Fixture: Sealed chamber with hand pump or syringe for pressure changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="63" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B202" s="63" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C202" s="63" t="inlineStr">
+        <is>
+          <t>Display Name</t>
+        </is>
+      </c>
+      <c r="D202" s="63" t="inlineStr">
+        <is>
+          <t>Sensor Types</t>
+        </is>
+      </c>
+      <c r="E202" s="63" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F202" s="63" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="G202" s="63" t="inlineStr">
+        <is>
+          <t>Jumper Setting</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>bme280</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>BME280</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pressure, altitude</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F203" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G203" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>bmp580</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>BMP580</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure, altitude</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>0x47</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>bmp581</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>BMP581</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure, altitude</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F205" s="30" t="inlineStr">
+        <is>
+          <t>0x46</t>
+        </is>
+      </c>
+      <c r="G205" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>lps22hb</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>LPS22HB</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>lps25hb</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>LPS25HB</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F207" s="30" t="inlineStr">
+        <is>
+          <t>0x5C</t>
+        </is>
+      </c>
+      <c r="G207" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>mpl115a2</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>MPL115A2</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>0x60</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>bme680</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>BME680</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pressure, altitude, gas-resistance</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F209" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G209" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>bmp585</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>BMP585</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure, altitude</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>0x47</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>lps28dfw</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>LPS28DFW</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>0x5C</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>lps33hw</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>LPS33HW</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>mprls</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>MPRLS</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>pressure</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>0x18</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>bme688</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>BME688</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pressure, altitude, gas-resistance</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F214" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G214" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>lps35hw</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>LPS35HW</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>0x5D</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>bmp280</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>BMP280</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure, altitude</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="F216" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G216" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>ms8607</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>MS8607</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pressure</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>0x40</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>bmp388</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>BMP388</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure, altitude</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch4</t>
+        </is>
+      </c>
+      <c r="F218" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G218" s="30" t="inlineStr">
+        <is>
+          <t>ADDR:closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>bmp390</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>BMP390</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure, altitude</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch5</t>
+        </is>
+      </c>
+      <c r="F219" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G219" s="30" t="inlineStr">
+        <is>
+          <t>ADDR:closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>dps310</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>DPS310</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch6</t>
+        </is>
+      </c>
+      <c r="F220" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G220" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>spa06_003</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>SPA06-003</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, pressure</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch7</t>
+        </is>
+      </c>
+      <c r="F221" s="30" t="inlineStr">
+        <is>
+          <t>0x76</t>
+        </is>
+      </c>
+      <c r="G221" s="30" t="inlineStr">
+        <is>
+          <t>SDO:GND</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="64" t="inlineStr">
+        <is>
+          <t>Light  (12 components)</t>
+        </is>
+      </c>
+      <c r="B223" s="65" t="n"/>
+      <c r="C223" s="65" t="n"/>
+      <c r="D223" s="65" t="n"/>
+      <c r="E223" s="65" t="n"/>
+      <c r="F223" s="65" t="n"/>
+      <c r="G223" s="65" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="53" t="inlineStr">
+        <is>
+          <t>Fixture: Dimmable LED or lamp with known lux levels; light-tight enclosure for dark baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="66" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B225" s="66" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C225" s="66" t="inlineStr">
+        <is>
+          <t>Display Name</t>
+        </is>
+      </c>
+      <c r="D225" s="66" t="inlineStr">
+        <is>
+          <t>Sensor Types</t>
+        </is>
+      </c>
+      <c r="E225" s="66" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F225" s="66" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="G225" s="66" t="inlineStr">
+        <is>
+          <t>Jumper Setting</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>bh1750</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>BH1750</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>0x23</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>vcnl4020</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>VCNL4020</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>light, proximity</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>0x13</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>vcnl4200</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>VCNL4200</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>light, proximity</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>0x51</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>veml7700</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>VEML7700</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>0x10</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>apds9999</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>APDS9999</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>light, proximity</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>0x52</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>ltr303</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>LTR-303</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>light, raw</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>ltr390</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>LTR-390</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>light, raw</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>0x53</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>max44009</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>MAX44009</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>0x4A</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>tsl2591</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>TSL2591</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F234" s="30" t="inlineStr">
+        <is>
+          <t>0x39</t>
+        </is>
+      </c>
+      <c r="G234" s="30" t="inlineStr">
+        <is>
+          <t>mux isolation</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>ltr329</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>LTR-329</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>light, raw</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>vcnl4040</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>VCNL4040</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>light, proximity</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>0x60</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>vl6180x</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>VL6180X</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>proximity, light</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch6</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="67" t="inlineStr">
+        <is>
+          <t>Proximity / ToF  (9 components)</t>
+        </is>
+      </c>
+      <c r="B239" s="68" t="n"/>
+      <c r="C239" s="68" t="n"/>
+      <c r="D239" s="68" t="n"/>
+      <c r="E239" s="68" t="n"/>
+      <c r="F239" s="68" t="n"/>
+      <c r="G239" s="68" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="53" t="inlineStr">
+        <is>
+          <t>Fixture: Servo-driven target at known distances; flat reflective surface</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="69" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B241" s="69" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C241" s="69" t="inlineStr">
+        <is>
+          <t>Display Name</t>
+        </is>
+      </c>
+      <c r="D241" s="69" t="inlineStr">
+        <is>
+          <t>Sensor Types</t>
+        </is>
+      </c>
+      <c r="E241" s="69" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F241" s="69" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="G241" s="69" t="inlineStr">
+        <is>
+          <t>Jumper Setting</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>vcnl4020</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>VCNL4020</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>light, proximity</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>0x13</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>vcnl4200</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>VCNL4200</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>light, proximity</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>0x51</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>apds9999</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>APDS9999</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>light, proximity</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>0x52</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>vcnl4040</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>VCNL4040</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>light, proximity</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>0x60</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>vl53l0x</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>VL53L0X</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>proximity</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>vl53l1x</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>VL53L1X</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>proximity</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>vl53l4cd</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>VL53L4CD</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>proximity</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch4</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>vl53l4cx</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>VL53L4CX</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>proximity, raw</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch5</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>vl6180x</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>VL6180X</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>proximity, light</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch6</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="70" t="inlineStr">
+        <is>
+          <t>Current / Voltage  (7 components)</t>
+        </is>
+      </c>
+      <c r="B252" s="71" t="n"/>
+      <c r="C252" s="71" t="n"/>
+      <c r="D252" s="71" t="n"/>
+      <c r="E252" s="71" t="n"/>
+      <c r="F252" s="71" t="n"/>
+      <c r="G252" s="71" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="53" t="inlineStr">
+        <is>
+          <t>Fixture: Programmable power supply or known resistive load; DAC for voltage reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="72" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B254" s="72" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C254" s="72" t="inlineStr">
+        <is>
+          <t>Display Name</t>
+        </is>
+      </c>
+      <c r="D254" s="72" t="inlineStr">
+        <is>
+          <t>Sensor Types</t>
+        </is>
+      </c>
+      <c r="E254" s="72" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F254" s="72" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="G254" s="72" t="inlineStr">
+        <is>
+          <t>Jumper Setting</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>lc709203f</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>LC709203F</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>voltage, unitless-percent</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>0x0B</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>ina219</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>INA219</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>voltage, current</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F256" s="30" t="inlineStr">
+        <is>
+          <t>0x41</t>
+        </is>
+      </c>
+      <c r="G256" s="30" t="inlineStr">
+        <is>
+          <t>A0:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>max17048</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>MAX17048/MAX17049</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>voltage, unitless-percent</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>0x36</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>ina228</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>INA228</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>voltage, current</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F258" s="30" t="inlineStr">
+        <is>
+          <t>0x41</t>
+        </is>
+      </c>
+      <c r="G258" s="30" t="inlineStr">
+        <is>
+          <t>A0:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>ina237</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>INA237</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>voltage, current</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F259" s="30" t="inlineStr">
+        <is>
+          <t>0x45</t>
+        </is>
+      </c>
+      <c r="G259" s="30" t="inlineStr">
+        <is>
+          <t>A0:1 A1:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>ina238</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>INA238</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>voltage, current</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="F260" s="30" t="inlineStr">
+        <is>
+          <t>0x41</t>
+        </is>
+      </c>
+      <c r="G260" s="30" t="inlineStr">
+        <is>
+          <t>A0:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>ina260</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>INA260</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>voltage, current</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="F261" s="30" t="inlineStr">
+        <is>
+          <t>0x45</t>
+        </is>
+      </c>
+      <c r="G261" s="30" t="inlineStr">
+        <is>
+          <t>A0:1 A1:1</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="73" t="inlineStr">
+        <is>
+          <t>Particulate Matter  (6 components)</t>
+        </is>
+      </c>
+      <c r="B263" s="74" t="n"/>
+      <c r="C263" s="74" t="n"/>
+      <c r="D263" s="74" t="n"/>
+      <c r="E263" s="74" t="n"/>
+      <c r="F263" s="74" t="n"/>
+      <c r="G263" s="74" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="53" t="inlineStr">
+        <is>
+          <t>Fixture: Sealed chamber with smoke/dust source; HEPA-filtered clean air baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="75" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B265" s="75" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C265" s="75" t="inlineStr">
+        <is>
+          <t>Display Name</t>
+        </is>
+      </c>
+      <c r="D265" s="75" t="inlineStr">
+        <is>
+          <t>Sensor Types</t>
+        </is>
+      </c>
+      <c r="E265" s="75" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F265" s="75" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="G265" s="75" t="inlineStr">
+        <is>
+          <t>Jumper Setting</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>pmsa003i</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>PMSA003I</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>pm10-std, pm25-std, pm100-std</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>0x12</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>sen66</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>SEN66</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pm10-std, pm25-std, pm100-std, voc-index, nox-index, co2</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>0x6B</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>sen50</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>SEN50</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>pm10-std, pm25-std, pm100-std</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>sen54</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>SEN54</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pm10-std, pm25-std, pm100-std, voc-index</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>sen55</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>SEN55</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pm10-std, pm25-std, pm100-std, voc-index, nox-index</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch2</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>sen5x</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>SEN5x</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, humidity, pm10-std, pm25-std, pm100-std, voc-index, nox-index</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch3</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>0x69</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="76" t="inlineStr">
+        <is>
+          <t>Temperature (IR)  (4 components)</t>
+        </is>
+      </c>
+      <c r="B273" s="77" t="n"/>
+      <c r="C273" s="77" t="n"/>
+      <c r="D273" s="77" t="n"/>
+      <c r="E273" s="77" t="n"/>
+      <c r="F273" s="77" t="n"/>
+      <c r="G273" s="77" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="53" t="inlineStr">
+        <is>
+          <t>Fixture: IR heat lamp or warm object at known distance; background target for baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="78" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B275" s="78" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C275" s="78" t="inlineStr">
+        <is>
+          <t>Display Name</t>
+        </is>
+      </c>
+      <c r="D275" s="78" t="inlineStr">
+        <is>
+          <t>Sensor Types</t>
+        </is>
+      </c>
+      <c r="E275" s="78" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F275" s="78" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="G275" s="78" t="inlineStr">
+        <is>
+          <t>Jumper Setting</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>d6t1a</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>D6T-1A Thermal Sensor</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, object-temp, object-temp-fahrenheit</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>0x0A</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>mlx90632b</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>MLX90632-B (Standard)</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, object-temp, object-temp-fahrenheit</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>0x3A</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>mlx90632d_ext</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>MLX90632 (Extended Mode)</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, object-temp, object-temp-fahrenheit</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch0</t>
+        </is>
+      </c>
+      <c r="F278" s="30" t="inlineStr">
+        <is>
+          <t>0x3B</t>
+        </is>
+      </c>
+      <c r="G278" s="30" t="inlineStr">
+        <is>
+          <t>alternate</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>mlx90632d_med</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>MLX90632</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>ambient-temp, ambient-temp-fahrenheit, object-temp, object-temp-fahrenheit</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>0x3A</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="79" t="inlineStr">
+        <is>
+          <t>Other (Percent)  (2 components)</t>
+        </is>
+      </c>
+      <c r="B281" s="80" t="n"/>
+      <c r="C281" s="80" t="n"/>
+      <c r="D281" s="80" t="n"/>
+      <c r="E281" s="80" t="n"/>
+      <c r="F281" s="80" t="n"/>
+      <c r="G281" s="80" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="53" t="inlineStr">
+        <is>
+          <t>Fixture: Depends on specific sensor (e.g. soil moisture probe in wet/dry soil)</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="81" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B283" s="81" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C283" s="81" t="inlineStr">
+        <is>
+          <t>Display Name</t>
+        </is>
+      </c>
+      <c r="D283" s="81" t="inlineStr">
+        <is>
+          <t>Sensor Types</t>
+        </is>
+      </c>
+      <c r="E283" s="81" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="F283" s="81" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="G283" s="81" t="inlineStr">
+        <is>
+          <t>Jumper Setting</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>lc709203f</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>LC709203F</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>voltage, unitless-percent</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>Direct Bus (No Mux)</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>0x0B</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>max17048</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>MAX17048/MAX17049</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>voltage, unitless-percent</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>TCA9548A (0x77) Ch1</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>0x36</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>